--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:05:55+00:00</t>
+          <t>2026-09-06T01:49:45+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,10 +7841,14 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:05:55+00:00</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr"/>
+          <t>2026-09-06T01:49:45+00:00</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06T01:49:45+00:00</t>
+        </is>
+      </c>
       <c r="L143" s="2" t="inlineStr"/>
       <c r="M143" s="2" t="inlineStr">
         <is>
@@ -7853,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>bcd727033e902d422492c99b8d716bf7cce5ff6d03124686c8cc49839664a511</t>
+          <t>958553c94fe8d44f25b399b78ae9b39395c55d209758a7ae6426edb9802093bd</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:05:55+00:00</t>
+          <t>2026-09-06T01:49:45+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
@@ -7969,7 +7973,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:05:55+00:00</t>
+          <t>2026-09-06T01:49:45+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
@@ -8029,7 +8033,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:05:55+00:00</t>
+          <t>2026-09-06T01:49:45+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:49:45+00:00</t>
+          <t>2026-09-06T01:53:19+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:49:45+00:00</t>
+          <t>2026-09-06T01:53:19+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:49:45+00:00</t>
+          <t>2026-09-06T01:51:27+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>958553c94fe8d44f25b399b78ae9b39395c55d209758a7ae6426edb9802093bd</t>
+          <t>fe9b38f4209ae69a95e44eeb72d10595ac9a7e74cddb9920098ec2d3a8c05dd7</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:49:45+00:00</t>
+          <t>2026-09-06T01:53:19+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:49:45+00:00</t>
+          <t>2026-09-06T01:53:19+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:49:45+00:00</t>
+          <t>2026-09-06T01:53:19+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:53:19+00:00</t>
+          <t>2026-09-06T01:58:05+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:53:19+00:00</t>
+          <t>2026-09-06T01:58:05+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:53:19+00:00</t>
+          <t>2026-09-06T01:58:05+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:53:19+00:00</t>
+          <t>2026-09-06T01:58:05+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:53:19+00:00</t>
+          <t>2026-09-06T01:58:05+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Priority" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programs'!$A$1:$N$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manual Watch'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Priority'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programs'!$A$1:$N$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manual Watch'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Priority'!$A$1:$J$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8321,8 +8321,2052 @@
       </c>
       <c r="N151" s="2" t="inlineStr"/>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Harvard Undergraduate Trading Competition</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>https://harvarduqt.com/</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>2026 - watch the site</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduates</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate intercollegiate trading competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. NOTE: the article's link (harvarduqt.com/competition) is a 404; the root domain works. Class year and team format not published - verify before planning.</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>harvard-undergraduate-trading-competitio</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Stevens High Frequency Trading Competition 2026</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>2026 - dates on the page</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>stevens-high-frequency-trading-competiti</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>IMC Launchpad (US)</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Students - verify class year</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>imc-launchpad-us</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Optiver FutureFocus Chicago 2026</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>2026 - dates on the page</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>optiver-futurefocus-chicago-2026</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>HedgeWest SF Meetup Series</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>https://hedgewestsf.org/</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>hedgewest-sf-meetup-series</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>IAQF Academic Paper Competition</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.iaqf.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Students - verify</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>iaqf-academic-paper-competition</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Open Source Quantitative Finance Conference</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>https://osqf.org/</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>open-source-quantitative-finance-confere</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg Global Trading Challenge</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>TBA for 2026</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr"/>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>CME Group University Trading Challenge</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>University students</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Hull Tactical Market Prediction (Kaggle)</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Rolling - see Kaggle</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Anyone with an account</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Rolling - see Kaggle</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Anyone with an account</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>CFA Institute Research Challenge</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>2026 cycle</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>IICPC Codefest 2026</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>https://codefest.iicpc.com/</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Quantiacs Crypto Contest</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>https://quantiacs.com/</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>2026 contest cycles</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr"/>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>G-Research Spring into Quant Finance 2026</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Spring 2026</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Students - verify</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>IMC Women in Trading and Engineering</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Optiver regional recruitment events (non-US)</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>D. E. Shaw London Insight Programme</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>https://campus.deshaw.com/additional-experiences</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>IMC EU Business Course</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Bank of America APAC Quant Conference</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bofa.com/</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>https://en.tmtpost.com/post/7752441</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Databento partner quant events (Shanghai, London)</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>https://databento.com/</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>CQA Young Professionals Event</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>CMF Select New York 2026</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>FutureAlpha / QuantStrats 2026</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.qwafafew.org/</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Limex Challenge</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>https://challenges.limex.com/</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Quantegies Global Quant Competition</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>https://quantegies.com/</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Future Investment Manager Academy (FIMA)</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>https://fima.partners/</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N151"/>
+  <autoFilter ref="A1:N187"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -8469,6 +10513,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId181"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8754,7 +10834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9650,8 +11730,304 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg Global Trading Challenge</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Never - blocked</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Probed 2026-09-06: robots.txt explicitly DISALLOWS this path, and the page yields 23 characters of text. Respecting robots.txt means this cannot be polled.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Open the Bloomberg for Education portal in your browser.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Check each quarter; 2026 dates were still TBA.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CME Group University Trading Challenge</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Never - blocked</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Probed 2026-09-06: the connection failed for an automated client (no HTTP status returned), which usually indicates bot filtering.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Open cmegroup.com in your browser.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Check in early fall.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Hull Tactical Market Prediction (Kaggle)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Planned - phase 2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Probed 2026-09-06: 42 characters of text - Kaggle pages are JS shells. Automatable via the official Kaggle API once KAGGLE_USERNAME/KAGGLE_KEY secrets exist.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Browse kaggle.com/competitions.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Rolling - never urgent.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Planned - phase 2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Kaggle listing pages are JS shells; use the official Kaggle API.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Browse kaggle.com/competitions.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Rolling.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CFA Institute Research Challenge</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Never - announced off-web</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Entry is via a university-sponsored team, so the binding information arrives through a Stanford club or department, not the CFA Institute page.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Ask Stanford Finance / Traders @ Stanford whether a team is forming.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Early fall.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>IICPC Codefest 2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Never - nothing to diff</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Probed 2026-09-06: 83 characters of visible text. There is nothing to diff even with a browser.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Open codefest.iicpc.com directly.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Check once in spring.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>https://codefest.iicpc.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Quantiacs Crypto Contest</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Never - nothing to diff</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Probed 2026-09-06: 94 characters of visible text; the site is client-rendered.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Open quantiacs.com and check the current contest.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Each quarter.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>https://quantiacs.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>G-Research Spring into Quant Finance 2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Planned - phase 3</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Not probed during ingest. Likely UK-based, which would rule it out on geography.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Open the G-Research events page.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Early spring.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G24"/>
+  <autoFilter ref="A1:G32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -9675,6 +12051,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9686,7 +12070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11249,8 +13633,208 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>C - open entry, participation is the only gate</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Harvard Undergraduate Trading Competition</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Medium-high</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Watch from early fall</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>No - needs phase 3 page watching</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Intercollegiate competitions are team registration rather than individual selection, so entry mostly depends on hearing in time. Same class as Cornell CTC and UChicago UTC.</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>https://harvarduqt.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>C - open entry, participation is the only gate</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Stevens High Frequency Trading Competition 2026</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Medium-high</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Watch from winter</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>No - needs phase 3 page watching</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>An HFT-specific competition is unusually on-point for quant dev, and the page is one of the cleanest to watch of anything added from this article.</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A - high value, do not miss</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>IMC Launchpad (US)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Check site - unpublished</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>No - needs phase 3 page watching</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>A US-based program at a major market maker, and one of the few genuinely new firm programs in this article that is not geography- or identity-gated. Eligibility is unverified, so confirm the class year before investing effort.</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A - high value, do not miss</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Optiver FutureFocus Chicago 2026</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Medium-high</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026 - watch the page</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>No - needs phase 3 page watching</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>The only US-based Optiver student event in the article; the rest are other continents. Recruitment events are a low-cost way onto a firm's radar early.</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -11281,6 +13865,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -8334,7 +8334,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>https://harvarduqt.com/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. NOTE: the article's link (harvarduqt.com/competition) is a 404; the root domain works. Class year and team format not published - verify before planning.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>https://harvarduqt.com/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
     </row>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -8359,7 +8359,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>harvard-undergraduate-trading-competitio</t>
+          <t>harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>stevens-high-frequency-trading-competiti</t>
+          <t>stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>open-source-quantitative-finance-confere</t>
+          <t>open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Priority" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programs'!$A$1:$N$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programs'!$A$1:$N$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manual Watch'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Priority'!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Priority'!$A$1:$J$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N187"/>
+  <dimension ref="A1:N188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10365,8 +10365,68 @@
       </c>
       <c r="N187" s="2" t="inlineStr"/>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>MIT Battlecode 2027</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>https://battlecode.org/</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Register ~early Jan 2027; season runs all January, ends ~Jan 31</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Any undergrad year</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>mit-battlecode-2027</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N187"/>
+  <autoFilter ref="A1:N188"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -10549,6 +10609,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12070,7 +12131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13833,8 +13894,58 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>C - open entry, participation is the only gate</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>MIT Battlecode 2027</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Dec-Jan</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Yes - plain HTML, pollable</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>No application and no MIT affiliation required - registering is the only gate, so probability is entirely up to you. The catch is timing: the whole season runs during January, which overlaps Stanford winter quarter rather than a break, so treat it as a time commitment decision and not a deadline to hit.</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>https://battlecode.org/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:J36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -13869,6 +13980,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:58:05+00:00</t>
+          <t>2026-09-07T16:42:35+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:58:05+00:00</t>
+          <t>2026-09-07T16:42:35+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:51:27+00:00</t>
+          <t>2026-09-07T16:42:35+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>fe9b38f4209ae69a95e44eeb72d10595ac9a7e74cddb9920098ec2d3a8c05dd7</t>
+          <t>7fc143ceb98ac92883eb38c3019bae500ce8ff47db54414363f16c941d4eb4a0</t>
         </is>
       </c>
     </row>
@@ -7909,10 +7909,14 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:58:05+00:00</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr"/>
+          <t>2026-09-07T16:42:35+00:00</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:42:35+00:00</t>
+        </is>
+      </c>
       <c r="L144" s="2" t="inlineStr"/>
       <c r="M144" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7925,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>fa7a84502fd1334e1fadab7feaee57579968a3d92af6b4c1c15b35f7810b3e4f</t>
+          <t>bca8dbaaeab258f990b8a51c80a016985792548fec897f4e2d7f54c215dc4867</t>
         </is>
       </c>
     </row>
@@ -7973,10 +7977,14 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:58:05+00:00</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr"/>
+          <t>2026-09-07T16:42:35+00:00</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:42:35+00:00</t>
+        </is>
+      </c>
       <c r="L145" s="2" t="inlineStr"/>
       <c r="M145" s="2" t="inlineStr">
         <is>
@@ -7985,7 +7993,7 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>c65c8da3aee53cb04884715418e7a0f636544ae6093687a1a0bc56ac58df227b</t>
+          <t>770702cb19ea8d996aed49851c54d2d3a4bc930f4c445257f7e6626ae1b193e8</t>
         </is>
       </c>
     </row>
@@ -8033,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T01:58:05+00:00</t>
+          <t>2026-09-07T16:42:35+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-07T18:18:32+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-07T18:18:32+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-07T18:18:32+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>7fc143ceb98ac92883eb38c3019bae500ce8ff47db54414363f16c941d4eb4a0</t>
+          <t>170fb42f2827b7d4363891200f13444b61566ea7aafc7957e1260e34de21d6c7</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-07T18:18:32+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-07T18:18:32+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-07T18:18:32+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:18:32+00:00</t>
+          <t>2026-09-08T17:18:46+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:18:32+00:00</t>
+          <t>2026-09-08T17:18:46+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:18:32+00:00</t>
+          <t>2026-09-08T17:18:46+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>170fb42f2827b7d4363891200f13444b61566ea7aafc7957e1260e34de21d6c7</t>
+          <t>bb9048572570a77e92c2a6dccdc02b43c0c81ea68043dc3530cd9856848c9166</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:18:32+00:00</t>
+          <t>2026-09-08T17:18:46+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:18:32+00:00</t>
+          <t>2026-09-08T17:18:46+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:18:32+00:00</t>
+          <t>2026-09-08T17:18:46+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:18:46+00:00</t>
+          <t>2026-09-08T17:58:07+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:18:46+00:00</t>
+          <t>2026-09-08T17:58:07+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:18:46+00:00</t>
+          <t>2026-09-08T17:58:07+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:18:46+00:00</t>
+          <t>2026-09-08T17:58:07+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:18:46+00:00</t>
+          <t>2026-09-08T17:58:07+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:58:07+00:00</t>
+          <t>2026-09-08T18:52:26+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:58:07+00:00</t>
+          <t>2026-09-08T18:52:26+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:58:07+00:00</t>
+          <t>2026-09-08T18:52:26+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:58:07+00:00</t>
+          <t>2026-09-08T18:52:26+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:58:07+00:00</t>
+          <t>2026-09-08T18:52:26+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T18:52:26+00:00</t>
+          <t>2026-09-08T19:47:04+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T18:52:26+00:00</t>
+          <t>2026-09-08T19:47:04+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T18:52:26+00:00</t>
+          <t>2026-09-08T19:47:04+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T18:52:26+00:00</t>
+          <t>2026-09-08T19:47:04+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T18:52:26+00:00</t>
+          <t>2026-09-08T19:47:04+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T19:47:04+00:00</t>
+          <t>2026-09-09T12:16:57+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T19:47:04+00:00</t>
+          <t>2026-09-09T12:16:57+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:18:46+00:00</t>
+          <t>2026-09-09T12:16:57+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>bb9048572570a77e92c2a6dccdc02b43c0c81ea68043dc3530cd9856848c9166</t>
+          <t>4ad63790373474da10fedb09d3783c590aa7ab5e6fda532a4eacd09613f2c726</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T19:47:04+00:00</t>
+          <t>2026-09-09T12:16:57+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T19:47:04+00:00</t>
+          <t>2026-09-09T12:16:57+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T19:47:04+00:00</t>
+          <t>2026-09-09T12:16:57+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:16:57+00:00</t>
+          <t>2026-09-09T12:59:11+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:16:57+00:00</t>
+          <t>2026-09-09T12:59:11+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:16:57+00:00</t>
+          <t>2026-09-09T12:59:11+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>4ad63790373474da10fedb09d3783c590aa7ab5e6fda532a4eacd09613f2c726</t>
+          <t>2eed58de6e8c3d84d486cd873c4f279ceaff58ab0808df1d8bb8b2584109392a</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:16:57+00:00</t>
+          <t>2026-09-09T12:59:11+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:16:57+00:00</t>
+          <t>2026-09-09T12:59:11+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:16:57+00:00</t>
+          <t>2026-09-09T12:59:11+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:59:11+00:00</t>
+          <t>2026-09-09T13:55:00+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:59:11+00:00</t>
+          <t>2026-09-09T13:55:00+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:59:11+00:00</t>
+          <t>2026-09-09T13:55:00+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>2eed58de6e8c3d84d486cd873c4f279ceaff58ab0808df1d8bb8b2584109392a</t>
+          <t>e7b033ab2d8e9a42a94767e81740e1f38afa64a09cdd9df04cd9b1a539002b14</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:59:11+00:00</t>
+          <t>2026-09-09T13:55:00+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:59:11+00:00</t>
+          <t>2026-09-09T13:55:00+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T12:59:11+00:00</t>
+          <t>2026-09-09T13:55:00+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:55:00+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:55:00+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:55:00+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>e7b033ab2d8e9a42a94767e81740e1f38afa64a09cdd9df04cd9b1a539002b14</t>
+          <t>8f9ce6596381c64bdbb3b0e4aa51958ff46bb66b9a02cd900564a9de6eb834f9</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:55:00+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:42:35+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr"/>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>bca8dbaaeab258f990b8a51c80a016985792548fec897f4e2d7f54c215dc4867</t>
+          <t>de71475901207962ca947d6f8f4202f2de5be54ec3c1592fc60d8211806d9b25</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:55:00+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T13:55:00+00:00</t>
+          <t>2026-09-10T12:11:00+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-10T12:56:09+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-10T12:56:09+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-10T12:56:09+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-10T12:56:09+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-10T12:56:09+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:56:09+00:00</t>
+          <t>2026-09-10T13:49:13+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:56:09+00:00</t>
+          <t>2026-09-10T13:49:13+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:11:00+00:00</t>
+          <t>2026-09-10T13:49:13+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>8f9ce6596381c64bdbb3b0e4aa51958ff46bb66b9a02cd900564a9de6eb834f9</t>
+          <t>b5f26837f8aa9736997f79129117de740519cbc5848e258bf943fee05ef1e1c4</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:56:09+00:00</t>
+          <t>2026-09-10T13:49:13+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:56:09+00:00</t>
+          <t>2026-09-10T13:49:13+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:56:09+00:00</t>
+          <t>2026-09-10T13:49:13+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:49:13+00:00</t>
+          <t>2026-09-11T04:26:32+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:49:13+00:00</t>
+          <t>2026-09-11T04:26:32+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:49:13+00:00</t>
+          <t>2026-09-11T04:26:32+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>b5f26837f8aa9736997f79129117de740519cbc5848e258bf943fee05ef1e1c4</t>
+          <t>d2a1d6e73cc2a6e238e4d953033362e6346c235c2e5e77b389aca849d48fe70d</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:49:13+00:00</t>
+          <t>2026-09-11T04:26:32+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:49:13+00:00</t>
+          <t>2026-09-11T04:26:32+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:49:13+00:00</t>
+          <t>2026-09-11T04:26:32+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T04:26:32+00:00</t>
+          <t>2026-09-11T12:09:53+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T04:26:32+00:00</t>
+          <t>2026-09-11T12:09:53+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T04:26:32+00:00</t>
+          <t>2026-09-11T12:09:53+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>d2a1d6e73cc2a6e238e4d953033362e6346c235c2e5e77b389aca849d48fe70d</t>
+          <t>1f4428d4719385a1e9cf011e598b42d3a66a8a3da8f3717d0f0f9328bd3e586b</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T04:26:32+00:00</t>
+          <t>2026-09-11T12:09:53+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T04:26:32+00:00</t>
+          <t>2026-09-11T12:09:53+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T04:26:32+00:00</t>
+          <t>2026-09-11T12:09:53+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:53+00:00</t>
+          <t>2026-09-11T12:51:06+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:53+00:00</t>
+          <t>2026-09-11T12:51:06+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:53+00:00</t>
+          <t>2026-09-11T12:51:06+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>1f4428d4719385a1e9cf011e598b42d3a66a8a3da8f3717d0f0f9328bd3e586b</t>
+          <t>5d9f55897ec5a5849a664473999dfa88e9d4a1f06ecaa7cff531b04aecd4df12</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:53+00:00</t>
+          <t>2026-09-11T12:51:06+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:53+00:00</t>
+          <t>2026-09-11T12:51:06+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:53+00:00</t>
+          <t>2026-09-11T12:51:06+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:51:06+00:00</t>
+          <t>2026-09-11T13:49:47+00:00</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:51:06+00:00</t>
+          <t>2026-09-11T13:49:47+00:00</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:51:06+00:00</t>
+          <t>2026-09-11T13:49:47+00:00</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr"/>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>5d9f55897ec5a5849a664473999dfa88e9d4a1f06ecaa7cff531b04aecd4df12</t>
+          <t>bd8c1ce600109c2433e233319fc76d333941de2357bd66d5fc70ecb75ce763a2</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:51:06+00:00</t>
+          <t>2026-09-11T13:49:47+00:00</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:51:06+00:00</t>
+          <t>2026-09-11T13:49:47+00:00</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:51:06+00:00</t>
+          <t>2026-09-11T13:49:47+00:00</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Citadel Launch</t>
+          <t>Akuna University - Options 101 / 201</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1554,22 +1554,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Aug-Sep</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Early undergrad</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/open-opportunities/students/internships/</t>
+          <t>https://akunacapital.com/careers</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>11-week engineering internship for students early in their journey.</t>
+          <t>Self-serve options curriculum.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Trading Invitational</t>
+          <t>Citadel Launch</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1591,22 +1591,22 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~mid-Feb; event spring</t>
+          <t>Aug-Sep</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Early undergrad</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/the-trading-invitational/</t>
+          <t>https://www.citadel.com/careers/open-opportunities/students/internships/</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Same structure, market-making focus.</t>
+          <t>11-week engineering internship for students early in their journey.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Citadel Trading Invitational</t>
+          <t>Citadel Securities Trading Invitational</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/the-trading-invitational/</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/the-trading-invitational/</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Travel + hotel + meals covered (~$750 value). Simulated trading scenario.</t>
+          <t>Same structure, market-making focus.</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cubist Systematic Strategies Hackathon</t>
+          <t>Citadel Trading Invitational</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Deadline ~mid-Feb; event spring</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>https://careers.point72.com/</t>
+          <t>https://www.citadel.com/careers/programs-and-events/the-trading-invitational/</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>NYC, models built on NYC Open Data.</t>
+          <t>Travel + hotel + meals covered (~$750 value). Simulated trading scenario.</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Discover Citadel</t>
+          <t>Cubist Systematic Strategies Hackathon</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1702,22 +1702,22 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Nov/Dec-Jan</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/discover-citadel/</t>
+          <t>https://careers.point72.com/</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Invitation-only 2-day event; NY, London, Hong Kong or Singapore. Grad window Dec 2027-Jun 2029 in current cycle.</t>
+          <t>NYC, models built on NYC Open Data.</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Discover Citadel Securities</t>
+          <t>Discover Citadel</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.citadel.com/careers/programs-and-events/discover-citadel/</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Separate application from the hedge fund side. Apply to both.</t>
+          <t>Invitation-only 2-day event; NY, London, Hong Kong or Singapore. Grad window Dec 2027-Jun 2029 in current cycle.</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Flow Traders E-House Day</t>
+          <t>Discover Citadel Securities</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1776,22 +1776,22 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Nov/Dec-Jan</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://www.flowtraders.com/careers</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Virtual ETF / strategy session.</t>
+          <t>Separate application from the hedge fund side. Apply to both.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Flow Traders Trading Business Course</t>
+          <t>Flow Traders E-House Day</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1826,7 +1826,11 @@
           <t>https://www.flowtraders.com/careers</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Virtual ETF / strategy session.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1836,7 +1840,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>Flow Traders Trading Business Course</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1846,24 +1850,20 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Tutorial ~mid-Mar; rounds Apr</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>18+ and enrolled</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
-        </is>
-      </c>
+          <t>https://www.flowtraders.com/careers</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Market Prediction (Kaggle)</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1883,20 +1883,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>When live</t>
+          <t>Tutorial ~mid-Mar; rounds Apr</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>18+ and enrolled</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
+          <t>https://prosperity.imc.com/</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1906,7 +1910,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Puzzles (monthly)</t>
+          <t>Jane Street Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1916,7 +1920,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>When live</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1926,14 +1930,10 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/puzzles/</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>The free on-ramp to the ETC/Symposium invite ecosystem. Do these.</t>
-        </is>
-      </c>
+          <t>https://www.kaggle.com/competitions</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SF Puzzle City</t>
+          <t>Jane Street Puzzles (monthly)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>In-person puzzle event.</t>
+          <t>The free on-ramp to the ETC/Symposium invite ecosystem. Do these.</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>SIG First Year Discovery Day</t>
+          <t>Jane Street SF Puzzle City</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Opens ~Aug-Sep; EVENT OCT 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1st year only</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://www.janestreet.com/puzzles/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Virtual. No prior finance experience required. Confirmed date - nearest hard deadline on this list.</t>
+          <t>In-person puzzle event.</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>SIG First Year Discovery Day</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2027,22 +2027,22 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Registration opens ~Mar 17</t>
+          <t>Opens ~Aug-Sep; EVENT OCT 2026</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>18+, university students</t>
+          <t>1st year only</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>Virtual. No prior finance experience required. Confirmed date - nearest hard deadline on this list.</t>
         </is>
       </c>
     </row>
@@ -2054,32 +2054,32 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DOE SULI</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Summer cycle opens fall; deadline ~Jan</t>
+          <t>Registration opens ~Mar 17</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>NO class-year requirement</t>
+          <t>18+, university students</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://science.osti.gov/wdts/suli</t>
+          <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>TOP PICK. Any full-time undergrad, 18+, 3.0 GPA, US citizen or LPR. Name SLAC as first choice and email slacinternships@slac.stanford.edu.</t>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Math REU master list (2027)</t>
+          <t>DOE SULI</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Dec-Feb</t>
+          <t>Summer cycle opens fall; deadline ~Jan</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Varies by site</t>
+          <t>NO class-year requirement</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/mathreu</t>
+          <t>https://science.osti.gov/wdts/suli</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Spreadsheet of REUs planning to run in summer 2027.</t>
+          <t>TOP PICK. Any full-time undergrad, 18+, 3.0 GPA, US citizen or LPR. Name SLAC as first choice and email slacinternships@slac.stanford.edu.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>NASA Internships</t>
+          <t>Math REU master list (2027)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2138,22 +2138,22 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Dec-Feb</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Varies by posting</t>
+          <t>Varies by site</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://intern.nasa.gov/</t>
+          <t>https://sites.google.com/view/mathreu</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Many individual postings accept freshmen.</t>
+          <t>Spreadsheet of REUs planning to run in summer 2027.</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PCMI Undergraduate Summer School</t>
+          <t>NASA Internships</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2175,22 +2175,22 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Deadline Jan 31 (via MathPrograms.org)</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>All undergraduate levels</t>
+          <t>Varies by posting</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>https://www.ias.edu/pcmi</t>
+          <t>https://intern.nasa.gov/</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>3 weeks in residence + Experimental Math Lab. Prereqs vary by year's theme - 2026 needed group theory, 2025 only combinatorics.</t>
+          <t>Many individual postings accept freshmen.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Polymath Jr REU</t>
+          <t>PCMI Undergraduate Summer School</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Apr 1</t>
+          <t>Deadline Jan 31 (via MathPrograms.org)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad with proof-writing experience</t>
+          <t>All undergraduate levels</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>https://geometrynyc.wixsite.com/polymathreu</t>
+          <t>https://www.ias.edu/pcmi</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Online, groups of 10-25 working toward a paper. No citizenship restriction. Part-time allowed, so it stacks with something else.</t>
+          <t>3 weeks in residence + Experimental Math Lab. Prereqs vary by year's theme - 2026 needed group theory, 2025 only combinatorics.</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>Polymath Jr REU</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2249,20 +2249,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Dec-Feb</t>
+          <t>Deadline ~Apr 1</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Freshmen</t>
+          <t>Any undergrad with proof-writing experience</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
+          <t>https://geometrynyc.wixsite.com/polymathreu</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Online, groups of 10-25 working toward a paper. No citizenship restriction. Part-time allowed, so it stacks with something else.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>SLAC internships (beyond SULI)</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2282,24 +2286,20 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Dec-Feb</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Freshmen</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://careers.slac.stanford.edu/</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>e.g. the LCLS internship. A mile from campus.</t>
-        </is>
-      </c>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>UChicago Math REU - Apprentice Program</t>
+          <t>SLAC internships (beyond SULI)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Feb 6</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Freshmen &amp; sophomores</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://math.uchicago.edu/~may/REU2026/</t>
+          <t>https://careers.slac.stanford.edu/</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program.</t>
+          <t>e.g. the LCLS internship. A mile from campus.</t>
         </is>
       </c>
     </row>
@@ -2346,32 +2346,32 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Stanford CS Section Leading (106A/B)</t>
+          <t>UChicago Math REU - Apprentice Program</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Each quarter</t>
+          <t>Deadline ~Feb 6</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>After taking 106A/106B</t>
+          <t>Freshmen &amp; sophomores</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://cs198.stanford.edu/</t>
+          <t>https://math.uchicago.edu/~may/REU2026/</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Paid, prestigious, sophomores routinely hold it. Take the courses this year to qualify.</t>
+          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program.</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>Stanford CS Section Leading (106A/B)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2393,22 +2393,22 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Jan 27 - Feb 10</t>
+          <t>Each quarter</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>After taking 106A/106B</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://cs198.stanford.edu/</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay.</t>
+          <t>Paid, prestigious, sophomores routinely hold it. Take the courses this year to qualify.</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Stanford Directed Reading Program (math)</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2430,22 +2430,22 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Start of each quarter</t>
+          <t>Jan 27 - Feb 10</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad, any major</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay.</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Stanford Finance</t>
+          <t>Stanford Directed Reading Program (math)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2467,22 +2467,22 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Start of each quarter</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Any Stanford undergrad, any major</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanfordfinance.stanford.edu/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Workshop series, networking, 1:1 officer mentorship.</t>
+          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter.</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>Stanford Finance</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2504,22 +2504,22 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Feb 26</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Stanford undergrads with proof-writing coursework</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://www.stanfordfinance.stanford.edu/</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math).</t>
+          <t>Workshop series, networking, 1:1 officer mentorship.</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Stanford SymSys Summer Internships</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2541,22 +2541,22 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Priority Feb 18; opens to non-majors Mar 9</t>
+          <t>Deadline ~Feb 26</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Stanford undergrads</t>
+          <t>Stanford undergrads with proof-writing coursework</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>https://symsys.stanford.edu/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math).</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Faculty / Departmental Grants</t>
+          <t>Stanford SymSys Summer Internships</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Faculty Feb 15; Departmental Oct 31</t>
+          <t>Priority Feb 18; opens to non-majors Mar 9</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Stanford undergrads</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://symsys.stanford.edu/</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
+          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window.</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Small Grants</t>
+          <t>Stanford VPUE Faculty / Departmental Grants</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Quarterly deadlines</t>
+          <t>Faculty Feb 15; Departmental Oct 31</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Part-time, year-round. Good way to start something this winter.</t>
+          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Stanford opportunity portal (SOLO)</t>
+          <t>Stanford VPUE Small Grants</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -2652,22 +2652,22 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>Quarterly deadlines</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford student</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://solo.stanford.edu/</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Aggregates all of the above.</t>
+          <t>Part-time, year-round. Good way to start something this winter.</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Traders @ Stanford / Quant Gym</t>
+          <t>Stanford opportunity portal (SOLO)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2689,22 +2689,22 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Any Stanford student</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanfordacm.org/quantGym</t>
+          <t>https://solo.stanford.edu/</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>JOIN IN WEEK ONE. Nearly every competition on this sheet is team-based and university-affiliated; this is where teams and invites form.</t>
+          <t>Aggregates all of the above.</t>
         </is>
       </c>
     </row>
@@ -2716,32 +2716,32 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Capital One TEIP</t>
+          <t>Traders @ Stanford / Quant Gym</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Dec-Jan</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Freshman/sophomore</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/</t>
+          <t>https://www.stanfordacm.org/quantGym</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Underclassman version of TIP (which is rising-seniors only). Real SWE work, full intern comp.</t>
+          <t>JOIN IN WEEK ONE. Nearly every competition on this sheet is team-based and university-affiliated; this is where teams and invites form.</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows</t>
+          <t>Capital One TEIP</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2763,20 +2763,24 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Dec-Jan</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates</t>
+          <t>Freshman/sophomore</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/company/careers</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
+          <t>https://www.capitalonecareers.com/</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Underclassman version of TIP (which is rising-seniors only). Real SWE work, full intern comp.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2786,7 +2790,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Duolingo Thrive</t>
+          <t>Databricks Student Fellows</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2801,12 +2805,12 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Underclassmen</t>
+          <t>Undergraduates</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/</t>
+          <t>https://www.databricks.com/company/careers</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr"/>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Etched - Supercomputing Intern</t>
+          <t>Duolingo Thrive</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2829,17 +2833,17 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's-track, no class cutoff</t>
+          <t>Underclassmen</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>https://www.etched.com/</t>
+          <t>https://careers.duolingo.com/</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr"/>
@@ -2852,7 +2856,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Explore Microsoft</t>
+          <t>Etched - Supercomputing Intern</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2862,24 +2866,20 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Late summer-fall (2027 US posting not up as of Aug 2026)</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Bachelor's-track, no class cutoff</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://careers.microsoft.com/v2/global/en/exploremicrosoft</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>12 weeks; rotate through design, build and quality phases in a pod. Set a job alert - no universal date published.</t>
-        </is>
-      </c>
+          <t>https://www.etched.com/</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Google ASDI (formerly STEP)</t>
+          <t>Explore Microsoft</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Early fall</t>
+          <t>Late summer-fall (2027 US posting not up as of Aug 2026)</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/</t>
+          <t>https://careers.microsoft.com/v2/global/en/exploremicrosoft</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>RENAMED - search 'ASDI', not 'STEP'. 12 weeks, paired with a host engineer and a co-intern.</t>
+          <t>12 weeks; rotate through design, build and quality phases in a pod. Set a job alert - no universal date published.</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Google Student Researcher, BS/MS</t>
+          <t>Google ASDI (formerly STEP)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Deadline Nov 27, 2026 (rolling, may close early)</t>
+          <t>Early fall</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Any enrolled bachelor's</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>MOST UNDERRATED ITEM HERE - research role across Google Research, DeepMind and Cloud with NO class-year gate. Must be US-based.</t>
+          <t>RENAMED - search 'ASDI', not 'STEP'. 12 weeks, paired with a host engineer and a co-intern.</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Google Summer of Code</t>
+          <t>Google Student Researcher, BS/MS</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Orgs announced Feb; apps ~Mar 16-31</t>
+          <t>Deadline Nov 27, 2026 (rolling, may close early)</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>18+, limited prior OSS experience</t>
+          <t>Any enrolled bachelor's</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>https://summerofcode.withgoogle.com/</t>
+          <t>https://www.google.com/about/careers/applications/</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Design FAVOURS beginners. Pre-application contributions are the strongest predictor of selection - start contributing in January.</t>
+          <t>MOST UNDERRATED ITEM HERE - research role across Google Research, DeepMind and Cloud with NO class-year gate. Must be US-based.</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Handshake AI Fellowship</t>
+          <t>Google Summer of Code</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3010,22 +3010,22 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Orgs announced Feb; apps ~Mar 16-31</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Undergrad and above</t>
+          <t>18+, limited prior OSS experience</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://joinhandshake.com/ai/</t>
+          <t>https://summerofcode.withgoogle.com/</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>NOT an internship - 1099 AI-training gig work. Math queues pay the top tier ($17-125/hr). Volatile workflow; two lawsuits allege withheld payments. Read each project's time cap.</t>
+          <t>Design FAVOURS beginners. Pre-application contributions are the strongest predictor of selection - start contributing in January.</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Kalshi - Support Ops Intern</t>
+          <t>Handshake AI Fellowship</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>No class-year gate</t>
+          <t>Undergrad and above</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>https://kalshi.com/careers</t>
+          <t>https://joinhandshake.com/ai/</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Ops rather than SWE. $20-25/hr.</t>
+          <t>NOT an internship - 1099 AI-training gig work. Math queues pay the top tier ($17-125/hr). Volatile workflow; two lawsuits allege withheld payments. Read each project's time cap.</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn First Play</t>
+          <t>Kalshi - Support Ops Intern</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3084,20 +3084,24 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Completed 1st or 2nd year of CS</t>
+          <t>No class-year gate</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
+          <t>https://kalshi.com/careers</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Ops rather than SWE. $20-25/hr.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MLH Fellowship</t>
+          <t>LinkedIn First Play</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3117,17 +3121,17 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Rolling (fall batch closed Aug 31, 2026)</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Any student</t>
+          <t>Completed 1st or 2nd year of CS</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>https://fellowship.mlh.io/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr"/>
@@ -3140,7 +3144,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Ignite</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3150,24 +3154,20 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Aug-Sep; deadline Oct-Nov</t>
+          <t>Rolling (fall batch closed Aug 31, 2026)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Current freshmen &amp; sophomores</t>
+          <t>Any student</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>12-week 'pre-internship'. Software / Hardware / Business Ops tracks. Some NVIDIA pages say 'underrepresented communities', main US pages say 'wide range of backgrounds' - do not self-select out.</t>
-        </is>
-      </c>
+          <t>https://fellowship.mlh.io/</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Internship (software / systems)</t>
+          <t>NVIDIA Ignite</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Aug-Oct, rolling</t>
+          <t>Aug-Sep; deadline Oct-Nov</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>BS and above</t>
+          <t>Current freshmen &amp; sophomores</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Long shot but no GPA cutoff. $20-71/hr software + $1,800-2,800/mo housing. Avoid AI-research reqs (8 of 9 want MS/PhD).</t>
+          <t>12-week 'pre-internship'. Software / Hardware / Business Ops tracks. Some NVIDIA pages say 'underrepresented communities', main US pages say 'wide range of backgrounds' - do not self-select out.</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Scale AI - AI Builder Intern</t>
+          <t>NVIDIA Internship (software / systems)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3224,20 +3224,24 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Aug-Oct, rolling</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad, no class-year gate</t>
+          <t>BS and above</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://scale.com/careers</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Long shot but no GPA cutoff. $20-71/hr software + $1,800-2,800/mo housing. Avoid AI-research reqs (8 of 9 want MS/PhD).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3247,69 +3251,65 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
+          <t>Scale AI - AI Builder Intern</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Any undergrad, no class-year gate</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>https://scale.com/careers</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
           <t>UberSTAR</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Dec-Jan</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Freshman/sophomore</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>https://www.uber.com/us/en/careers/</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>Consistently positive reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Bloomberg Global Trading Challenge</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>TBA for 2026</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>Bloomberg Global Trading Challenge</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>2026 cycle</t>
+          <t>TBA for 2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
+          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
+          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>CME Group University Trading Challenge</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>2026 cycle</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>University students</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
+          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
+          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Citadel x Amplify Trading Challenge</t>
+          <t>CME Group University Trading Challenge</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3410,15 +3410,19 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>University students</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr"/>
+          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -3428,7 +3432,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Gemini Collegiate Quantitative Trading Competition</t>
+          <t>Citadel x Amplify Trading Challenge</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3438,24 +3442,20 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Check via student orgs</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Students, allocated by team</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://www.gemini.com/</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>Trades on the live Gemini exchange under competition accounts.</t>
-        </is>
-      </c>
+          <t>https://www.citadel.com/careers/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Hull Tactical Market Prediction (Kaggle)</t>
+          <t>Gemini Collegiate Quantitative Trading Competition</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>Check via student orgs</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>Students, allocated by team</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
+          <t>https://www.gemini.com/</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
+          <t>Trades on the live Gemini exchange under competition accounts.</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>IICPC Codefest 2026</t>
+          <t>Hull Tactical Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3512,22 +3512,22 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Rolling - see Kaggle</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://codefest.iicpc.com/</t>
+          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
+          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+          <t>IICPC Codefest 2026</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3549,22 +3549,22 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
+          <t>https://codefest.iicpc.com/</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
+          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Quantiacs Crypto Contest</t>
+          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -3586,22 +3586,22 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>2026 contest cycles</t>
+          <t>Rolling - see Kaggle</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://quantiacs.com/</t>
+          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
+          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>The Deck Game</t>
+          <t>Quantiacs Crypto Contest</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3623,22 +3623,22 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>2026 contest cycles</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>https://thedeckgame.com/</t>
+          <t>https://quantiacs.com/</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
+          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
         </is>
       </c>
     </row>
@@ -3650,32 +3650,32 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Code for Good</t>
+          <t>The Deck Game</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>VERIFY - historically broader across years</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://thedeckgame.com/</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
+          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Quant Invitational</t>
+          <t>JPMorgan Code for Good</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>VERIFY - historically broader across years</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Listed on their programs page; class-year requirement not published.</t>
+          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Cubist Quant Academy</t>
+          <t>Citadel Securities Quant Invitational</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3739,15 +3739,19 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://careers.point72.com/</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr"/>
+          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Listed on their programs page; class-year requirement not published.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -3757,7 +3761,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Discover DRW</t>
+          <t>Cubist Quant Academy</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3772,19 +3776,15 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED for 1st year</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>https://drw.com/work-at-drw/category/campus</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>2-day quant trading immersion. Verify class year directly.</t>
-        </is>
-      </c>
+          <t>https://careers.point72.com/</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Five Rings Winternship</t>
+          <t>Discover DRW</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://fiverings.com/careers</t>
+          <t>https://drw.com/work-at-drw/category/campus</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
+          <t>2-day quant trading immersion. Verify class year directly.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>G-Research Spring into Quant Finance 2026</t>
+          <t>Five Rings Winternship</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Students - verify</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+          <t>https://fiverings.com/careers</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
+          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Optiver Insight Days</t>
+          <t>G-Research Spring into Quant Finance 2026</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3878,20 +3878,24 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>Students - verify</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr"/>
+          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -3901,7 +3905,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Optiver Market Making Competition</t>
+          <t>Optiver Insight Days</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3934,7 +3938,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Optiver Trading Day</t>
+          <t>Optiver Market Making Competition</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3967,7 +3971,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>SIG Insight Week</t>
+          <t>Optiver Trading Day</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3987,7 +3991,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr"/>
@@ -4000,7 +4004,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Financial Modeling Challenge</t>
+          <t>SIG Insight Week</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4020,7 +4024,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/</t>
+          <t>https://careers.sig.com/</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr"/>
@@ -4028,86 +4032,82 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Financial Modeling Challenge</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED - too early</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>NISA Investment Advisors - Intern</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Fall-winter</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.nisa.com/early-careers</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>APPLIED - too early</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Edward Jones Internship</t>
+          <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Fall-winter</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
+          <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>10-week program, St. Louis or Tempe.</t>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Stifel - Institutional Group Internship</t>
+          <t>Edward Jones Internship</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>~Nov, rolling per office/desk</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.stifel.com/careers/internships</t>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
@@ -4181,32 +4181,32 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Opens ~Oct; closes mid-Nov</t>
+          <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.stifel.com/careers/internships</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging.</t>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4228,22 +4228,22 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Winter-spring</t>
+          <t>Opens ~Oct; closes mid-Nov</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Rising sophomore+</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund.</t>
+          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging.</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4265,20 +4265,24 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Winter-spring</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Rising sophomore+</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr"/>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -4288,7 +4292,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4321,7 +4325,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4354,7 +4358,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4387,7 +4391,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4410,11 +4414,7 @@
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
-        </is>
-      </c>
+      <c r="G108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4439,17 +4439,17 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
@@ -4461,69 +4461,69 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4609,12 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>CMF Select New York 2026</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
+          <t>CMF Select New York 2026</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>https://fima.partners/</t>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
+          <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+          <t>https://fima.partners/</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+          <t>FutureAlpha / QuantStrats 2026</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>https://www.qwafafew.org/</t>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Tapia Conference</t>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4804,22 +4804,22 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Open, but serves underrepresented groups in computing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
+          <t>https://www.qwafafew.org/</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>You can attend; low relative value for you.</t>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4831,69 +4831,69 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
+          <t>Tapia Conference</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Open, but serves underrepresented groups in computing</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>https://tapiaconference.cmd-it.org/</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>You can attend; low relative value for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Duke Career Hub early-insight table</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>First-year/sophomore</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>https://careerhub.students.duke.edu/</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>Public list of early insight programs by target year.</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Yale 'Gorick's List' for quant trading</t>
+          <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4920,55 +4920,92 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>First-year/sophomore</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr"/>
+          <t>https://careerhub.students.duke.edu/</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Public list of early insight programs by target year.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Yale 'Gorick's List' for quant trading</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G123"/>
+  <autoFilter ref="A1:G124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -5089,6 +5126,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8551,7 +8589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8597,7 +8635,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Already watched by akuna-academy</t>
+          <t>Already watched by akunacapital-greenhouse</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -8629,12 +8667,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Already watched by akuna-academy</t>
+          <t>Already watched by akunacapital-greenhouse</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Akuna University - Options 101 / 201</t>
+          <t>Akuna Virtual Quant Trading Challenge</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -8649,24 +8687,24 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://akunacapital.com/careers</t>
+          <t>https://akunacapital.com/careers/job/7986086/?gh_jid=7986086</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Self-serve options curriculum.</t>
+          <t>Write market-making bots against an open exchange.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Already watched by akuna-academy</t>
+          <t>Already watched by bridgewater-students</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Akuna Virtual Quant Trading Challenge</t>
+          <t>Bridgewater Investment Immersion Program</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -8674,68 +8712,68 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://akunacapital.com/careers/job/7986086/?gh_jid=7986086</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Write market-making bots against an open exchange.</t>
+          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bridgewater-students</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Investment Immersion Program</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -8745,44 +8783,44 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by hrt-student-opportunities</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Explore HRT / Inside HRT</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>3-day immersive for 1st/2nd years in CS, math or STEM.</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8832,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Explore HRT / Inside HRT</t>
+          <t>HRT Sophomore Winternship</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -8802,9 +8840,9 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -8814,56 +8852,56 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3-day immersive for 1st/2nd years in CS, math or STEM.</t>
+          <t>January, 2-4 weeks, Python/C++.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hrt-student-opportunities</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>HRT Sophomore Winternship</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>January, 2-4 weeks, Python/C++.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -8873,24 +8911,24 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -8898,31 +8936,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -8930,19 +8968,19 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8992,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -8962,19 +9000,19 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
         </is>
       </c>
     </row>
@@ -8986,7 +9024,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -8994,9 +9032,9 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>INVITE</t>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -9006,7 +9044,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9056,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -9026,9 +9064,9 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -9036,11 +9074,7 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -9050,7 +9084,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -9060,7 +9094,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -9073,27 +9107,27 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://github.com/LuisaE/opportunities</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -9101,109 +9135,113 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr"/>
+          <t>https://battlecode.org/</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -9213,24 +9251,24 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -9245,136 +9283,136 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr"/>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>You cannot apply (NO)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://www.bofa.com/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9386,12 +9424,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -9401,12 +9439,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
         </is>
       </c>
     </row>
@@ -9418,12 +9456,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -9433,12 +9471,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9450,12 +9488,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -9465,12 +9503,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -9482,12 +9520,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9497,12 +9535,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.codingitforward.com/fellowship</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
         </is>
       </c>
     </row>
@@ -9514,12 +9552,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -9529,14 +9567,10 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
-        </is>
-      </c>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -9546,7 +9580,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9574,7 +9608,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9589,10 +9623,14 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
+          <t>https://campus.deshaw.com/additional-experiences</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -9602,7 +9640,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9617,14 +9655,10 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -9634,12 +9668,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -9649,10 +9683,14 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr"/>
+          <t>https://databento.com/</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -9662,12 +9700,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -9677,12 +9715,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://en.tmtpost.com/post/7752441</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9694,12 +9732,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -9709,12 +9747,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9764,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -9741,12 +9779,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Geographic exclusion - you are US-based.</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9796,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -9773,14 +9811,10 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Geographic exclusion - you are US-based.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -9790,7 +9824,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9805,10 +9839,14 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr"/>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -9818,12 +9856,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -9833,12 +9871,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>That is a junior-year window. Not you.</t>
         </is>
       </c>
     </row>
@@ -9850,12 +9888,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -9865,12 +9903,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window. Not you.</t>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9920,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -9900,11 +9938,7 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
-        </is>
-      </c>
+      <c r="F43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -9914,7 +9948,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -9929,10 +9963,14 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>For women, transgender and gender-expansive people.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -9942,7 +9980,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -9957,12 +9995,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
         </is>
       </c>
     </row>
@@ -9974,7 +10012,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -9989,14 +10027,10 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -10006,7 +10040,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -10024,7 +10058,11 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Women / trans / gender-expansive students.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -10034,12 +10072,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -10049,12 +10087,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://kaxanuk.mx/kn-hack</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10104,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -10081,12 +10119,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
         </is>
       </c>
     </row>
@@ -10098,12 +10136,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -10111,14 +10149,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>https://pokerbots.org/</t>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
         </is>
       </c>
     </row>
@@ -10130,12 +10168,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -10143,14 +10181,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10200,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>Optiver Quantitative Intern Summer 2027</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -10177,12 +10215,12 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Highest pay in the industry, but you are too early.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10232,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>Optiver regional recruitment events (non-US)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -10209,12 +10247,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+          <t>https://optiver.com/recruitment-events/</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but you are too early.</t>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10264,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>PEAK6 Trading Bootcamp</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -10241,12 +10279,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://peak6.com/campus/</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
         </is>
       </c>
     </row>
@@ -10258,12 +10296,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>Palantir Path</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -10271,16 +10309,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>https://peak6.com/campus/</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
-        </is>
-      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -10290,12 +10324,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>Point72 Academy</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -10303,12 +10337,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -10318,7 +10356,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -10333,14 +10371,10 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -10350,7 +10384,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>Two Sigma College Mentor Connect</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -10365,10 +10399,14 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr"/>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -10378,7 +10416,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -10396,11 +10434,7 @@
           <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>6-week remote mentorship on open-source projects.</t>
-        </is>
-      </c>
+      <c r="F59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -10410,7 +10444,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Two Sigma PhD Fellowship</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -10425,7 +10459,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr"/>
@@ -10438,7 +10472,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Virtu Financial Women's Winternship</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -10453,7 +10487,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+          <t>https://www.virtu.com/careers/</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
@@ -10466,12 +10500,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Wharton Global High School Investment Competition</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -10481,10 +10515,14 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr"/>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -10494,12 +10532,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Women in Quantitative Finance Americas Conference</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -10509,12 +10547,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://www.wbstraining.com/events/wqfa</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10564,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Women in Quantitative Finance London Conference</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -10541,7 +10579,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -10553,69 +10591,37 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>You cannot apply (STALE)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>STALE</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+          <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>You cannot apply (STALE)</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>zapplyjobs underclassmen-internships</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>STALE</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/zapplyjobs/underclassmen-internships</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F66"/>
+  <autoFilter ref="A1:F65"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -10665,11 +10671,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
@@ -10679,7 +10685,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6374,7 +6374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8187,8 +8187,58 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>B - strong fit, worth the effort</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Aug-Sep 2027</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Yes - the Morgan Stanley Campus board is watched</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>A sophomore-specific summer analyst seat at a major firm, which is a narrower and less contested door than the junior programme. He is one year early for the 2027 cycle; the 2028 cycle is his first shot and it closed in late September for 2027, so the window opens earlier than most people expect.</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J36"/>
+  <autoFilter ref="A1:J37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -8224,6 +8274,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8589,7 +8640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9167,113 +9218,113 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by morganstanley-campus-p1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>Morgan Stanley Campus - Global Programs board</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by morganstanley-campus-p1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -9283,57 +9334,61 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr"/>
+          <t>https://osqf.org/</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -9343,24 +9398,20 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -9368,83 +9419,83 @@
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9507,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -9471,12 +9522,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://www.bofa.com/</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9539,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -9503,12 +9554,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
         </is>
       </c>
     </row>
@@ -9520,12 +9571,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9535,12 +9586,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9603,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9567,10 +9618,14 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Invite-only weeklong program for sophomore women.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -9580,12 +9635,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -9595,10 +9650,14 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr"/>
+          <t>https://www.codingitforward.com/fellowship</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -9608,7 +9667,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9623,14 +9682,10 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -9640,7 +9695,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9668,12 +9723,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -9683,12 +9738,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://campus.deshaw.com/additional-experiences</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9700,12 +9755,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -9715,14 +9770,10 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -9732,12 +9783,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -9747,12 +9798,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://databento.com/</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9815,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -9779,12 +9830,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://en.tmtpost.com/post/7752441</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - you are US-based.</t>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9847,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -9811,10 +9862,14 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr"/>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -9824,7 +9879,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9839,12 +9894,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Geographic exclusion - you are US-based.</t>
         </is>
       </c>
     </row>
@@ -9856,12 +9911,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -9871,14 +9926,10 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>That is a junior-year window. Not you.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -9888,7 +9939,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9903,12 +9954,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -9920,12 +9971,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -9935,10 +9986,14 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
+          <t>https://careers.jpmorgan.com/</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>That is a junior-year window. Not you.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -9948,7 +10003,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -9963,12 +10018,12 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
         </is>
       </c>
     </row>
@@ -9980,7 +10035,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -9995,14 +10050,10 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -10012,7 +10063,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10027,10 +10078,14 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>For women, transgender and gender-expansive people.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -10040,7 +10095,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -10055,12 +10110,12 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10127,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -10087,14 +10142,10 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -10104,12 +10155,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -10119,12 +10170,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Women / trans / gender-expansive students.</t>
         </is>
       </c>
     </row>
@@ -10136,12 +10187,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -10149,14 +10200,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>https://kaxanuk.mx/kn-hack</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10219,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -10183,12 +10234,12 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
         </is>
       </c>
     </row>
@@ -10200,12 +10251,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -10213,14 +10264,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but you are too early.</t>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10283,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -10247,12 +10298,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10315,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>Optiver Quantitative Intern Summer 2027</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -10279,12 +10330,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>Highest pay in the industry, but you are too early.</t>
         </is>
       </c>
     </row>
@@ -10296,12 +10347,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>Optiver regional recruitment events (non-US)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -10309,12 +10360,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -10324,7 +10379,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>PEAK6 Trading Bootcamp</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -10339,12 +10394,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
+          <t>https://peak6.com/campus/</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10411,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>Palantir Path</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -10369,9 +10424,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr"/>
@@ -10384,7 +10439,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Point72 Academy</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -10399,12 +10454,12 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://point72.com/point72-academy/</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>6-week remote mentorship on open-source projects.</t>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10471,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -10431,7 +10486,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr"/>
@@ -10444,7 +10499,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Two Sigma College Mentor Connect</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -10459,10 +10514,14 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr"/>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -10472,7 +10531,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -10487,7 +10546,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
@@ -10500,12 +10559,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Two Sigma PhD Fellowship</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -10515,14 +10574,10 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -10532,12 +10587,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Virtu Financial Women's Winternship</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -10547,14 +10602,10 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -10564,12 +10615,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>Wharton Global High School Investment Competition</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -10579,49 +10630,113 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F65"/>
+  <autoFilter ref="A1:F67"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -10671,12 +10786,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
@@ -10685,6 +10800,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Optiver Insight Days</t>
+          <t>Morgan Stanley Campus - Global Programs board</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3915,20 +3915,24 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>1st-4th year, varies by programme</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -3938,7 +3942,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Optiver Market Making Competition</t>
+          <t>Optiver Insight Days</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3971,7 +3975,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Optiver Trading Day</t>
+          <t>Optiver Market Making Competition</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -4004,7 +4008,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>SIG Insight Week</t>
+          <t>Optiver Trading Day</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4024,7 +4028,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr"/>
@@ -4037,7 +4041,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Financial Modeling Challenge</t>
+          <t>SIG Insight Week</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/</t>
+          <t>https://careers.sig.com/</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr"/>
@@ -4065,86 +4069,82 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Financial Modeling Challenge</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED - too early</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>NISA Investment Advisors - Intern</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Fall-winter</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.nisa.com/early-careers</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>APPLIED - too early</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Edward Jones Internship</t>
+          <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Fall-winter</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
+          <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>10-week program, St. Louis or Tempe.</t>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Stifel - Institutional Group Internship</t>
+          <t>Edward Jones Internship</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>~Nov, rolling per office/desk</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>https://www.stifel.com/careers/internships</t>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
@@ -4218,32 +4218,32 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Opens ~Oct; closes mid-Nov</t>
+          <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.stifel.com/careers/internships</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging.</t>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4265,22 +4265,22 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Winter-spring</t>
+          <t>Opens ~Oct; closes mid-Nov</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Rising sophomore+</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund.</t>
+          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging.</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4302,20 +4302,24 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Winter-spring</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Rising sophomore+</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr"/>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -4325,7 +4329,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4335,20 +4339,24 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -4358,7 +4366,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4391,7 +4399,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4424,7 +4432,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4447,11 +4455,7 @@
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
-        </is>
-      </c>
+      <c r="G109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4476,19 +4480,15 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -4498,106 +4498,106 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>CMF Select New York 2026</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>https://fima.partners/</t>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
+          <t>CMF Select New York 2026</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+          <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>https://www.qwafafew.org/</t>
+          <t>https://fima.partners/</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Tapia Conference</t>
+          <t>FutureAlpha / QuantStrats 2026</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4841,22 +4841,22 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Open, but serves underrepresented groups in computing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>You can attend; low relative value for you.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4868,144 +4868,218 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qwafafew.org/</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Tapia Conference</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Open, but serves underrepresented groups in computing</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>https://tapiaconference.cmd-it.org/</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>You can attend; low relative value for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
         </is>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Duke Career Hub early-insight table</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>First-year/sophomore</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>https://careerhub.students.duke.edu/</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>Public list of early insight programs by target year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Yale 'Gorick's List' for quant trading</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Duke Career Hub early-insight table</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>First-year/sophomore</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>https://careerhub.students.duke.edu/</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Public list of early insight programs by target year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Yale 'Gorick's List' for quant trading</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G124"/>
+  <autoFilter ref="A1:G126"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -5127,6 +5201,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8223,7 +8299,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Yes - the Morgan Stanley Campus board is watched</t>
+          <t>No - the campus board was dropped 2026-09-21; check it by hand</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -8640,7 +8716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9218,113 +9294,113 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by morganstanley-campus-p1</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Campus - Global Programs board</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by morganstanley-campus-p1</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -9334,61 +9410,57 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -9398,20 +9470,24 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr"/>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -9419,83 +9495,83 @@
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>You cannot apply (NO)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://www.bofa.com/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>You cannot apply (NO)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9583,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -9522,12 +9598,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9615,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -9554,12 +9630,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9647,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9586,12 +9662,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://www.codingitforward.com/fellowship</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9679,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9618,14 +9694,10 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
-        </is>
-      </c>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -9635,12 +9707,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -9650,14 +9722,10 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
-        </is>
-      </c>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -9667,7 +9735,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9682,10 +9750,14 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
+          <t>https://campus.deshaw.com/additional-experiences</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -9695,7 +9767,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9723,12 +9795,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -9738,12 +9810,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
+          <t>https://databento.com/</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9827,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -9770,10 +9842,14 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr"/>
+          <t>https://en.tmtpost.com/post/7752441</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -9783,12 +9859,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -9798,12 +9874,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9891,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -9830,12 +9906,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Geographic exclusion - you are US-based.</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9923,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -9862,14 +9938,10 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -9879,7 +9951,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9894,12 +9966,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - you are US-based.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -9911,12 +9983,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -9926,10 +9998,14 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr"/>
+          <t>https://careers.jpmorgan.com/</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>That is a junior-year window. Not you.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -9939,7 +10015,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9954,12 +10030,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
         </is>
       </c>
     </row>
@@ -9971,12 +10047,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -9986,14 +10062,10 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>That is a junior-year window. Not you.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -10003,7 +10075,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10018,12 +10090,12 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>For women, transgender and gender-expansive people.</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10107,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -10050,10 +10122,14 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -10063,7 +10139,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10078,14 +10154,10 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>For women, transgender and gender-expansive people.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -10095,7 +10167,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -10110,12 +10182,12 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
+          <t>Women / trans / gender-expansive students.</t>
         </is>
       </c>
     </row>
@@ -10127,12 +10199,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -10142,10 +10214,14 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr"/>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -10155,12 +10231,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -10170,12 +10246,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10263,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -10200,14 +10276,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
         </is>
       </c>
     </row>
@@ -10219,12 +10295,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -10234,12 +10310,12 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -10251,12 +10327,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>Optiver Quantitative Intern Summer 2027</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -10264,14 +10340,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Highest pay in the industry, but you are too early.</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10359,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>Optiver regional recruitment events (non-US)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -10298,12 +10374,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://optiver.com/recruitment-events/</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10391,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>PEAK6 Trading Bootcamp</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -10330,12 +10406,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+          <t>https://peak6.com/campus/</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but you are too early.</t>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
         </is>
       </c>
     </row>
@@ -10347,12 +10423,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Palantir Path</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -10360,16 +10436,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>https://optiver.com/recruitment-events/</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -10379,7 +10451,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>Point72 Academy</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -10394,12 +10466,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://point72.com/point72-academy/</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10483,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -10424,9 +10496,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr"/>
@@ -10439,7 +10511,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>Two Sigma College Mentor Connect</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -10454,12 +10526,12 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+          <t>6-week remote mentorship on open-source projects.</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10543,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -10486,7 +10558,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr"/>
@@ -10499,7 +10571,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Two Sigma PhD Fellowship</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -10514,14 +10586,10 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>6-week remote mentorship on open-source projects.</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -10531,7 +10599,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Virtu Financial Women's Winternship</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -10546,7 +10614,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://www.virtu.com/careers/</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
@@ -10559,12 +10627,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Wharton Global High School Investment Competition</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -10574,10 +10642,14 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr"/>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -10587,12 +10659,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Women in Quantitative Finance Americas Conference</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -10602,10 +10674,14 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr"/>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -10615,12 +10691,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Women in Quantitative Finance London Conference</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -10630,113 +10706,49 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>You cannot apply (STALE)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>STALE</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
+          <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>You cannot apply (NO)</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Women in Quantitative Finance London Conference</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>You cannot apply (STALE)</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>zapplyjobs underclassmen-internships</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>STALE</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/zapplyjobs/underclassmen-internships</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F67"/>
+  <autoFilter ref="A1:F65"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -10786,12 +10798,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
@@ -10800,8 +10812,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$126</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Berkeley Trading Competition</t>
+          <t>Citadel + Correlation One Summer Invitational</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -583,22 +583,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Winter; event late Feb</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Undergrad + grad</t>
+          <t>Any undergrad</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
+          <t>https://www.citadel.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list.</t>
+          <t>Another name for the Datathon - do NOT double-apply.</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Citadel + Correlation One Summer Invitational</t>
+          <t>Citadel Datathon / Data Open</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Regional then global finals</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Another name for the Datathon - do NOT double-apply.</t>
+          <t>Compete to earn an interview. No class-year gate.</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Citadel Datathon / Data Open</t>
+          <t>Citadel Securities Terminal / Terminal AI</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Regional then global finals</t>
+          <t>Regional rounds</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Compete to earn an interview. No class-year gate.</t>
+          <t>Tower-defense algorithm competition. Winners earn access to exclusive job opportunities.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Terminal / Terminal AI</t>
+          <t>Georgetown Quant Club Trading Competition</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -694,22 +694,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Regional rounds</t>
+          <t>Winter; event ~Mar</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.georgetownquants.com/competition</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Tower-defense algorithm competition. Winners earn access to exclusive job opportunities.</t>
+          <t>Newer and less saturated - inaugural event was Mar 2026.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>Kaggle - Optiver / Jane Street sponsored</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>EARLY FALL 2026 - imminent</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad or masters</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://www.kaggle.com/competitions</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>Legitimate substitute if ETC never materialises. Reads as an ML-research credential.</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>Kaggle Competitions (all active)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling - always something open</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Students worldwide</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://www.kaggle.com/competitions</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment.</t>
+          <t>Open entry, no class-year or identity gate, free. A public leaderboard placing is portable evidence for quant and ML applications. The listing page is a JS shell (39 characters of text), so polling needs the official Kaggle API with free credentials - see source kaggle-competitions.</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Georgetown Quant Club Trading Competition</t>
+          <t>Kalshi Trading Competition</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Winter; event ~Mar</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>https://www.georgetownquants.com/competition</t>
+          <t>https://kalshi.com/</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Newer and less saturated - inaugural event was Mar 2026.</t>
+          <t>Event contracts; has offered $5,000 in credits plus a potential internship.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>Putnam Competition</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -842,20 +842,24 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Register Sep-Oct; exam early Dec</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Any undergraduate</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>https://maa.org/putnam</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Highest-signal single line you can add to a quant resume in year one. A high placement reportedly overrides GPA and non-target background. | Checked 2026-09-26: maa.org returns 403 to this client, so it cannot be watched; registration goes through Stanford's local supervisor, typically opening in September and closing before the early-December exam.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -865,7 +869,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Kaggle - Optiver / Jane Street sponsored</t>
+          <t>QuantConnect Quant League</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -875,22 +879,22 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>EVERY CALENDAR QUARTER</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions</t>
+          <t>https://www.quantconnect.com/league/</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Legitimate substitute if ETC never materialises. Reads as an ML-research credential.</t>
+          <t>Continuously open - the only always-available one here.</t>
         </is>
       </c>
     </row>
@@ -902,7 +906,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Kaggle Competitions (all active)</t>
+          <t>Thinkorswim Challenge</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -912,24 +916,20 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Rolling - always something open</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Open entry, no class-year or identity gate, free. A public leaderboard placing is portable evidence for quant and ML applications. The listing page is a JS shell (39 characters of text), so polling needs the official Kaggle API with free credentials - see source kaggle-competitions.</t>
-        </is>
-      </c>
+          <t>https://www.schwab.com/</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kalshi Trading Competition</t>
+          <t>4th Quantitative Finance Conference USA (NYC)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -954,19 +954,15 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>https://kalshi.com/</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Event contracts; has offered $5,000 in credits plus a potential internship.</t>
-        </is>
-      </c>
+          <t>Open registration</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Check organiser site</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -976,34 +972,30 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Putnam Competition</t>
+          <t>Columbia Future of Portfolio Management Conference</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Register Sep-Oct; exam early Dec</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Any undergraduate</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>https://maa.org/putnam</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Highest-signal single line you can add to a quant resume in year one. A high placement reportedly overrides GPA and non-target background.</t>
-        </is>
-      </c>
+          <t>https://www.columbia.edu/</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1013,32 +1005,32 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>QuantConnect Quant League</t>
+          <t>JPM Quantitative Research Virtual Experience (Forage)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>EVERY CALENDAR QUARTER</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>https://www.quantconnect.com/league/</t>
+          <t>https://www.theforage.com/</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Continuously open - the only always-available one here.</t>
+          <t>Free, self-paced, no gate. Low signal but zero cost.</t>
         </is>
       </c>
     </row>
@@ -1050,17 +1042,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Thinkorswim Challenge</t>
+          <t>Princeton Quant Trading Conference</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall (at IIT) and spring (at Princeton)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1070,10 +1062,14 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>https://www.schwab.com/</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>https://www.princeton.edu/</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Networking value, low signal value. Pick at most one conference.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1083,34 +1079,30 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Traders@MIT Trading Competition</t>
+          <t>Quaint Quant Conference (UT Dallas)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Winter/spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Any university</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>https://traders.mit.edu/competition</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to you.</t>
-        </is>
-      </c>
+          <t>https://www.utdallas.edu/</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1120,34 +1112,30 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>UChicago Trading Competition</t>
+          <t>QuantVision (Fordham)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>NOVEMBER 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Open registration</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>https://tradingcompetition.uchicago.edu/</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
-        </is>
-      </c>
+          <t>https://www.fordham.edu/</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1157,12 +1145,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Yale Undergraduate Trading Competition</t>
+          <t>Urban Initiative Traders Poker Tournament</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1172,19 +1160,15 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Undergrad + grad</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.yale.edu/</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>$10,000+ in prizes, nationwide.</t>
-        </is>
-      </c>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Check organiser site</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1194,30 +1178,34 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>4th Quantitative Finance Conference USA (NYC)</t>
+          <t>Regional firms to cold-email</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Sep and Jan</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Open registration</t>
+          <t>No structured freshman programs</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Check organiser site</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Kennedy Capital, Argent Capital, Confluence, Moneta, Advantage Capital, Guggenheim STL, RGA; tech: Mastercard O'Fallon, Boeing Defense, WWT. Email a PM or quant research lead directly - no portal.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1227,30 +1215,34 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Columbia Future of Portfolio Management Conference</t>
+          <t>AQR Early Engagement Day</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>https://www.columbia.edu/</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
+          <t>https://careers.aqr.com/jobs/department/university-jobs</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Explicitly first and second year. Inside track to the summer internship. NOT in the NUFT repo - easy to miss.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1260,12 +1252,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>JPM Quantitative Research Virtual Experience (Forage)</t>
+          <t>AQR Quanta Academy</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1280,12 +1272,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theforage.com/</t>
+          <t>https://www.aqr.com/Insights/Quanta-Academy</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Free, self-paced, no gate. Low signal but zero cost.</t>
+          <t>Self-serve educational resource, not an application. | Checked 2026-09-26: now redirects to aqr.com/404. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -1297,32 +1289,32 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Princeton Quant Trading Conference</t>
+          <t>Akuna University - Options 101 / 201</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Fall (at IIT) and spring (at Princeton)</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>https://www.princeton.edu/</t>
+          <t>https://akunacapital.com/careers</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Networking value, low signal value. Pick at most one conference.</t>
+          <t>Self-serve options curriculum.</t>
         </is>
       </c>
     </row>
@@ -1334,30 +1326,34 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Quaint Quant Conference (UT Dallas)</t>
+          <t>Citadel Launch</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Aug-Sep</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Early undergrad</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>https://www.utdallas.edu/</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+          <t>https://www.citadel.com/careers/open-opportunities/students/internships/</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>11-week engineering internship for students early in their journey.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1367,30 +1363,34 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>QuantVision (Fordham)</t>
+          <t>Citadel Securities Trading Invitational</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Deadline ~mid-Feb; event spring</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Open registration</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>https://www.fordham.edu/</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/the-trading-invitational/</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Same structure, market-making focus.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1400,30 +1400,34 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Urban Initiative Traders Poker Tournament</t>
+          <t>Citadel Trading Invitational</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Deadline ~mid-Feb; event spring</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Check organiser site</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+          <t>1st &amp; 2nd year</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.citadel.com/careers/programs-and-events/the-trading-invitational/</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Travel + hotel + meals covered (~$750 value). Simulated trading scenario.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1433,32 +1437,32 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Regional firms to cold-email</t>
+          <t>Cubist Systematic Strategies Hackathon</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Local (St. Louis)</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Sep and Jan</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>No structured freshman programs</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.point72.com/</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Capital, Argent Capital, Confluence, Moneta, Advantage Capital, Guggenheim STL, RGA; tech: Mastercard O'Fallon, Boeing Defense, WWT. Email a PM or quant research lead directly - no portal.</t>
+          <t>NYC, models built on NYC Open Data.</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1474,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>AQR Early Engagement Day</t>
+          <t>Discover Citadel</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1480,7 +1484,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Nov/Dec-Jan</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1490,12 +1494,12 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>https://careers.aqr.com/jobs/department/university-jobs</t>
+          <t>https://www.citadel.com/careers/programs-and-events/discover-citadel/</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Explicitly first and second year. Inside track to the summer internship. NOT in the NUFT repo - easy to miss.</t>
+          <t>Invitation-only 2-day event; NY, London, Hong Kong or Singapore. Grad window Dec 2027-Jun 2029 in current cycle.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>AQR Quanta Academy</t>
+          <t>Discover Citadel Securities</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1517,22 +1521,22 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>Nov/Dec-Jan</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>https://www.aqr.com/Insights/Quanta-Academy</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Self-serve educational resource, not an application.</t>
+          <t>Separate application from the hedge fund side. Apply to both.</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1548,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Akuna University - Options 101 / 201</t>
+          <t>Flow Traders E-House Day</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1554,22 +1558,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>https://akunacapital.com/careers</t>
+          <t>https://www.flowtraders.com/careers</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Self-serve options curriculum.</t>
+          <t>Virtual ETF / strategy session.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1585,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Citadel Launch</t>
+          <t>Flow Traders Trading Business Course</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1591,24 +1595,20 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Aug-Sep</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Early undergrad</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/open-opportunities/students/internships/</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>11-week engineering internship for students early in their journey.</t>
-        </is>
-      </c>
+          <t>https://www.flowtraders.com/careers</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Trading Invitational</t>
+          <t>Jane Street Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1628,24 +1628,20 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~mid-Feb; event spring</t>
+          <t>When live</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/the-trading-invitational/</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Same structure, market-making focus.</t>
-        </is>
-      </c>
+          <t>https://www.kaggle.com/competitions</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1655,7 +1651,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Citadel Trading Invitational</t>
+          <t>Jane Street Puzzles (monthly)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1665,22 +1661,22 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~mid-Feb; event spring</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/the-trading-invitational/</t>
+          <t>https://www.janestreet.com/puzzles/</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Travel + hotel + meals covered (~$750 value). Simulated trading scenario.</t>
+          <t>The free on-ramp to the ETC/Symposium invite ecosystem. Do these.</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1688,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Cubist Systematic Strategies Hackathon</t>
+          <t>Jane Street SF Puzzle City</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1707,17 +1703,17 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>https://careers.point72.com/</t>
+          <t>https://www.janestreet.com/puzzles/</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>NYC, models built on NYC Open Data.</t>
+          <t>In-person puzzle event.</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1725,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Discover Citadel</t>
+          <t>SIG First Year Discovery Day</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1739,22 +1735,22 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Nov/Dec-Jan</t>
+          <t>Opens ~Aug-Sep; EVENT OCT 2026</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>1st year only</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/discover-citadel/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Invitation-only 2-day event; NY, London, Hong Kong or Singapore. Grad window Dec 2027-Jun 2029 in current cycle.</t>
+          <t>Virtual. No prior finance experience required. Confirmed date - nearest hard deadline on this list.</t>
         </is>
       </c>
     </row>
@@ -1766,32 +1762,32 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Discover Citadel Securities</t>
+          <t>DOE SULI</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Nov/Dec-Jan</t>
+          <t>Summer cycle opens fall; deadline ~Jan</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>NO class-year requirement</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://science.osti.gov/wdts/suli</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Separate application from the hedge fund side. Apply to both.</t>
+          <t>TOP PICK. Any full-time undergrad, 18+, 3.0 GPA, US citizen or LPR. Name SLAC as first choice and email slacinternships@slac.stanford.edu.</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1799,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Flow Traders E-House Day</t>
+          <t>Math REU master list (2027)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Dec-Feb</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Varies by site</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>https://www.flowtraders.com/careers</t>
+          <t>https://sites.google.com/view/mathreu</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Virtual ETF / strategy session.</t>
+          <t>Spreadsheet of REUs planning to run in summer 2027. | Checked 2026-09-26: the data lives in a Google Sheet (docs.google.com/spreadsheets/d/1U-27BeHMSJCWumbNByal2tHyYo9wRVud9WoRE70E47Y), which holds 1 row (350 chars) - below the 500-char content floor, so it is not watched yet. MathPrograms.org is watched instead.</t>
         </is>
       </c>
     </row>
@@ -1840,30 +1836,34 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Flow Traders Trading Business Course</t>
+          <t>NASA Internships</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Varies by posting</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>https://www.flowtraders.com/careers</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
+          <t>https://intern.nasa.gov/</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Many individual postings accept freshmen.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1873,32 +1873,32 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>PCMI Undergraduate Summer School</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Tutorial ~mid-Mar; rounds Apr</t>
+          <t>Deadline Jan 31 (via MathPrograms.org)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>18+ and enrolled</t>
+          <t>All undergraduate levels</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://www.ias.edu/pcmi</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>3 weeks in residence + Experimental Math Lab. Prereqs vary by year's theme - 2026 needed group theory, 2025 only combinatorics.</t>
         </is>
       </c>
     </row>
@@ -1910,30 +1910,34 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Market Prediction (Kaggle)</t>
+          <t>Polymath Jr REU</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>When live</t>
+          <t>Deadline ~Apr 1</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>Any undergrad with proof-writing experience</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+          <t>https://geometrynyc.wixsite.com/polymathreu</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Online, groups of 10-25 working toward a paper. No citizenship restriction. Part-time allowed, so it stacks with something else.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1943,32 +1947,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Puzzles (monthly)</t>
+          <t>SLAC internships (beyond SULI)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/puzzles/</t>
+          <t>https://careers.slac.stanford.edu/</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>The free on-ramp to the ETC/Symposium invite ecosystem. Do these.</t>
+          <t>e.g. the LCLS internship. A mile from campus.</t>
         </is>
       </c>
     </row>
@@ -1980,32 +1984,32 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SF Puzzle City</t>
+          <t>UChicago Math REU - Apprentice Program</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Deadline ~Feb 6</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Freshmen &amp; sophomores</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/puzzles/</t>
+          <t>https://math.uchicago.edu/~may/REU2026/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>In-person puzzle event.</t>
+          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
         </is>
       </c>
     </row>
@@ -2017,32 +2021,32 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>SIG First Year Discovery Day</t>
+          <t>Stanford CS Section Leading (106A/B)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Opens ~Aug-Sep; EVENT OCT 2026</t>
+          <t>Each quarter</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1st year only</t>
+          <t>After taking 106A/106B</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://cs198.stanford.edu/</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Virtual. No prior finance experience required. Confirmed date - nearest hard deadline on this list.</t>
+          <t>Paid, prestigious, sophomores routinely hold it. Take the courses this year to qualify.</t>
         </is>
       </c>
     </row>
@@ -2054,32 +2058,32 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>Stanford Directed Reading Program (math)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Registration opens ~Mar 17</t>
+          <t>Start of each quarter</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>18+, university students</t>
+          <t>Any Stanford undergrad, any major</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter.</t>
         </is>
       </c>
     </row>
@@ -2091,32 +2095,32 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>DOE SULI</t>
+          <t>Stanford Finance</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Summer cycle opens fall; deadline ~Jan</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>NO class-year requirement</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>https://science.osti.gov/wdts/suli</t>
+          <t>https://www.stanfordfinance.stanford.edu/</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>TOP PICK. Any full-time undergrad, 18+, 3.0 GPA, US citizen or LPR. Name SLAC as first choice and email slacinternships@slac.stanford.edu.</t>
+          <t>Workshop series, networking, 1:1 officer mentorship.</t>
         </is>
       </c>
     </row>
@@ -2128,32 +2132,32 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Math REU master list (2027)</t>
+          <t>Stanford SymSys Summer Internships</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Dec-Feb</t>
+          <t>Priority Feb 18; opens to non-majors Mar 9</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Varies by site</t>
+          <t>Stanford undergrads</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/mathreu</t>
+          <t>https://symsys.stanford.edu/</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Spreadsheet of REUs planning to run in summer 2027.</t>
+          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window.</t>
         </is>
       </c>
     </row>
@@ -2165,32 +2169,32 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>NASA Internships</t>
+          <t>Stanford VPUE Faculty / Departmental Grants</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Faculty Feb 15; Departmental Oct 31</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Varies by posting</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>https://intern.nasa.gov/</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Many individual postings accept freshmen.</t>
+          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2206,32 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PCMI Undergraduate Summer School</t>
+          <t>Stanford VPUE Small Grants</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Deadline Jan 31 (via MathPrograms.org)</t>
+          <t>Quarterly deadlines</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>All undergraduate levels</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>https://www.ias.edu/pcmi</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>3 weeks in residence + Experimental Math Lab. Prereqs vary by year's theme - 2026 needed group theory, 2025 only combinatorics.</t>
+          <t>Part-time, year-round. Good way to start something this winter.</t>
         </is>
       </c>
     </row>
@@ -2239,32 +2243,32 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Polymath Jr REU</t>
+          <t>Stanford opportunity portal (SOLO)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Apr 1</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad with proof-writing experience</t>
+          <t>Any Stanford student</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>https://geometrynyc.wixsite.com/polymathreu</t>
+          <t>https://solo.stanford.edu/</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Online, groups of 10-25 working toward a paper. No citizenship restriction. Part-time allowed, so it stacks with something else.</t>
+          <t>Aggregates all of the above.</t>
         </is>
       </c>
     </row>
@@ -2276,30 +2280,34 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>Traders @ Stanford / Quant Gym</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Dec-Feb</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Freshmen</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
+          <t>https://www.stanfordacm.org/quantGym</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>JOIN IN WEEK ONE. Nearly every competition on this sheet is team-based and university-affiliated; this is where teams and invites form.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2309,32 +2317,32 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>SLAC internships (beyond SULI)</t>
+          <t>Capital One TEIP</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Dec-Jan</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Freshman/sophomore</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://careers.slac.stanford.edu/</t>
+          <t>https://www.capitalonecareers.com/</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>e.g. the LCLS internship. A mile from campus.</t>
+          <t>Underclassman version of TIP (which is rising-seniors only). Real SWE work, full intern comp.</t>
         </is>
       </c>
     </row>
@@ -2346,34 +2354,30 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>UChicago Math REU - Apprentice Program</t>
+          <t>Databricks Student Fellows</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Feb 6</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Freshmen &amp; sophomores</t>
+          <t>Undergraduates</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://math.uchicago.edu/~may/REU2026/</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program.</t>
-        </is>
-      </c>
+          <t>https://www.databricks.com/company/careers</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2383,34 +2387,30 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Stanford CS Section Leading (106A/B)</t>
+          <t>Duolingo Thrive</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Each quarter</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>After taking 106A/106B</t>
+          <t>Underclassmen</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://cs198.stanford.edu/</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Paid, prestigious, sophomores routinely hold it. Take the courses this year to qualify.</t>
-        </is>
-      </c>
+          <t>https://careers.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2420,34 +2420,30 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>Etched - Supercomputing Intern</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Jan 27 - Feb 10</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Bachelor's-track, no class cutoff</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay.</t>
-        </is>
-      </c>
+          <t>https://www.etched.com/</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2457,32 +2453,32 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Stanford Directed Reading Program (math)</t>
+          <t>Explore Microsoft</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Start of each quarter</t>
+          <t>Late summer-fall (2027 US posting not up as of Aug 2026)</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad, any major</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://careers.microsoft.com/v2/global/en/exploremicrosoft</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter.</t>
+          <t>12 weeks; rotate through design, build and quality phases in a pod. Set a job alert - no universal date published.</t>
         </is>
       </c>
     </row>
@@ -2494,32 +2490,32 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Stanford Finance</t>
+          <t>Google ASDI (formerly STEP)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Early fall</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanfordfinance.stanford.edu/</t>
+          <t>https://www.google.com/about/careers/applications/</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Workshop series, networking, 1:1 officer mentorship.</t>
+          <t>RENAMED - search 'ASDI', not 'STEP'. 12 weeks, paired with a host engineer and a co-intern.</t>
         </is>
       </c>
     </row>
@@ -2531,32 +2527,32 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>Google Student Researcher, BS/MS</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Feb 26</t>
+          <t>Deadline Nov 27, 2026 (rolling, may close early)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Stanford undergrads with proof-writing coursework</t>
+          <t>Any enrolled bachelor's</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://www.google.com/about/careers/applications/</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math).</t>
+          <t>MOST UNDERRATED ITEM HERE - research role across Google Research, DeepMind and Cloud with NO class-year gate. Must be US-based.</t>
         </is>
       </c>
     </row>
@@ -2568,32 +2564,32 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Stanford SymSys Summer Internships</t>
+          <t>Google Summer of Code</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Priority Feb 18; opens to non-majors Mar 9</t>
+          <t>Orgs announced Feb; apps ~Mar 16-31</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Stanford undergrads</t>
+          <t>18+, limited prior OSS experience</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://symsys.stanford.edu/</t>
+          <t>https://summerofcode.withgoogle.com/</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window.</t>
+          <t>Design FAVOURS beginners. Pre-application contributions are the strongest predictor of selection - start contributing in January.</t>
         </is>
       </c>
     </row>
@@ -2605,32 +2601,32 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Faculty / Departmental Grants</t>
+          <t>Handshake AI Fellowship</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Faculty Feb 15; Departmental Oct 31</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Undergrad and above</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://joinhandshake.com/ai/</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
+          <t>NOT an internship - 1099 AI-training gig work. Math queues pay the top tier ($17-125/hr). Volatile workflow; two lawsuits allege withheld payments. Read each project's time cap.</t>
         </is>
       </c>
     </row>
@@ -2642,32 +2638,32 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Small Grants</t>
+          <t>Kalshi - Support Ops Intern</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Quarterly deadlines</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>No class-year gate</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://kalshi.com/careers</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Part-time, year-round. Good way to start something this winter.</t>
+          <t>Ops rather than SWE. $20-25/hr.</t>
         </is>
       </c>
     </row>
@@ -2679,34 +2675,30 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Stanford opportunity portal (SOLO)</t>
+          <t>LinkedIn First Play</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford student</t>
+          <t>Completed 1st or 2nd year of CS</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>https://solo.stanford.edu/</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>Aggregates all of the above.</t>
-        </is>
-      </c>
+          <t>https://careers.linkedin.com/</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2716,34 +2708,30 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Traders @ Stanford / Quant Gym</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Rolling (fall batch closed Aug 31, 2026)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Any student</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanfordacm.org/quantGym</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>JOIN IN WEEK ONE. Nearly every competition on this sheet is team-based and university-affiliated; this is where teams and invites form.</t>
-        </is>
-      </c>
+          <t>https://fellowship.mlh.io/</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2753,7 +2741,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Capital One TEIP</t>
+          <t>NVIDIA Ignite</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2763,22 +2751,22 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Dec-Jan</t>
+          <t>Aug-Sep; deadline Oct-Nov</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Freshman/sophomore</t>
+          <t>Current freshmen &amp; sophomores</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/</t>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Underclassman version of TIP (which is rising-seniors only). Real SWE work, full intern comp.</t>
+          <t>12-week 'pre-internship'. Software / Hardware / Business Ops tracks. Some NVIDIA pages say 'underrepresented communities', main US pages say 'wide range of backgrounds' - do not self-select out.</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2778,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows</t>
+          <t>NVIDIA Internship (software / systems)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2800,20 +2788,24 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Aug-Oct, rolling</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates</t>
+          <t>BS and above</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/company/careers</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Long shot but no GPA cutoff. $20-71/hr software + $1,800-2,800/mo housing. Avoid AI-research reqs (8 of 9 want MS/PhD).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2823,7 +2815,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Duolingo Thrive</t>
+          <t>Scale AI - AI Builder Intern</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2833,17 +2825,17 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Underclassmen</t>
+          <t>Any undergrad, no class-year gate</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/</t>
+          <t>https://scale.com/careers</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr"/>
@@ -2856,7 +2848,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Etched - Supercomputing Intern</t>
+          <t>UberSTAR</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2866,450 +2858,462 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Dec-Jan</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's-track, no class cutoff</t>
+          <t>Freshman/sophomore</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://www.etched.com/</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
+          <t>https://www.uber.com/us/en/careers/</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Consistently positive reviews.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Explore Microsoft</t>
+          <t>Bloomberg Global Trading Challenge</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Late summer-fall (2027 US posting not up as of Aug 2026)</t>
+          <t>TBA for 2026</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>https://careers.microsoft.com/v2/global/en/exploremicrosoft</t>
+          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>12 weeks; rotate through design, build and quality phases in a pod. Set a job alert - no universal date published.</t>
+          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Google ASDI (formerly STEP)</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Early fall</t>
+          <t>2026 cycle</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/</t>
+          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>RENAMED - search 'ASDI', not 'STEP'. 12 weeks, paired with a host engineer and a co-intern.</t>
+          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Google Student Researcher, BS/MS</t>
+          <t>CME Group University Trading Challenge</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Deadline Nov 27, 2026 (rolling, may close early)</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Any enrolled bachelor's</t>
+          <t>University students</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/</t>
+          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>MOST UNDERRATED ITEM HERE - research role across Google Research, DeepMind and Cloud with NO class-year gate. Must be US-based.</t>
+          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Google Summer of Code</t>
+          <t>Citadel x Amplify Trading Challenge</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Orgs announced Feb; apps ~Mar 16-31</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>18+, limited prior OSS experience</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://summerofcode.withgoogle.com/</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>Design FAVOURS beginners. Pre-application contributions are the strongest predictor of selection - start contributing in January.</t>
-        </is>
-      </c>
+          <t>https://www.citadel.com/careers/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Handshake AI Fellowship</t>
+          <t>Gemini Collegiate Quantitative Trading Competition</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Check via student orgs</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Undergrad and above</t>
+          <t>Students, allocated by team</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>https://joinhandshake.com/ai/</t>
+          <t>https://www.gemini.com/</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>NOT an internship - 1099 AI-training gig work. Math queues pay the top tier ($17-125/hr). Volatile workflow; two lawsuits allege withheld payments. Read each project's time cap.</t>
+          <t>Trades on the live Gemini exchange under competition accounts.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Kalshi - Support Ops Intern</t>
+          <t>Hull Tactical Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Rolling - see Kaggle</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>No class-year gate</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://kalshi.com/careers</t>
+          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Ops rather than SWE. $20-25/hr.</t>
+          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn First Play</t>
+          <t>IICPC Codefest 2026</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>https://codefest.iicpc.com/</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Rolling - see Kaggle</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Anyone with an account</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Quantiacs Crypto Contest</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>2026 contest cycles</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>https://quantiacs.com/</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>The Deck Game</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>Completed 1st or 2nd year of CS</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.linkedin.com/</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>MLH Fellowship</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Rolling (fall batch closed Aug 31, 2026)</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Any student</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>https://fellowship.mlh.io/</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Ignite</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Aug-Sep; deadline Oct-Nov</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>Current freshmen &amp; sophomores</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>12-week 'pre-internship'. Software / Hardware / Business Ops tracks. Some NVIDIA pages say 'underrepresented communities', main US pages say 'wide range of backgrounds' - do not self-select out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Internship (software / systems)</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Aug-Oct, rolling</t>
-        </is>
-      </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>BS and above</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+          <t>https://thedeckgame.com/</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Long shot but no GPA cutoff. $20-71/hr software + $1,800-2,800/mo housing. Avoid AI-research reqs (8 of 9 want MS/PhD).</t>
+          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Scale AI - AI Builder Intern</t>
+          <t>Goldman Sachs Possibilities Summits</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad, no class-year gate</t>
+          <t>Varies by summit</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>https://scale.com/careers</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr"/>
+          <t>https://higher.gs.com/campus</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26. Restricted to specific underrepresented groups - confirm by hand. higher.gs.com/campus is a JavaScript shell (29 chars) and the programme URLs guessed from lists 404.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>UberSTAR</t>
+          <t>JPMorgan Code for Good</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Dec-Jan</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Freshman/sophomore</t>
+          <t>VERIFY - historically broader across years</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://www.uber.com/us/en/careers/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Consistently positive reviews.</t>
+          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3325,32 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg Global Trading Challenge</t>
+          <t>Citadel Securities Quant Invitational</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>TBA for 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
+          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
+          <t>Listed on their programs page; class-year requirement not published.</t>
         </is>
       </c>
     </row>
@@ -3358,34 +3362,30 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>Cubist Quant Academy</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>2026 cycle</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
-        </is>
-      </c>
+          <t>https://careers.point72.com/</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>CME Group University Trading Challenge</t>
+          <t>Discover DRW</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>University students</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
+          <t>https://drw.com/work-at-drw/category/campus</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
+          <t>2-day quant trading immersion. Verify class year directly.</t>
         </is>
       </c>
     </row>
@@ -3432,30 +3432,34 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Citadel x Amplify Trading Challenge</t>
+          <t>Five Rings Winternship</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr"/>
+          <t>https://fiverings.com/careers</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -3465,32 +3469,32 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Gemini Collegiate Quantitative Trading Competition</t>
+          <t>G-Research Spring into Quant Finance 2026</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Check via student orgs</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Students, allocated by team</t>
+          <t>Students - verify</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>https://www.gemini.com/</t>
+          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Trades on the live Gemini exchange under competition accounts.</t>
+          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
         </is>
       </c>
     </row>
@@ -3502,32 +3506,32 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Hull Tactical Market Prediction (Kaggle)</t>
+          <t>Morgan Stanley Campus - Global Programs board</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>1st-4th year, varies by programme</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
         </is>
       </c>
     </row>
@@ -3539,34 +3543,30 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>IICPC Codefest 2026</t>
+          <t>Optiver Insight Days</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://codefest.iicpc.com/</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -3576,34 +3576,30 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+          <t>Optiver Market Making Competition</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -3613,34 +3609,30 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Quantiacs Crypto Contest</t>
+          <t>Optiver Trading Day</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>2026 contest cycles</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>https://quantiacs.com/</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -3650,12 +3642,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>The Deck Game</t>
+          <t>SIG Insight Week</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3665,19 +3657,15 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://thedeckgame.com/</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -3687,34 +3675,30 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Code for Good</t>
+          <t>Two Sigma Financial Modeling Challenge</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>VERIFY - historically broader across years</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3724,12 +3708,12 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Quant Invitational</t>
+          <t>Bloomberg First Year Insights</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3739,437 +3723,445 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>First-years (unverified)</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
+          <t>https://www.bloomberg.com/company/careers/</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Listed on their programs page; class-year requirement not published.</t>
+          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>VIA CLUB</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Cubist Quant Academy</t>
+          <t>Rotman International Trading Competition</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Fall, via your university</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>University-sponsored team</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rotman.utoronto.ca/</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>APPLIED - too early</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>NISA Investment Advisors - Intern</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Local (St. Louis)</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Fall-winter</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.nisa.com/early-careers</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Edward Jones Internship</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Local (St. Louis)</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Juniors</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>10-week program, St. Louis or Tempe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Stifel - Institutional Group Internship</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Local (St. Louis)</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>~Nov, rolling per office/desk</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Juniors</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.stifel.com/careers/internships</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.point72.com/</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Discover DRW</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Winter-spring</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Rising sophomore+</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED for 1st year</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>https://drw.com/work-at-drw/category/campus</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>2-day quant trading immersion. Verify class year directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Five Rings Winternship</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED for 1st year</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>https://fiverings.com/careers</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>G-Research Spring into Quant Finance 2026</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>2nd year</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Spring 2026</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>Students - verify</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Morgan Stanley Campus - Global Programs board</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>2nd year</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Day - Technology</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>1st-4th year, varies by programme</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Optiver Insight Days</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>2nd year</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Optiver Market Making Competition</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>2nd year</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Day - Trading</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Optiver Trading Day</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>SIG Insight Week</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.sig.com/</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>Two Sigma Financial Modeling Challenge</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>https://www.twosigma.com/</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>VIA CLUB</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Rotman International Trading Competition</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Fall, via your university</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>University-sponsored team</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>https://www.rotman.utoronto.ca/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>APPLIED - too early</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>NISA Investment Advisors - Intern</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Local (St. Louis)</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Fall-winter</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://careers.nisa.com/early-careers</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
@@ -4181,32 +4173,32 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Edward Jones Internship</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Local (St. Louis)</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>10-week program, St. Louis or Tempe.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
@@ -4218,868 +4210,514 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Stifel - Institutional Group Internship</t>
+          <t>Wells Fargo Sophomore Experience</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Local (St. Louis)</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>~Nov, rolling per office/desk</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Sophomores</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://www.stifel.com/careers/internships</t>
+          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Opens ~Oct; closes mid-Nov</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Winter-spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Rising sophomore+</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr"/>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>CMF Select New York 2026</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr"/>
+          <t>https://fima.partners/</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>FutureAlpha / QuantStrats 2026</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr"/>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://www.qwafafew.org/</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>Tapia Conference</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>Open, but serves underrepresented groups in computing</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://tapiaconference.cmd-it.org/</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
+          <t>You can attend; low relative value for you.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
+          <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>First-year/sophomore</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
+          <t>https://careerhub.students.duke.edu/</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Public list of early insight programs by target year.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>Yale 'Gorick's List' for quant trading</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://openquant.co/</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>CMF Select New York 2026</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>https://fima.partners/</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>https://www.qwafafew.org/</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Tapia Conference</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Spring</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>Open, but serves underrepresented groups in computing</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>You can attend; low relative value for you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>PwC AI Externship (via Extern)</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>https://www.extern.com/pwc-ai-externships</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>Duke Career Hub early-insight table</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>First-year/sophomore</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>https://careerhub.students.duke.edu/</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>Public list of early insight programs by target year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Yale 'Gorick's List' for quant trading</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>OpenQuant job board + newsletter</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>https://openquant.co/</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G126"/>
+  <autoFilter ref="A1:G116"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -5091,18 +4729,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId25"/>
@@ -5193,16 +4831,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5214,7 +4842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6406,8 +6034,119 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg First Year Insights</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Never - blocks automation</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>403 to the honest User-Agent on every bloomberg.com/company path.</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Open Bloomberg's students page in your browser.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Monthly, Sep-Feb</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/company/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Wells Fargo Sophomore Experience</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Never - blocks automation</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>403 to the honest User-Agent.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Open Wells Fargo's undergraduate programmes page in your browser.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Monthly, next academic year</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Possibilities Summits</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Planned - phase 3</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript shell with no found API.</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Open higher.gs.com/campus in your browser.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Monthly, Sep-Feb</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>https://higher.gs.com/campus</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:G35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -6439,6 +6178,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8716,7 +8458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8826,49 +8568,49 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bridgewater-students</t>
+          <t>Already watched by berkeley-trading-competition</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Investment Immersion Program</t>
+          <t>Berkeley Trading Competition</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
+          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by bofa-campus-events</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>Bank of America campus events (Early Insights)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -8878,120 +8620,120 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by bridgewater-students</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Bridgewater Investment Immersion Program</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hrt-student-opportunities</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Explore HRT / Inside HRT</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3-day immersive for 1st/2nd years in CS, math or STEM.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hrt-student-opportunities</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>HRT Sophomore Winternship</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>January, 2-4 weeks, Python/C++.</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -8999,36 +8741,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -9038,29 +8780,29 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -9070,24 +8812,24 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -9102,24 +8844,24 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -9129,94 +8871,98 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>INVITE</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr"/>
+          <t>https://www.duke.edu/</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -9226,48 +8972,56 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -9282,88 +9036,88 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by hrt-student-opportunities</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Explore HRT / Inside HRT</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>3-day immersive for 1st/2nd years in CS, math or STEM.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by hrt-student-opportunities</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>HRT Sophomore Winternship</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -9371,36 +9125,36 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>January, 2-4 weeks, Python/C++.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -9410,52 +9164,56 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr"/>
+          <t>https://www.iaqf.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -9463,95 +9221,95 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://prosperity.imc.com/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -9559,63 +9317,63 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep.</t>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -9623,63 +9381,63 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9687,27 +9445,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9715,14 +9477,14 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
@@ -9730,12 +9492,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9743,339 +9505,343 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by jefferies-campus</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>Jefferies campus opportunities</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
+          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by jpmc-career-edyou</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>JPMorganChase Career.edYOU Academy</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by jpmc-fellowship</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>JPMC Fellowship Program</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://github.com/LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by mathprograms-listing</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>MathPrograms.org programme listing</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://www.mathprograms.org/db/program</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - you are US-based.</t>
+          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by meta-hacker-cup</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>Meta Hacker Cup</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr"/>
+          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://battlecode.org/</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by mit-trading-competition</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>Traders@MIT Trading Competition</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://traders.mit.edu/competition</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window. Not you.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to you.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
+          <t>https://osqf.org/</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10083,31 +9849,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -10115,46 +9881,42 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by reufinder-freshmen</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
@@ -10162,328 +9924,332 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by seo-tech</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>SEO Tech Developer + First-Year Academy</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://tech.seo-usa.org/</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by sfi-ucr</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>SFI Undergraduate Complexity Research</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by smart-scholarship</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>SMART Scholarship</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.smartscholarship.org/smart</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by spcs-jobs</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://spcs.stanford.edu/jobs</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but you are too early.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by surim-apply</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by treehacks</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>TreeHacks</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://treehacks.com/</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by uchicago-trading-competition</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>UChicago Trading Competition</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr"/>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>https://tradingcompetition.uchicago.edu/</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by worldquant-iqc</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -10491,47 +10257,51 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr"/>
+          <t>https://www.worldquant.com/brain/iqc/</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yutc</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Yale Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://www.yale.edu/</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>6-week remote mentorship on open-source projects.</t>
+          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
         </is>
       </c>
     </row>
@@ -10543,12 +10313,12 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -10558,10 +10328,14 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
+          <t>https://www.bofa.com/</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -10571,7 +10345,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -10586,10 +10360,14 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr"/>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -10599,12 +10377,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -10614,10 +10392,14 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr"/>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -10627,12 +10409,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -10642,12 +10424,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10441,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -10674,12 +10456,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
+          <t>https://www.codingitforward.com/fellowship</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
         </is>
       </c>
     </row>
@@ -10691,12 +10473,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -10706,49 +10488,1073 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>D. E. Shaw Latitude Fellowship</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>D. E. Shaw London Insight Programme</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>https://campus.deshaw.com/additional-experiences</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>D. E. Shaw Momentum Fellowship</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Databento partner quant events (Shanghai, London)</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>https://databento.com/</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>https://en.tmtpost.com/post/7752441</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>IMC EU Business Course</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>IMC UK Masterclass</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.imc.com/</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Geographic exclusion - you are US-based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>IMC WiT (Women in Technology)</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>IMC Women in Trading and Engineering</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>JPMorgan Data for Good Hackathon</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.jpmorgan.com/</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>That is a junior-year window. Not you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Jane Street FOCUS and IN FOCUS</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Jane Street Graduate Research Fellowship</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Jane Street INSIGHT</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>For women, transgender and gender-expansive people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Jane Street JSIP</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Jane Street WiSE</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Women / trans / gender-expansive students.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>MIT Pokerbots</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>https://pokerbots.org/</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Meta University</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Optiver Quantitative Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Highest pay in the industry, but you are too early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Optiver regional recruitment events (non-US)</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>PEAK6 Trading Bootcamp</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>https://peak6.com/campus/</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Palantir Path</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Point72 Academy</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma College Mentor Connect</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Virtu Financial Women's Winternship</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F65"/>
+  <autoFilter ref="A1:F98"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -10798,20 +11604,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Flow Traders E-House Day</t>
+          <t>Explore HRT / Inside HRT</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1558,22 +1558,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Check - was closed as of last look</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>https://www.flowtraders.com/careers</t>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Virtual ETF / strategy session.</t>
+          <t>3-day immersive for 1st/2nd years in CS, math or STEM.</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Flow Traders Trading Business Course</t>
+          <t>Flow Traders E-House Day</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1608,7 +1608,11 @@
           <t>https://www.flowtraders.com/careers</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Virtual ETF / strategy session.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1618,7 +1622,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Market Prediction (Kaggle)</t>
+          <t>Flow Traders Trading Business Course</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1628,17 +1632,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>When live</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Anyone</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions</t>
+          <t>https://www.flowtraders.com/careers</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Puzzles (monthly)</t>
+          <t>Jane Street Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1661,7 +1665,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>When live</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1671,14 +1675,10 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/puzzles/</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>The free on-ramp to the ETC/Symposium invite ecosystem. Do these.</t>
-        </is>
-      </c>
+          <t>https://www.kaggle.com/competitions</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SF Puzzle City</t>
+          <t>Jane Street Puzzles (monthly)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Anyone</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>In-person puzzle event.</t>
+          <t>The free on-ramp to the ETC/Symposium invite ecosystem. Do these.</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>SIG First Year Discovery Day</t>
+          <t>Jane Street SF Puzzle City</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Opens ~Aug-Sep; EVENT OCT 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>1st year only</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://www.janestreet.com/puzzles/</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Virtual. No prior finance experience required. Confirmed date - nearest hard deadline on this list.</t>
+          <t>In-person puzzle event.</t>
         </is>
       </c>
     </row>
@@ -1762,32 +1762,32 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DOE SULI</t>
+          <t>SIG First Year Discovery Day</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Summer cycle opens fall; deadline ~Jan</t>
+          <t>Opens ~Aug-Sep; EVENT OCT 2026</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>NO class-year requirement</t>
+          <t>1st year only</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://science.osti.gov/wdts/suli</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>TOP PICK. Any full-time undergrad, 18+, 3.0 GPA, US citizen or LPR. Name SLAC as first choice and email slacinternships@slac.stanford.edu.</t>
+          <t>Virtual. No prior finance experience required. Confirmed date - nearest hard deadline on this list.</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Math REU master list (2027)</t>
+          <t>DOE SULI</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1809,22 +1809,22 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Dec-Feb</t>
+          <t>Summer cycle opens fall; deadline ~Jan</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Varies by site</t>
+          <t>NO class-year requirement</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/mathreu</t>
+          <t>https://science.osti.gov/wdts/suli</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Spreadsheet of REUs planning to run in summer 2027. | Checked 2026-09-26: the data lives in a Google Sheet (docs.google.com/spreadsheets/d/1U-27BeHMSJCWumbNByal2tHyYo9wRVud9WoRE70E47Y), which holds 1 row (350 chars) - below the 500-char content floor, so it is not watched yet. MathPrograms.org is watched instead.</t>
+          <t>TOP PICK. Any full-time undergrad, 18+, 3.0 GPA, US citizen or LPR. Name SLAC as first choice and email slacinternships@slac.stanford.edu.</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>NASA Internships</t>
+          <t>Math REU master list (2027)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1846,22 +1846,22 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Dec-Feb</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Varies by posting</t>
+          <t>Varies by site</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>https://intern.nasa.gov/</t>
+          <t>https://sites.google.com/view/mathreu</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Many individual postings accept freshmen.</t>
+          <t>Spreadsheet of REUs planning to run in summer 2027. | Checked 2026-09-26: the data lives in a Google Sheet (docs.google.com/spreadsheets/d/1U-27BeHMSJCWumbNByal2tHyYo9wRVud9WoRE70E47Y), which holds 1 row (350 chars) - below the 500-char content floor, so it is not watched yet. MathPrograms.org is watched instead.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PCMI Undergraduate Summer School</t>
+          <t>NASA Internships</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1883,22 +1883,22 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Deadline Jan 31 (via MathPrograms.org)</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>All undergraduate levels</t>
+          <t>Varies by posting</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://www.ias.edu/pcmi</t>
+          <t>https://intern.nasa.gov/</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>3 weeks in residence + Experimental Math Lab. Prereqs vary by year's theme - 2026 needed group theory, 2025 only combinatorics.</t>
+          <t>Many individual postings accept freshmen.</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Polymath Jr REU</t>
+          <t>PCMI Undergraduate Summer School</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Apr 1</t>
+          <t>Deadline Jan 31 (via MathPrograms.org)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad with proof-writing experience</t>
+          <t>All undergraduate levels</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>https://geometrynyc.wixsite.com/polymathreu</t>
+          <t>https://www.ias.edu/pcmi</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Online, groups of 10-25 working toward a paper. No citizenship restriction. Part-time allowed, so it stacks with something else.</t>
+          <t>3 weeks in residence + Experimental Math Lab. Prereqs vary by year's theme - 2026 needed group theory, 2025 only combinatorics.</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>SLAC internships (beyond SULI)</t>
+          <t>Polymath Jr REU</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1957,22 +1957,22 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Deadline ~Apr 1</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Any undergrad with proof-writing experience</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>https://careers.slac.stanford.edu/</t>
+          <t>https://geometrynyc.wixsite.com/polymathreu</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>e.g. the LCLS internship. A mile from campus.</t>
+          <t>Online, groups of 10-25 working toward a paper. No citizenship restriction. Part-time allowed, so it stacks with something else.</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>UChicago Math REU - Apprentice Program</t>
+          <t>SLAC internships (beyond SULI)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Deadline ~Feb 6</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Freshmen &amp; sophomores</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://math.uchicago.edu/~may/REU2026/</t>
+          <t>https://careers.slac.stanford.edu/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
+          <t>e.g. the LCLS internship. A mile from campus.</t>
         </is>
       </c>
     </row>
@@ -2021,32 +2021,32 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Stanford CS Section Leading (106A/B)</t>
+          <t>UChicago Math REU - Apprentice Program</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Each quarter</t>
+          <t>Deadline ~Feb 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>After taking 106A/106B</t>
+          <t>Freshmen &amp; sophomores</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>https://cs198.stanford.edu/</t>
+          <t>https://math.uchicago.edu/~may/REU2026/</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Paid, prestigious, sophomores routinely hold it. Take the courses this year to qualify.</t>
+          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Stanford Directed Reading Program (math)</t>
+          <t>SIEPR Summer Undergraduate Research Fellows</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2068,22 +2068,22 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Start of each quarter</t>
+          <t>Not on page (winter quarter typical)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad, any major</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://siepr.stanford.edu/programs/undergraduate-student-opportunities/undergraduate-research-fellows-program/siepr-summer</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter.</t>
+          <t>Verified 2026-09-30: 'Participants must be current Stanford undergraduates during the summer quarter.' 10 weeks, $8,500, economic-policy research RA with SIEPR faculty.</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Stanford Finance</t>
+          <t>Sophomore College (SoCo)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2105,22 +2105,22 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Apply ~Mar 2 - Apr 14 (spring quarter week 3)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>1st year (apply as frosh)</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanfordfinance.stanford.edu/</t>
+          <t>https://september.stanford.edu/apply/student-applicant</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Workshop series, networking, 1:1 officer mentorship.</t>
+          <t>Verified 2026-09-30: 'Eligible students typically apply as frosh ... and will be enrolled sophomores ... in the autumn quarter immediately following Sophomore College.' 3-week residential course before autumn quarter; check that year's course list for a math/CS offering.</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Stanford SymSys Summer Internships</t>
+          <t>Stanford CS Section Leading (106A/B)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Priority Feb 18; opens to non-majors Mar 9</t>
+          <t>Each quarter</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Stanford undergrads</t>
+          <t>After taking 106A/106B</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://symsys.stanford.edu/</t>
+          <t>https://cs198.stanford.edu/</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window.</t>
+          <t>Paid, prestigious, sophomores routinely hold it. Take the courses this year to qualify.</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Faculty / Departmental Grants</t>
+          <t>Stanford Directed Reading Program (math)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2179,22 +2179,22 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Faculty Feb 15; Departmental Oct 31</t>
+          <t>Start of each quarter</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford undergrad</t>
+          <t>Any Stanford undergrad, any major</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
+          <t>Quarter with a grad-student mentor, ends in a colloquium talk. Near-zero barrier and the cheapest route to a SURIM letter.</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Small Grants</t>
+          <t>Stanford Finance</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Quarterly deadlines</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://www.stanfordfinance.stanford.edu/</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Part-time, year-round. Good way to start something this winter.</t>
+          <t>Workshop series, networking, 1:1 officer mentorship.</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Stanford opportunity portal (SOLO)</t>
+          <t>Stanford SymSys Summer Internships</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2253,22 +2253,22 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Always open</t>
+          <t>Priority Feb 18; opens to non-majors Mar 9</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Any Stanford student</t>
+          <t>Stanford undergrads</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>https://solo.stanford.edu/</t>
+          <t>https://symsys.stanford.edu/</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Aggregates all of the above.</t>
+          <t>$8,500 + up to $1,500. A real backdoor if funds remain after the priority window.</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Traders @ Stanford / Quant Gym</t>
+          <t>Stanford VPUE Faculty / Departmental Grants</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Faculty Feb 15; Departmental Oct 31</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanfordacm.org/quantGym</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>JOIN IN WEEK ONE. Nearly every competition on this sheet is team-based and university-affiliated; this is where teams and invites form.</t>
+          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
         </is>
       </c>
     </row>
@@ -2317,32 +2317,32 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Capital One TEIP</t>
+          <t>Stanford VPUE Small Grants</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Dec-Jan</t>
+          <t>Quarterly deadlines</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Freshman/sophomore</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Underclassman version of TIP (which is rising-seniors only). Real SWE work, full intern comp.</t>
+          <t>Part-time, year-round. Good way to start something this winter.</t>
         </is>
       </c>
     </row>
@@ -2354,30 +2354,34 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows</t>
+          <t>Stanford opportunity portal (SOLO)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Always open</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates</t>
+          <t>Any Stanford student</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/company/careers</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr"/>
+          <t>https://solo.stanford.edu/</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Aggregates all of the above.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2387,30 +2391,34 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Duolingo Thrive</t>
+          <t>Traders @ Stanford / Quant Gym</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Underclassmen</t>
+          <t>Any Stanford undergrad</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr"/>
+          <t>https://www.stanfordacm.org/quantGym</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>JOIN IN WEEK ONE. Nearly every competition on this sheet is team-based and university-affiliated; this is where teams and invites form.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2420,7 +2428,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Etched - Supercomputing Intern</t>
+          <t>Capital One TEIP</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2430,20 +2438,24 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Dec-Jan</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's-track, no class cutoff</t>
+          <t>Freshman/sophomore</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>https://www.etched.com/</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
+          <t>https://www.capitalonecareers.com/</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Underclassman version of TIP (which is rising-seniors only). Real SWE work, full intern comp.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2453,7 +2465,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Explore Microsoft</t>
+          <t>Databricks Student Fellows</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2463,24 +2475,20 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Late summer-fall (2027 US posting not up as of Aug 2026)</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Undergraduates</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>https://careers.microsoft.com/v2/global/en/exploremicrosoft</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>12 weeks; rotate through design, build and quality phases in a pod. Set a job alert - no universal date published.</t>
-        </is>
-      </c>
+          <t>https://www.databricks.com/company/careers</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2490,7 +2498,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Google ASDI (formerly STEP)</t>
+          <t>Duolingo Thrive</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2500,24 +2508,20 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Early fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1st &amp; 2nd year</t>
+          <t>Underclassmen</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>RENAMED - search 'ASDI', not 'STEP'. 12 weeks, paired with a host engineer and a co-intern.</t>
-        </is>
-      </c>
+          <t>https://careers.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2527,7 +2531,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Google Student Researcher, BS/MS</t>
+          <t>Etched - Supercomputing Intern</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2537,24 +2541,20 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Deadline Nov 27, 2026 (rolling, may close early)</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Any enrolled bachelor's</t>
+          <t>Bachelor's-track, no class cutoff</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>MOST UNDERRATED ITEM HERE - research role across Google Research, DeepMind and Cloud with NO class-year gate. Must be US-based.</t>
-        </is>
-      </c>
+          <t>https://www.etched.com/</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Google Summer of Code</t>
+          <t>Explore Microsoft</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Orgs announced Feb; apps ~Mar 16-31</t>
+          <t>Late summer-fall (2027 US posting not up as of Aug 2026)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>18+, limited prior OSS experience</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://summerofcode.withgoogle.com/</t>
+          <t>https://careers.microsoft.com/v2/global/en/exploremicrosoft</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Design FAVOURS beginners. Pre-application contributions are the strongest predictor of selection - start contributing in January.</t>
+          <t>12 weeks; rotate through design, build and quality phases in a pod. Set a job alert - no universal date published.</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Handshake AI Fellowship</t>
+          <t>Google ASDI (formerly STEP)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2611,22 +2611,22 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Early fall</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Undergrad and above</t>
+          <t>1st &amp; 2nd year</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>https://joinhandshake.com/ai/</t>
+          <t>https://www.google.com/about/careers/applications/</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>NOT an internship - 1099 AI-training gig work. Math queues pay the top tier ($17-125/hr). Volatile workflow; two lawsuits allege withheld payments. Read each project's time cap.</t>
+          <t>RENAMED - search 'ASDI', not 'STEP'. 12 weeks, paired with a host engineer and a co-intern.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Kalshi - Support Ops Intern</t>
+          <t>Google Student Researcher, BS/MS</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Deadline Nov 27, 2026 (rolling, may close early)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>No class-year gate</t>
+          <t>Any enrolled bachelor's</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://kalshi.com/careers</t>
+          <t>https://www.google.com/about/careers/applications/</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Ops rather than SWE. $20-25/hr.</t>
+          <t>MOST UNDERRATED ITEM HERE - research role across Google Research, DeepMind and Cloud with NO class-year gate. Must be US-based.</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>LinkedIn First Play</t>
+          <t>Google Summer of Code</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2685,20 +2685,24 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Orgs announced Feb; apps ~Mar 16-31</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Completed 1st or 2nd year of CS</t>
+          <t>18+, limited prior OSS experience</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
+          <t>https://summerofcode.withgoogle.com/</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Design FAVOURS beginners. Pre-application contributions are the strongest predictor of selection - start contributing in January.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2708,7 +2712,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>MLH Fellowship</t>
+          <t>Handshake AI Fellowship</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -2718,20 +2722,24 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Rolling (fall batch closed Aug 31, 2026)</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Any student</t>
+          <t>Undergrad and above</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://fellowship.mlh.io/</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
+          <t>https://joinhandshake.com/ai/</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>NOT an internship - 1099 AI-training gig work. Math queues pay the top tier ($17-125/hr). Volatile workflow; two lawsuits allege withheld payments. Read each project's time cap.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2741,7 +2749,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Ignite</t>
+          <t>Kalshi - Support Ops Intern</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2751,22 +2759,22 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Aug-Sep; deadline Oct-Nov</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Current freshmen &amp; sophomores</t>
+          <t>No class-year gate</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+          <t>https://kalshi.com/careers</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>12-week 'pre-internship'. Software / Hardware / Business Ops tracks. Some NVIDIA pages say 'underrepresented communities', main US pages say 'wide range of backgrounds' - do not self-select out.</t>
+          <t>Ops rather than SWE. $20-25/hr.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2786,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Internship (software / systems)</t>
+          <t>LinkedIn First Play</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2788,24 +2796,20 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Aug-Oct, rolling</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>BS and above</t>
+          <t>Completed 1st or 2nd year of CS</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>Long shot but no GPA cutoff. $20-71/hr software + $1,800-2,800/mo housing. Avoid AI-research reqs (8 of 9 want MS/PhD).</t>
-        </is>
-      </c>
+          <t>https://careers.linkedin.com/</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2815,7 +2819,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Scale AI - AI Builder Intern</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2825,17 +2829,17 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Rolling (fall batch closed Aug 31, 2026)</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Any undergrad, no class-year gate</t>
+          <t>Any student</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>https://scale.com/careers</t>
+          <t>https://fellowship.mlh.io/</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr"/>
@@ -2848,143 +2852,139 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
+          <t>NVIDIA Ignite</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Aug-Sep; deadline Oct-Nov</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Current freshmen &amp; sophomores</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>12-week 'pre-internship'. Software / Hardware / Business Ops tracks. Some NVIDIA pages say 'underrepresented communities', main US pages say 'wide range of backgrounds' - do not self-select out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA Internship (software / systems)</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Aug-Oct, rolling</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>BS and above</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Long shot but no GPA cutoff. $20-71/hr software + $1,800-2,800/mo housing. Avoid AI-research reqs (8 of 9 want MS/PhD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Scale AI - AI Builder Intern</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Any undergrad, no class-year gate</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>https://scale.com/careers</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
           <t>UberSTAR</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Dec-Jan</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Freshman/sophomore</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>https://www.uber.com/us/en/careers/</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>Consistently positive reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Bloomberg Global Trading Challenge</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>TBA for 2026</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>CFA Institute Research Challenge</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>2026 cycle</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>CME Group University Trading Challenge</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Check site</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>University students</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Citadel x Amplify Trading Challenge</t>
+          <t>Bloomberg Global Trading Challenge</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3006,20 +3006,24 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>TBA for 2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadel.com/careers/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
+          <t>https://portal.bloombergforeducation.com/trading_challenges</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg's student trading simulation. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Cannot be monitored: robots.txt disallows this path and the page renders in JavaScript (23 chars of text).</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -3029,7 +3033,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Gemini Collegiate Quantitative Trading Competition</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -3039,22 +3043,22 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Check via student orgs</t>
+          <t>2026 cycle</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Students, allocated by team</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>https://www.gemini.com/</t>
+          <t>https://www.cfainstitute.org/insights/events/research-challenge</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Trades on the live Gemini exchange under competition accounts.</t>
+          <t>Equity-research competition entered as a university-sponsored team, so entry runs through a Stanford team rather than individual application. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Finance rather than quant, so weigh against the time cost.</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3070,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Hull Tactical Market Prediction (Kaggle)</t>
+          <t>CME Group University Trading Challenge</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3076,22 +3080,22 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>University students</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
+          <t>https://www.cmegroup.com/events/university-trading-challenge.html</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
+          <t>CME's university trading challenge, typically a multi-week team futures competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. The page would not load for an automated client.</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3107,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>IICPC Codefest 2026</t>
+          <t>Citadel x Amplify Trading Challenge</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3113,24 +3117,20 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>https://codefest.iicpc.com/</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
-        </is>
-      </c>
+          <t>https://www.citadel.com/careers/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+          <t>Gemini Collegiate Quantitative Trading Competition</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3150,22 +3150,22 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>Check via student orgs</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>Students, allocated by team</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
+          <t>https://www.gemini.com/</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
+          <t>Trades on the live Gemini exchange under competition accounts.</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Quantiacs Crypto Contest</t>
+          <t>Hull Tactical Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>2026 contest cycles</t>
+          <t>Rolling - see Kaggle</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>https://quantiacs.com/</t>
+          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
+          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>The Deck Game</t>
+          <t>IICPC Codefest 2026</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://thedeckgame.com/</t>
+          <t>https://codefest.iicpc.com/</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
+          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
         </is>
       </c>
     </row>
@@ -3251,32 +3251,32 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Goldman Sachs Possibilities Summits</t>
+          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling - see Kaggle</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Varies by summit</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>https://higher.gs.com/campus</t>
+          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26. Restricted to specific underrepresented groups - confirm by hand. higher.gs.com/campus is a JavaScript shell (29 chars) and the programme URLs guessed from lists 404.</t>
+          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
         </is>
       </c>
     </row>
@@ -3288,32 +3288,32 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Code for Good</t>
+          <t>Quantiacs Crypto Contest</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>2026 contest cycles</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>VERIFY - historically broader across years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://quantiacs.com/</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
+          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Quant Invitational</t>
+          <t>The Deck Game</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
+          <t>https://thedeckgame.com/</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Listed on their programs page; class-year requirement not published.</t>
+          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Cubist Quant Academy</t>
+          <t>Goldman Sachs Possibilities Summits</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3377,15 +3377,19 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>Varies by summit</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://careers.point72.com/</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr"/>
+          <t>https://higher.gs.com/campus</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26. Restricted to specific underrepresented groups - confirm by hand. higher.gs.com/campus is a JavaScript shell (29 chars) and the programme URLs guessed from lists 404.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -3395,32 +3399,32 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Discover DRW</t>
+          <t>JPMorgan Code for Good</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED for 1st year</t>
+          <t>VERIFY - historically broader across years</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>https://drw.com/work-at-drw/category/campus</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2-day quant trading immersion. Verify class year directly.</t>
+          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3436,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Five Rings Winternship</t>
+          <t>Citadel Securities Quant Invitational</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3442,22 +3446,22 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED for 1st year</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://fiverings.com/careers</t>
+          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
+          <t>Listed on their programs page; class-year requirement not published.</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>G-Research Spring into Quant Finance 2026</t>
+          <t>Cubist Quant Academy</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3479,24 +3483,20 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Students - verify</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
-        </is>
-      </c>
+          <t>https://careers.point72.com/</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Campus - Global Programs board</t>
+          <t>Discover DRW</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3516,22 +3516,22 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1st-4th year, varies by programme</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+          <t>https://drw.com/work-at-drw/category/campus</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+          <t>2-day quant trading immersion. Verify class year directly.</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Optiver Insight Days</t>
+          <t>Five Rings Winternship</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3553,20 +3553,24 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr"/>
+          <t>https://fiverings.com/careers</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -3576,7 +3580,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Optiver Market Making Competition</t>
+          <t>G-Research Spring into Quant Finance 2026</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -3586,20 +3590,24 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>Students - verify</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr"/>
+          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -3609,7 +3617,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Optiver Trading Day</t>
+          <t>Morgan Stanley Campus - Global Programs board</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3619,20 +3627,24 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>1st-4th year, varies by programme</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -3642,7 +3654,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>SIG Insight Week</t>
+          <t>Optiver Insight Days</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3662,7 +3674,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr"/>
@@ -3675,7 +3687,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Financial Modeling Challenge</t>
+          <t>Optiver Market Making Competition</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3695,7 +3707,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr"/>
@@ -3708,12 +3720,12 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg First Year Insights</t>
+          <t>Optiver Trading Day</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -3723,239 +3735,227 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>First-years (unverified)</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/company/careers/</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>SIG Insight Week</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Financial Modeling Challenge</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>'approximately 30 degree-seeking credits'</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>https://spcs.stanford.edu/jobs</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg First Year Insights</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>First-years (unverified)</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED - too early</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>NISA Investment Advisors - Intern</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Fall-winter</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.nisa.com/early-careers</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Edward Jones Internship</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Fall</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>Juniors</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>10-week program, St. Louis or Tempe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>Stifel - Institutional Group Internship</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>~Nov, rolling per office/desk</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>Juniors</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>https://www.stifel.com/careers/internships</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Winter-spring</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>Rising sophomore+</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>APPLIED - too early</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+          <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+          <t>Fall-winter</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+          <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
@@ -3967,12 +3967,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>Edward Jones Internship</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -3982,15 +3982,19 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>10-week program, St. Louis or Tempe.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -4000,30 +4004,34 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr"/>
+          <t>https://www.stifel.com/careers/internships</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -4033,7 +4041,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4043,20 +4051,24 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Winter-spring</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Rising sophomore+</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr"/>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -4066,7 +4078,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>HRT Sophomore Winternship</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -4086,10 +4098,14 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr"/>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>January, 2-4 weeks, Python/C++.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -4099,7 +4115,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4109,22 +4125,22 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4152,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4151,19 +4167,15 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -4173,34 +4185,30 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -4210,197 +4218,189 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Sophomore Experience</t>
+          <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Sophomores</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>CMF Select New York 2026</t>
+          <t>Wells Fargo Sophomore Experience</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Sophomores</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
         </is>
       </c>
     </row>
@@ -4432,12 +4432,12 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>https://fima.partners/</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://www.qwafafew.org/</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Tapia Conference</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4553,22 +4553,22 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Open, but serves underrepresented groups in computing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>You can attend; low relative value for you.</t>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -4580,144 +4580,366 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
+          <t>CMF Select New York 2026</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Future Investment Manager Academy (FIMA)</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>https://fima.partners/</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>FutureAlpha / QuantStrats 2026</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qwafafew.org/</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Tapia Conference</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Open, but serves underrepresented groups in computing</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>https://tapiaconference.cmd-it.org/</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>You can attend; low relative value for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>First-year/sophomore</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>https://careerhub.students.duke.edu/</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>Public list of early insight programs by target year.</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>MLH hackathon season calendar</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Weekly all year</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Any undergrad year</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mlh.com/seasons/2027/events</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-30: MLH's official season calendar (e.g. Gator Quant Hacks, MHacks, Oct 2026). Too high-churn for page_text; treat as a manual/calendar pointer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>Yale 'Gorick's List' for quant trading</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G116"/>
+  <autoFilter ref="A1:G122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -4831,6 +5053,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8458,7 +8686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8600,12 +8828,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bofa-campus-events</t>
+          <t>Already watched by bny-pre-internship</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bank of America campus events (Early Insights)</t>
+          <t>BNY Freshman Jumpstart</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -8613,100 +8841,100 @@
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
+          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bridgewater-students</t>
+          <t>Already watched by bofa-campus-events</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Investment Immersion Program</t>
+          <t>Bank of America campus events (Early Insights)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
+          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Already watched by capitalone-early-career</t>
+          <t>Already watched by bridgewater-students</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Capital One Analyst / Tech / Product Summits</t>
+          <t>Bridgewater Investment Immersion Program</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
+          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Already watched by comap-mcm</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>COMAP MCM/ICM</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -8716,29 +8944,29 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/undergraduate/contests/</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cornell-trading-competition</t>
+          <t>Already watched by citi-pre-internships</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>Citi Freshman Discovery</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -8748,29 +8976,29 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cra-dreu</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>CRA DREU</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -8780,29 +9008,29 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://cra.org/cra-wp/dreu/</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by curis</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8812,125 +9040,125 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cs-social-good-fellowships</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw campus site</t>
+          <t>CS+Social Good Summer Fellowships</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/</t>
+          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
+          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dimacs-reu</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>DIMACS REU</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://dimacs.rutgers.edu/reu-main</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dukequant-competition</t>
+          <t>Already watched by datasurf</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>Stanford DataSURF (formerly SURP-Stats)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -8940,189 +9168,189 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by evercore-campus</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Evercore student events</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by futureforce-launchpad</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.duke.edu/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hrt-student-opportunities</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Explore HRT / Inside HRT</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>3-day immersive for 1st/2nd years in CS, math or STEM.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hrt-student-opportunities</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>HRT Sophomore Winternship</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -9132,24 +9360,24 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>January, 2-4 weeks, Python/C++.</t>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -9164,29 +9392,29 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icerm-summer</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Summer@ICERM</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -9196,24 +9424,24 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://icerm.brown.edu/summerug/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icpc-pnw</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -9221,36 +9449,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -9260,29 +9488,29 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-prosperity</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -9292,24 +9520,24 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -9317,31 +9545,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-preview</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Preview</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -9349,31 +9577,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
+          <t>https://prosperity.imc.com/</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -9381,31 +9609,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -9415,17 +9643,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9665,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9445,19 +9673,19 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9697,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9487,7 +9715,11 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -9497,7 +9729,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9505,9 +9737,9 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -9515,269 +9747,269 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jefferies-campus</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Jefferies campus opportunities</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-career-edyou</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>JPMorganChase Career.edYOU Academy</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-fellowship</t>
+          <t>Already watched by jefferies-campus</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>JPMC Fellowship Program</t>
+          <t>Jefferies campus opportunities</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
+          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by jpmc-career-edyou</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>JPMorganChase Career.edYOU Academy</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr"/>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mathprograms-listing</t>
+          <t>Already watched by jpmc-fellowship</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MathPrograms.org programme listing</t>
+          <t>JPMC Fellowship Program</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://www.mathprograms.org/db/program</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
+          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Already watched by meta-hacker-cup</t>
+          <t>Already watched by jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Meta Hacker Cup</t>
+          <t>Jump Trading Campus Jump Early Access</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+          <t>https://www.jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by kkr-greenhouse</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>KKR Scholars Program</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-trading-competition</t>
+          <t>Already watched by kleinerperkins-fellows-ashby</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Traders@MIT Trading Competition</t>
+          <t>Kleiner Perkins Engineering Fellows</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://traders.mit.edu/competition</t>
+          <t>https://www.kleinerperkins.com/fellows/</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to you.</t>
+          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9787,34 +10019,30 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>USE WEEKLY</t>
+          <t>USE</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
-        </is>
-      </c>
+          <t>https://github.com/LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by mathprograms-listing</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>MathPrograms.org programme listing</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -9824,29 +10052,29 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.mathprograms.org/db/program</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by meta-hacker-cup</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>Meta Hacker Cup</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -9856,24 +10084,24 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by millennium-eightfold</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Meet Millennium</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -9888,80 +10116,88 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr"/>
+          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Already watched by reufinder-freshmen</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
+          <t>https://battlecode.org/</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Already watched by seo-tech</t>
+          <t>Already watched by mit-trading-competition</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SEO Tech Developer + First-Year Academy</t>
+          <t>Traders@MIT Trading Competition</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://tech.seo-usa.org/</t>
+          <t>https://traders.mit.edu/competition</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to you.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sfi-ucr</t>
+          <t>Already watched by nist-surf</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>SFI Undergraduate Complexity Research</t>
+          <t>NIST SURF</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -9969,31 +10205,31 @@
           <t>Research / math</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
+          <t>https://www.nist.gov/surf</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
+          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -10001,31 +10237,31 @@
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Already watched by smart-scholarship</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>SMART Scholarship</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10040,29 +10276,29 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>https://www.smartscholarship.org/smart</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Already watched by spcs-jobs</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -10072,29 +10308,29 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://spcs.stanford.edu/jobs</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -10104,29 +10340,25 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Already watched by surim-apply</t>
+          <t>Already watched by ramp-ashby</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>Ramp Emerging Talent</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -10136,56 +10368,52 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://ramp.com/emerging-talent</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
+          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Already watched by treehacks</t>
+          <t>Already watched by reufinder-freshmen</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>TreeHacks</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://treehacks.com/</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
-        </is>
-      </c>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Already watched by uchicago-trading-competition</t>
+          <t>Already watched by scudem</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>UChicago Trading Competition</t>
+          <t>SCUDEM XI 2026</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -10200,120 +10428,120 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>https://tradingcompetition.uchicago.edu/</t>
+          <t>https://www.contest.comap.com/scudem/index.html</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
+          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by seo-tech</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>SEO Tech Developer + First-Year Academy</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://tech.seo-usa.org/</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Already watched by worldquant-iqc</t>
+          <t>Already watched by sfi-ucr</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>SFI Undergraduate Complexity Research</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Already watched by yutc</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Yale Undergraduate Trading Competition</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://www.yale.edu/</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by smart-scholarship</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>SMART Scholarship</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -10321,223 +10549,223 @@
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://www.smartscholarship.org/smart</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by surim-apply</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by treehacks</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>TreeHacks</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://treehacks.com/</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by twosigma-campus</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>Two Sigma New Seekers Summit</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://www.twosigma.com/new-seekers-summit/</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by uchicago-trading-competition</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>UChicago Trading Competition</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://tradingcompetition.uchicago.edu/</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by worldquant-iqc</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -10545,51 +10773,51 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
+          <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yutc</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>Yale Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.yale.edu/</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10829,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -10616,12 +10844,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://www.bofa.com/</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10633,12 +10861,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -10648,12 +10876,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -10665,12 +10893,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -10680,12 +10908,12 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10925,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10712,12 +10940,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - you are US-based.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10957,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -10744,10 +10972,14 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr"/>
+          <t>https://www.codingitforward.com/fellowship</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -10757,7 +10989,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -10772,12 +11004,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -10789,12 +11021,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -10804,12 +11036,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window. Not you.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -10821,7 +11053,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -10836,12 +11068,12 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://campus.deshaw.com/additional-experiences</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
         </is>
       </c>
     </row>
@@ -10853,7 +11085,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -10868,10 +11100,14 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr"/>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -10881,12 +11117,12 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -10896,12 +11132,12 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://databento.com/</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10913,12 +11149,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -10928,12 +11164,12 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+          <t>https://en.tmtpost.com/post/7752441</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -10945,7 +11181,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -10960,10 +11196,14 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr"/>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -10973,7 +11213,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -10988,12 +11228,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Geographic exclusion - you are US-based.</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11245,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -11020,14 +11260,10 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -11037,12 +11273,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -11052,12 +11288,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -11069,12 +11305,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -11082,14 +11318,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>That is a junior-year window. Not you.</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11337,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -11116,12 +11352,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11369,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -11148,14 +11384,10 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>Highest pay in the industry, but you are too early.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -11165,7 +11397,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -11180,12 +11412,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>For women, transgender and gender-expansive people.</t>
         </is>
       </c>
     </row>
@@ -11197,7 +11429,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -11212,12 +11444,12 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
         </is>
       </c>
     </row>
@@ -11229,12 +11461,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -11242,9 +11474,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr"/>
@@ -11257,7 +11489,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -11272,12 +11504,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+          <t>Women / trans / gender-expansive students.</t>
         </is>
       </c>
     </row>
@@ -11289,12 +11521,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -11304,10 +11536,14 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr"/>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -11317,12 +11553,12 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -11332,12 +11568,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>6-week remote mentorship on open-source projects.</t>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11585,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -11362,12 +11598,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -11377,7 +11617,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -11392,10 +11632,14 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr"/>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -11405,7 +11649,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Optiver Quantitative Intern Summer 2027</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -11420,10 +11664,14 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr"/>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Highest pay in the industry, but you are too early.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -11433,12 +11681,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Optiver regional recruitment events (non-US)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -11448,12 +11696,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://optiver.com/recruitment-events/</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -11465,12 +11713,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>PEAK6 Trading Bootcamp</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -11480,12 +11728,12 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
+          <t>https://peak6.com/campus/</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
         </is>
       </c>
     </row>
@@ -11497,12 +11745,12 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>Palantir Path</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -11510,51 +11758,319 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Point72 Academy</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma College Mentor Connect</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Virtu Financial Women's Winternship</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F98"/>
+  <autoFilter ref="A1:F107"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -11637,20 +12153,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Highest-signal single line you can add to a quant resume in year one. A high placement reportedly overrides GPA and non-target background. | Checked 2026-09-26: maa.org returns 403 to this client, so it cannot be watched; registration goes through Stanford's local supervisor, typically opening in September and closing before the early-December exam.</t>
+          <t>Among the highest-signal lines a first-year can add to a quant resume. A high placement reportedly overrides GPA and non-target background. | Checked 2026-09-26: maa.org returns 403 to this client, so it cannot be watched; registration goes through Stanford's local supervisor, typically opening in September and closing before the early-December exam.</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Built for you: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
+          <t>Built for first-years: 5 weeks, discrete math, for students not yet in advanced courses. Apprentices often return to the full program. | Checked 2026-09-26: the URL is year-specific; REU2027/ returns 404 today and the parent page does not link it yet. Kept.</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>THE right entry point for a freshman - a professor applies on your behalf. VPUE calls these 'good starting points'.</t>
+          <t>THE right entry point for a freshman - a professor applies on the student's behalf. VPUE calls these 'good starting points'.</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21, asked for directly: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not you directly.</t>
+          <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not by individual application.</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - you qualify spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - Jason is class of 2030, so he is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>You can attend; low relative value for you.</t>
+          <t>Open to attend; low relative value for a first-year.</t>
         </is>
       </c>
     </row>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>The site is pollable, but announcements go out on the club's Instagram and university listservs BEFORE the page updates. By the time a diff fires you may be late.</t>
+          <t>The site is pollable, but announcements go out on the club's Instagram and university listservs BEFORE the page updates. By the time a diff fires it may be late.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Club Instagram plus your Traders @ Stanford channels.</t>
+          <t>Club Instagram plus Traders @ Stanford channels.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Watch your Stanford email and the campus recruiting calendar.</t>
+          <t>Watch Stanford email and the campus recruiting calendar.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Join the mailing list and Slack/GroupMe in your first week of fall quarter.</t>
+          <t>Join the mailing list and Slack/GroupMe in the first week of fall quarter.</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>First-year only, and the single highest-value freshman program in quant. Rolling review: slots have reportedly filled by late October, so week-one applications face the most open seats. If you do one thing this fall, do this.</t>
+          <t>First-year only, and the single highest-value freshman program in quant. Rolling review: slots have reportedly filled by late October, so week-one applications face the most open seats. The single highest-value action of the fall.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Both are freshman-eligible and marked YES in your sheet, and they are SEPARATE applications - apply to both. Citadel's sites 403 every automated client, so this tool is structurally blind to them. This is the biggest gap in the system.</t>
+          <t>Both are freshman-eligible and marked YES in programs.csv, and they are SEPARATE applications - apply to both. Citadel's sites 403 every automated client, so this tool is structurally blind to them. This is the biggest gap in the system.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>First-year only. Note your sheet's warning: the 'for Women' Discovery Days are a different, ineligible track - make sure you are looking at the general one.</t>
+          <t>First-year only. Note the warning in programs.csv: the 'for Women' Discovery Days are a different, ineligible track - the general one is the right track.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>No class-year gate - open to any enrolled bachelor's student, which is unusual and makes it one of the few research-track roles a first-year can actually win. Fixed deadline, so put it in your calendar now.</t>
+          <t>No class-year gate - open to any enrolled bachelor's student, which is unusual and makes it one of the few research-track roles a first-year can actually win. Fixed deadline, so it belongs in a calendar now.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Early-undergrad program, marked YES. Same Cloudflare block as the rest of Citadel - you must check this one by hand.</t>
+          <t>Early-undergrad program, marked YES. Same Cloudflare block as the rest of Citadel - this one must be checked by hand.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>First- and second-year eligible. HRT's student page is plain HTML and this tool watches it well, so a state change here should reach you.</t>
+          <t>First- and second-year eligible. HRT's student page is plain HTML and this tool watches it well, so a state change here should reach the digest.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Explicitly NO class-year requirement, paid, at a national lab - one of the strongest research options genuinely open to a first-year. Not mentioned in any repo this tool tracks, so it is on you until phase 3.</t>
+          <t>Explicitly NO class-year requirement, paid, at a national lab - one of the strongest research options genuinely open to a first-year. Not mentioned in any repo this tool tracks, so it is a manual check until phase 3.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Paid CS research with Stanford faculty, open to any Stanford undergrad. Competing against Stanford students only, which is a far smaller pool than any national program. The site is fully client-rendered and appears in zero tracked repos - check it yourself in January.</t>
+          <t>Paid CS research with Stanford faculty, open to any Stanford undergrad. Competing against Stanford students only, which is a far smaller pool than any national program. The site is fully client-rendered and appears in zero tracked repos - check it by hand in January.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Funding, not a competition - if you have a faculty sponsor and a coherent plan, these are close to a formality. The quarterly Small Grants are the easiest money on this entire sheet. Note the Major Grant mentor letter is due Mar 8.</t>
+          <t>Funding, not a competition - given a faculty sponsor and a coherent plan, these are close to a formality. The quarterly Small Grants are the easiest money on this entire sheet. Note the Major Grant mentor letter is due Mar 8.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Paid, on-campus, repeatable, and a genuine credential on a quant/SWE resume. Available as soon as you have taken 106A/B - apply the very first quarter you are eligible.</t>
+          <t>Paid, on-campus, repeatable, and a genuine credential on a quant/SWE resume. Available after 106A/B - apply in the first eligible quarter.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Not an application, and it is the gateway to several competitions that only accept university-sponsored teams. It is also where you will hear about Cornell CTC and UChicago UTC before any website says anything.</t>
+          <t>Not an application, and it is the gateway to several competitions that only accept university-sponsored teams. It is also where announcements come for Cornell CTC and UChicago UTC before any website says anything.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>No gate at all. A submitted solution is a real touchpoint with the firm you most want, every single month, for the price of an evening.</t>
+          <t>No gate at all. A submitted solution is a real touchpoint with the firm, every single month, for the price of an evening.</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Open entry, no class-year or identity gate. A leaderboard placing is portable, verifiable evidence - and the Optiver and Jane Street sponsored competitions read as quant credentials specifically. Your sheet already flags these as a legitimate substitute if ETC never materialises.</t>
+          <t>Open entry, no class-year or identity gate. A leaderboard placing is portable, verifiable evidence - and the Optiver and Jane Street sponsored competitions read as quant credentials specifically. programs.csv already flags these as a legitimate substitute if ETC never materialises.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Open to anyone 18+ and enrolled. Algorithmic trading against thousands of teams - high signal, zero admission risk. Appears in no tracked repo, so diarise mid-March yourself.</t>
+          <t>Open to anyone 18+ and enrolled. Algorithmic trading against thousands of teams - high signal, zero admission risk. Appears in no tracked repo, so it needs a mid-March calendar entry.</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Team registration rather than individual selection, so getting in is mostly about hearing in time. That is exactly what this tool cannot do for you: announcements go out on Instagram and listservs first. Cornell CTC in early fall is the most time-critical item on the whole sheet.</t>
+          <t>Team registration rather than individual selection, so getting in is mostly about hearing in time. That is exactly what this tool cannot do: announcements go out on Instagram and listservs first. Cornell CTC in early fall is the most time-critical item on the whole sheet.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Quarterly, so you get four attempts a year and missing one costs almost nothing. Good backtesting practice that produces something concrete to talk about.</t>
+          <t>Quarterly, so there are four attempts a year and missing one costs almost nothing. Good backtesting practice that produces something concrete to talk about.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>No deadline, no selection, no rejection. Worth doing once each in a quiet week purely so the firm's name appears on your resume with something real behind it. Do not spend fall on these at the expense of rank 1-12.</t>
+          <t>No deadline, no selection, no rejection. Worth doing once each in a quiet week purely so the firm's name appears on a resume with something real behind it. Do not spend fall on these at the expense of rank 1-12.</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>No application and no MIT affiliation required - registering is the only gate, so probability is entirely up to you. The catch is timing: the whole season runs during January, which overlaps Stanford winter quarter rather than a break, so treat it as a time commitment decision and not a deadline to hit.</t>
+          <t>No application and no MIT affiliation required - registering is the only gate, so the odds rest entirely on the applicant. The catch is timing: the whole season runs during January, which overlaps Stanford winter quarter rather than a break, so treat it as a time commitment decision and not a deadline to hit.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>A sophomore-specific summer analyst seat at a major firm, which is a narrower and less contested door than the junior programme. He is one year early for the 2027 cycle; the 2028 cycle is his first shot and it closed in late September for 2027, so the window opens earlier than most people expect.</t>
+          <t>A sophomore-specific summer analyst seat at a major firm, which is a narrower and less contested door than the junior programme. A class of 2030 student is one year early for the 2027 cycle; the 2028 cycle is the first realistic one, and it closed in late September for 2027, so the window opens earlier than most people expect.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>THE one for you next year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to you.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - you are US-based.</t>
+          <t>Geographic exclusion - excludes US-based students.</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window. Not you.</t>
+          <t>That is a junior-year window; a first-year does not qualify.</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but you are too early.</t>
+          <t>Highest pay in the industry, but a first-year is too early.</t>
         </is>
       </c>
     </row>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3819,32 +3819,32 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+          <t>NASA JPL internships</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>'approximately 30 degree-seeking credits'</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>https://spcs.stanford.edu/jobs</t>
+          <t>https://www.jpl.nasa.gov/edu/internships/</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+          <t>Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched; check by hand.</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg First Year Insights</t>
+          <t>NASA-Caltech JPL SURF</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3871,1075 +3871,3998 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>First-years (unverified)</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/company/careers/</t>
+          <t>https://www.jpl.nasa.gov/edu/intern/apply/caltech-summer-undergraduate-research-fellowship/</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+          <t>SURF projects hosted at JPL. jpl.nasa.gov returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Princeton summer research programs (non-Princeton undergraduates)</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates (see page)</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>https://undergraduateresearch.princeton.edu/programs/summer-programs</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Princeton's directory of summer research programmes; filterable by eligibility for non-Princeton students and by class year. | 2026-10-01: probed HTTP 200, then HTTP 403 from Cloudflare to the tracker's client minutes later, so it is not watched; check by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>REU SITE: DIAMONDS: Directed, Intensive and Mentored Opportunities in Data Science (Tufts University)</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547822</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547822, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>REU SITE: Research Experience for Undergraduates in Translational Applications of AI to Engineering (REU-TrACE) (Iowa State University)</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447479</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447479, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>REU SITE: Research in Consumer Networking Technologies (University of Missouri-Columbia)</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548100</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548100, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>REU SITE: WAVE SURF: Workforce Advancement in Verification and Emulation of Semiconductor Chips -- Undergraduate Research Fellowships (Texas A&amp;M Engineering Experiment Station)</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548388</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548388, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>REU Site Renewal: Enhancing AI-Driven Insights Within IoT-Enabled Ecosystems (AIoT-Sys) (University of California-Irvine)</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447884</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447884, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>REU Site in Software Engineering (REUSE) at Carnegie Mellon University (Carnegie Mellon University)</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447499</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447499, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: AI Research for Intelligent Systems and Efficiency (University of Arizona)</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548190</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548190, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: AI and Science Summer Lab: advancing AI-enabled scientific discovery across the physical and biological sciences (University of Chicago)</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447314</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447314, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Access to Inquiry in Mathematics Undergraduate Program (University of Wisconsin-Milwaukee)</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447752</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2447752, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Advancing high-performance computing opportunities in undergraduate research at UW-Eau Claire to meet challenges of multidisciplinary computational science (University of Wisconsin-Eau Claire)</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447779</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447779, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Agile AI Research for Safety Critical Systems (Embry-Riddle Aeronautical University)</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548167</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548167, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Algebra, Combinatorics, and Statistics (Texas State University - San Marcos)</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447229</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2447229, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Algorithms in Data Science with Applications (Montana State University)</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548411</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548411, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Applied Artificial Intelligence for Advanced Applications (Worcester Polytechnic Institute)</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349370</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349370, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Applied Computing Research in Unmanned Aerial Systems (Texas A&amp;M University Corpus Christi)</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447596</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447596, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Applied Mathematics in Real World Problems (Florida State University)</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349382</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2349382, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Applied Research in Deep Learning (Missouri State University)</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548161</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548161, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Applied and Computational Mathematics (University of California-Los Angeles)</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548181</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2548181, funded through 11/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Applying Data Science on Energy-efficient Cluster Systems and Applications (The University Corporation, Northridge)</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548509</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548509, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Artificial Intelligence for Computational Creativity (Brown University)</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447190</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447190, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Artificial Intelligence, Security, and Privacy (Northwestern University at Chicago)</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447155</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447155, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: CNS: Sensing and Smart Systems (Florida Atlantic University)</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447437</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447437, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Combinatorics, Algorithms, and AI applied to Real Problems (CAAR) (University of Maryland, College Park)</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447466</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447466, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Computational Methods for Understanding Music, Media and Minds (University of Rochester)</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447607</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447607, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Computational Number Theory (Clemson University)</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349174</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2349174, funded through 10/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Computational Sensing for Human-centered AI (Rochester Institute of Tech)</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445028</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2445028, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Computational and Applied Mathematics Program (Cal Poly Pomona Foundation, Inc.)</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2348984</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2348984, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Computing and Engineering for Safe and Healthy Digital Environment (New York Institute of Technology)</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447577</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447577, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Cryptography, Coding Theory and Quantum Computing at the USF (University of South Florida)</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548160</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548160, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Cyberinfrastructure (CI) Research for Societal Advancement REU (University of Texas at Austin)</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447887</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447887, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Cybersecurity Research of Unmanned Aerial Vehicles (Embry-Riddle Aeronautical University)</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548278</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548278, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Cybersecurity in Emerging Technologies (Mississippi State University)</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447266</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447266, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Data Science Across Disciplines (Marquette University)</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548034</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548034, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Deep Learning for Dynamical Systems in Biological and Physical Sciences (University of Southern Mississippi)</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447675</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2447675, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Digital Forensic Research on Emerging Computing Environments (Virginia Commonwealth University)</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447453</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447453, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: EXERCISE - Explore Emerging Computing in Science and Engineering (Salisbury University)</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447041</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447041, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Engineers for Exploration (University of California-San Diego)</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548467</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548467, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Exploring the FABRIC Research Instrument to Catalyze Multi-disciplinary Research in Networks, Distributed Systems, and Emerging CyberInfrastructure (CI) Applications (University of North Carolina at Chapel Hill)</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447441</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447441, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Extremal Graph Theory and Dynamical Systems at RIT (Rochester Institute of Tech)</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2243938</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, awards 2243938, 2547942, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Frontier Technologies for Biometrics and Authentication (SUNY at Buffalo)</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548357</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548357, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Hands-On Research in Federated Learning Security through Red Team vs. Blue Team Exercises (University of Nevada Las Vegas)</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548041</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548041, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Hardware Security (University of South Florida)</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445849</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2445849, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Home Embodied AI and Robot Technology (HEART) Undergraduate Research Experience (Northeastern University)</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548331</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548331, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Human-AI Interaction and Evaluation in Web and Information Systems (Old Dominion University Research Foundation)</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548125</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548125, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Integrative Challenges in Cybersecurity-Deception, Remediation, and Resilient Systems (SUNY at Albany)</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548335</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548335, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Interdisciplinary Research Experience in Computational Sciences (Louisiana State University)</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447810</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447810, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Knowledge Beyond Language with Vector Embeddings (University of North Texas)</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548192</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548192, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Making Generative Artificial Intelligence Responsible (University of North Texas)</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447834</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447834, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Math REU at Kent State (Kent State University)</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2439984</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2439984, funded through 08/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Mathematical Analysis and Applications (Regents of the University of Michigan - Dearborn)</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548087</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2548087, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Quantum Information Science and Engineering (University of Washington)</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446908</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2446908, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Quantum algorithms and optimization (QAO) (University of Tennessee Knoxville)</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548084</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548084, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: REU@UNO - An REU Site on Security and Artificial Intelligence/Machine Learning for the Internet of Things (University of Nebraska at Omaha)</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447289</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447289, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Research Experience for Undergraduates Intersecting Computing and Evolution (Grand Valley State University)</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547922</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547922, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Research Experiences for Undergraduates in Discrete and Applied Mathematics (Michigan State University)</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2244461</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2244461, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Research Experiences for Undergraduates in Mathematics at Indiana University (Indiana University)</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447563</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2447563, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Research on Prescriptive Analytics for AI-enabled Operations Engineering (University of Missouri-Columbia)</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548110</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548110, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Robotics and Autonomous Systems (University of Southern California)</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447397</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447397, funded through 11/30/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Robots in the Real World (Oregon State University)</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349747</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349747, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: SRAII: Safe and Reliable AI and the Internet (University of Southern California)</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447729</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447729, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Statistical Mathematics and Research Training (SMART) (Marist College)</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447324</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2447324, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Summer Program for Interdisciplinary Research and Education-Emerging Interface Technologies (Iowa State University)</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547899</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547899, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Summer Undergraduate Mathematics Research at Kansas State University (SUMaR at K-State) (Kansas State University)</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548038</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2548038, funded through 07/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Summer Undergraduate Research Experience (SURE) at Illinois Tech (Illinois Institute of Technology)</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548498</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2548498, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Technologies for Community-Driven Design (University of California-San Diego)</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447548</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447548, funded through 06/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: The Face and Mind of Artificial Intelligence (University of Southern California)</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446866</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2446866, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: The future of discovery: training students to build and apply open-source machine learning models and tools (University of Illinois at Urbana-Champaign)</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447843</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447843, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Trustworthy AI (Rochester Institute of Tech)</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447631</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447631, funded through 12/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Trustworthy AI and Security for Intelligent Vehicles and Transportation Systems (University of Alabama Tuscaloosa)</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548476</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548476, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: UT Rio Grande Valley REU Program on Applied Mathematics and Computational and Data Science (AMCADS) (The University of Texas Rio Grande Valley)</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447683</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2447683, funded through 11/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Undergraduate Computer Research in Cybersecurity and AI (UnCoRe-CyberAI) (Oakland University)</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349663</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349663, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Undergraduate Research  in Data Analytics (REU:URDA) (Marshall University Research Corporation)</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447660</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447660, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Undergraduate Research Experience in Edge Intelligence (Board of Regents, NSHE, obo University of Nevada, Reno)</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548395</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548395, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Undergraduate Research Experiences in Artificial Intelligence, Data Analytics, and Mixed Reality for Smart and Connected Health (Texas State University - San Marcos)</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447856</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447856, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>REU Site: Undergraduate Research in the Mathematical Sciences and their Applications (Texas A&amp;M University)</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Most REU sites open Dec-Feb; check the site</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548033</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>NSF REU Site, Mathematical Sciences, award 2548033, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>UC Davis GREAT program</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduates (see page)</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>https://great.ucdavis.edu/</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>Global Research Experience in Advanced Technologies. Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>'approximately 30 degree-seeking credits'</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>https://spcs.stanford.edu/jobs</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg First Year Insights</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>First-years (unverified)</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="F173" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not by individual application.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
         <is>
           <t>APPLIED - too early</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>Local (St. Louis)</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Fall-winter</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F174" s="4" t="inlineStr">
         <is>
           <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>Edward Jones Internship</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>Local (St. Louis)</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>Juniors</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>Local (St. Louis)</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>Juniors</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>https://www.stifel.com/careers/internships</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G176" s="3" t="inlineStr">
         <is>
           <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Winter-spring</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>Rising sophomore+</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>https://www.deshawresearch.com/stemfellowship/</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>HRT Sophomore Winternship</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>2nd year</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F178" s="4" t="inlineStr">
         <is>
           <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>January, 2-4 weeks, Python/C++.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
         <is>
           <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F179" s="4" t="inlineStr">
         <is>
           <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="G179" s="3" t="inlineStr">
         <is>
           <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>2nd year</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F180" s="4" t="inlineStr">
         <is>
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
         <is>
           <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>2nd year</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>2nd year</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+      <c r="G182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>2nd year</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F183" s="4" t="inlineStr">
         <is>
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+      <c r="G183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
         <is>
           <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>2nd year</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F184" s="4" t="inlineStr">
         <is>
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
+      <c r="G184" s="3" t="inlineStr">
         <is>
           <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
         <is>
           <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
         <is>
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>Fall</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>3rd year of 4-year degree</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G185" s="3" t="inlineStr">
         <is>
           <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>Stanford-only</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>Priority to juniors</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G186" s="3" t="inlineStr">
         <is>
           <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>LATER</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>Wells Fargo Sophomore Experience</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Sophomores</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="G187" s="3" t="inlineStr">
         <is>
           <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B188" s="3" t="inlineStr">
         <is>
           <t>Limex Challenge</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F188" s="4" t="inlineStr">
         <is>
           <t>https://challenges.limex.com/</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
+      <c r="G188" s="3" t="inlineStr">
         <is>
           <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
         <is>
           <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="F189" s="4" t="inlineStr">
         <is>
           <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G189" s="3" t="inlineStr">
         <is>
           <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="F190" s="4" t="inlineStr">
         <is>
           <t>https://quantegies.com/</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr">
+      <c r="G190" s="3" t="inlineStr">
         <is>
           <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
         <is>
           <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
         <is>
           <t>CMF Select New York 2026</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>https://global-cmf.com/cmfselectnewyork2026</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G192" s="3" t="inlineStr">
         <is>
           <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F193" s="4" t="inlineStr">
         <is>
           <t>https://fima.partners/</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>FutureAlpha / QuantStrats 2026</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="F194" s="4" t="inlineStr">
         <is>
           <t>https://www.alphaevents.com/events-futurealphaglobal</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
+      <c r="G194" s="3" t="inlineStr">
         <is>
           <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="6" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
         <is>
           <t>QWAFAFEW / QWAFAxNEW chapters</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>https://www.qwafafew.org/</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G195" s="3" t="inlineStr">
         <is>
           <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>Tapia Conference</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>Open, but serves underrepresented groups in computing</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="F196" s="4" t="inlineStr">
         <is>
           <t>https://tapiaconference.cmd-it.org/</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G196" s="3" t="inlineStr">
         <is>
           <t>Open to attend; low relative value for a first-year.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>LOW VALUE</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
         <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F197" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>First-year/sophomore</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="F198" s="4" t="inlineStr">
         <is>
           <t>https://careerhub.students.duke.edu/</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>Public list of early insight programs by target year.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>MLH hackathon season calendar</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Weekly all year</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>Any undergrad year</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>https://www.mlh.com/seasons/2027/events</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>Verified 2026-09-30: MLH's official season calendar (e.g. Gator Quant Hacks, MHacks, Oct 2026). Too high-churn for page_text; treat as a manual/calendar pointer.</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
         <is>
           <t>Yale 'Gorick's List' for quant trading</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="F200" s="4" t="inlineStr">
         <is>
           <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="G200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="F201" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G122"/>
+  <autoFilter ref="A1:G201"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -5059,6 +7982,85 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId197"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8686,7 +11688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8732,17 +11734,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Already watched by akunacapital-greenhouse</t>
+          <t>Already watched by ai2-internships</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Akuna Trading Sneak Peek Week</t>
+          <t>Ai2 internships (Allen Institute for AI)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -8752,12 +11754,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://akunacapital.com/careers</t>
+          <t>https://allenai.org/internships</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Options crash course: risk management, game theory, decision making.</t>
+          <t>Research internships are open to undergraduates in AI-related fields year-round; engineering internships are for juniors, seniors and graduate students.</t>
         </is>
       </c>
     </row>
@@ -8769,7 +11771,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Akuna Virtual Quant Trading Challenge</t>
+          <t>Akuna Trading Sneak Peek Week</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -8777,36 +11779,36 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://akunacapital.com/careers/job/7986086/?gh_jid=7986086</t>
+          <t>https://akunacapital.com/careers</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Write market-making bots against an open exchange.</t>
+          <t>Options crash course: risk management, game theory, decision making.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Already watched by berkeley-trading-competition</t>
+          <t>Already watched by akunacapital-greenhouse</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Berkeley Trading Competition</t>
+          <t>Akuna Virtual Quant Trading Challenge</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8816,125 +11818,125 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
+          <t>https://akunacapital.com/careers/job/7986086/?gh_jid=7986086</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
+          <t>Write market-making bots against an open exchange.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bny-pre-internship</t>
+          <t>Already watched by berkeley-superb</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BNY Freshman Jumpstart</t>
+          <t>Berkeley SUPERB-AI4E REU</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
+          <t>https://eecs.berkeley.edu/resources/undergrads/undergraduate-research/superb/</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
+          <t>NSF REU site in EECS at UC Berkeley. Page states: US citizens or permanent residents who are rising juniors or seniors with some upper-division EECS coursework, so a first-year is not yet eligible.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bofa-campus-events</t>
+          <t>Already watched by berkeley-trading-competition</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Bank of America campus events (Early Insights)</t>
+          <t>Berkeley Trading Competition</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
+          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bridgewater-students</t>
+          <t>Already watched by bny-pre-internship</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Investment Immersion Program</t>
+          <t>BNY Freshman Jumpstart</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
+          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Already watched by capitalone-early-career</t>
+          <t>Already watched by bofa-campus-events</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Capital One Analyst / Tech / Product Summits</t>
+          <t>Bank of America campus events (Early Insights)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -8944,61 +11946,61 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
+          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
+          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Already watched by citi-pre-internships</t>
+          <t>Already watched by bridgewater-students</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Citi Freshman Discovery</t>
+          <t>Bridgewater Investment Immersion Program</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
+          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by comap-mcm</t>
+          <t>Already watched by caltech-surf</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>COMAP MCM/ICM</t>
+          <t>Caltech SURF</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -9008,157 +12010,157 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/undergraduate/contests/</t>
+          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
+          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cornell-trading-competition</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cra-dreu</t>
+          <t>Already watched by citi-pre-internships</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CRA DREU</t>
+          <t>Citi Freshman Discovery</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://cra.org/cra-wp/dreu/</t>
+          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
+          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cs-social-good-fellowships</t>
+          <t>Already watched by cmu-riss</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CS+Social Good Summer Fellowships</t>
+          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
+          <t>https://riss.ri.cmu.edu/</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
+          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by curis</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by datasurf</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Stanford DataSURF (formerly SURP-Stats)</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -9168,125 +12170,125 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cs-social-good-fellowships</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw campus site</t>
+          <t>CS+Social Good Summer Fellowships</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/</t>
+          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
+          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dimacs-reu</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>DIMACS REU</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://dimacs.rutgers.edu/reu-main</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dukequant-competition</t>
+          <t>Already watched by datasurf</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>Stanford DataSURF (formerly SURP-Stats)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -9296,157 +12298,157 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by evercore-campus</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Evercore student events</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by futureforce-launchpad</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.duke.edu/</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -9456,56 +12458,56 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icerm-summer</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Summer@ICERM</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://icerm.brown.edu/summerug/</t>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icpc-pnw</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -9513,36 +12515,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -9552,120 +12554,120 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-prosperity</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-preview</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Preview</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9673,31 +12675,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9705,63 +12707,63 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>INVITE</t>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://prosperity.imc.com/</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by ipam-rips</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>IPAM RIPS (UCLA)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
+          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9769,27 +12771,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>INVITE</t>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -9804,116 +12810,120 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jefferies-campus</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Jefferies campus opportunities</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-career-edyou</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>JPMorganChase Career.edYOU Academy</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-fellowship</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>JPMC Fellowship Program</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jumptrading-greenhouse</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading Campus Jump Early Access</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -9921,31 +12931,27 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.jumptrading.com/hr/students-new-grads</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kkr-greenhouse</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>KKR Scholars Program</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9953,36 +12959,32 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kleinerperkins-fellows-ashby</t>
+          <t>Already watched by jefferies-campus</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Kleiner Perkins Engineering Fellows</t>
+          <t>Jefferies campus opportunities</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -9992,116 +12994,120 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://www.kleinerperkins.com/fellows/</t>
+          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by jhuapl-internships</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>Johns Hopkins APL internships</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
+          <t>https://www.jhuapl.edu/careers/internships</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mathprograms-listing</t>
+          <t>Already watched by jpmc-career-edyou</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MathPrograms.org programme listing</t>
+          <t>JPMorganChase Career.edYOU Academy</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://www.mathprograms.org/db/program</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
+          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Already watched by meta-hacker-cup</t>
+          <t>Already watched by jpmc-fellowship</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Meta Hacker Cup</t>
+          <t>JPMC Fellowship Program</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Already watched by millennium-eightfold</t>
+          <t>Already watched by jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Meet Millennium</t>
+          <t>Jump Trading Campus Jump Early Access</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -10109,95 +13115,95 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
+          <t>https://www.jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
+          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by kkr-greenhouse</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>KKR Scholars Program</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-trading-competition</t>
+          <t>Already watched by kleinerperkins-fellows-ashby</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Traders@MIT Trading Competition</t>
+          <t>Kleiner Perkins Engineering Fellows</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://traders.mit.edu/competition</t>
+          <t>https://www.kleinerperkins.com/fellows/</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
+          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nist-surf</t>
+          <t>Already watched by lanl-students</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>NIST SURF</t>
+          <t>LANL student internships (Los Alamos National Laboratory)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -10205,100 +13211,96 @@
           <t>Research / math</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/surf</t>
+          <t>https://www.lanl.gov/engage/collaboration/internships</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
+          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by llnl-students</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
-        </is>
-      </c>
+          <t>https://github.com/LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by mathprograms-listing</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>MathPrograms.org programme listing</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -10308,29 +13310,29 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://www.mathprograms.org/db/program</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by meta-hacker-cup</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Meta Hacker Cup</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -10340,80 +13342,88 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr"/>
+          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ramp-ashby</t>
+          <t>Already watched by millennium-eightfold</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Ramp Emerging Talent</t>
+          <t>Meet Millennium</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://ramp.com/emerging-talent</t>
+          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
+          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Already watched by reufinder-freshmen</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr"/>
+          <t>https://battlecode.org/</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Already watched by scudem</t>
+          <t>Already watched by mit-trading-competition</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>SCUDEM XI 2026</t>
+          <t>Traders@MIT Trading Competition</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -10428,29 +13438,29 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/scudem/index.html</t>
+          <t>https://traders.mit.edu/competition</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Already watched by seo-tech</t>
+          <t>Already watched by mitll-students</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>SEO Tech Developer + First-Year Academy</t>
+          <t>MIT Lincoln Laboratory student opportunities</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -10460,24 +13470,24 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://tech.seo-usa.org/</t>
+          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
+          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sfi-ucr</t>
+          <t>Already watched by nist-surf</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>SFI Undergraduate Complexity Research</t>
+          <t>NIST SURF</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -10485,100 +13495,100 @@
           <t>Research / math</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
+          <t>https://www.nist.gov/surf</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
+          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by nsa-students</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>NSA student programs</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://www.intelligencecareers.gov/nsa/students</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Already watched by smart-scholarship</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>SMART Scholarship</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.smartscholarship.org/smart</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -10588,61 +13598,61 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Already watched by surim-apply</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Already watched by treehacks</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>TreeHacks</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -10652,61 +13662,57 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://treehacks.com/</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Already watched by twosigma-campus</t>
+          <t>Already watched by purdue-srop</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma New Seekers Summit</t>
+          <t>Purdue Summer Research Opportunities Program (SROP)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/new-seekers-summit/</t>
+          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
+          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Already watched by uchicago-trading-competition</t>
+          <t>Already watched by ramp-ashby</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>UChicago Trading Competition</t>
+          <t>Ramp Emerging Talent</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -10716,88 +13722,84 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://tradingcompetition.uchicago.edu/</t>
+          <t>https://ramp.com/emerging-talent</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
+          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by reufinder-freshmen</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>USE WEEKLY</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
-        </is>
-      </c>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Already watched by worldquant-iqc</t>
+          <t>Already watched by sandia-students</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>Sandia National Laboratories student internships</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>Undergraduate and graduate internships across Sandia's sites.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Already watched by yutc</t>
+          <t>Already watched by scudem</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Yale Undergraduate Trading Competition</t>
+          <t>SCUDEM XI 2026</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10812,248 +13814,248 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>https://www.yale.edu/</t>
+          <t>https://www.contest.comap.com/scudem/index.html</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
+          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by seo-tech</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>SEO Tech Developer + First-Year Academy</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://tech.seo-usa.org/</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by sfi-ucr</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>SFI Undergraduate Complexity Research</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
+          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by smart-scholarship</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>SMART Scholarship</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.smartscholarship.org/smart</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by surim-apply</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by treehacks</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>TreeHacks</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://treehacks.com/</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by twosigma-campus</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>Two Sigma New Seekers Summit</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -11061,127 +14063,127 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
+          <t>https://www.twosigma.com/new-seekers-summit/</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by uchicago-trading-competition</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>UChicago Trading Competition</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://tradingcompetition.uchicago.edu/</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by usc-ict-summer</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>USC ICT Summer Research Program</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://ict.usc.edu/careers/internships/summer-research-program-application/</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>USC Institute for Creative Technologies summer research programme.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by worldquant-iqc</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -11189,51 +14191,51 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yutc</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>Yale Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://www.yale.edu/</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - excludes US-based students.</t>
+          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
         </is>
       </c>
     </row>
@@ -11245,12 +14247,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -11260,10 +14262,14 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr"/>
+          <t>https://www.bofa.com/</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -11273,7 +14279,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -11288,12 +14294,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -11305,7 +14311,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -11320,12 +14326,12 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window; a first-year does not qualify.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -11337,7 +14343,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -11352,12 +14358,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -11369,12 +14375,12 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -11384,10 +14390,14 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr"/>
+          <t>https://www.codingitforward.com/fellowship</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -11397,7 +14407,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -11412,12 +14422,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +14439,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -11444,12 +14454,12 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -11461,7 +14471,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -11476,10 +14486,14 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr"/>
+          <t>https://campus.deshaw.com/additional-experiences</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -11489,7 +14503,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -11504,12 +14518,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -11521,12 +14535,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -11536,12 +14550,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+          <t>https://databento.com/</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -11553,7 +14567,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -11568,12 +14582,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://en.tmtpost.com/post/7752441</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -11585,12 +14599,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -11598,14 +14612,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -11617,7 +14631,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -11632,12 +14646,12 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Geographic exclusion - excludes US-based students.</t>
         </is>
       </c>
     </row>
@@ -11649,7 +14663,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -11664,14 +14678,10 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>Highest pay in the industry, but a first-year is too early.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -11681,7 +14691,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -11696,12 +14706,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -11713,12 +14723,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -11728,12 +14738,12 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>That is a junior-year window; a first-year does not qualify.</t>
         </is>
       </c>
     </row>
@@ -11745,12 +14755,12 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -11758,12 +14768,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -11773,7 +14787,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -11788,14 +14802,10 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -11805,7 +14815,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -11820,10 +14830,14 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>For women, transgender and gender-expansive people.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -11833,7 +14847,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -11848,12 +14862,12 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>6-week remote mentorship on open-source projects.</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
         </is>
       </c>
     </row>
@@ -11865,7 +14879,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -11880,7 +14894,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr"/>
@@ -11893,7 +14907,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -11908,10 +14922,14 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Women / trans / gender-expansive students.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -11921,12 +14939,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -11936,10 +14954,14 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr"/>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -11949,7 +14971,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -11964,12 +14986,12 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
         </is>
       </c>
     </row>
@@ -11981,12 +15003,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -11994,14 +15016,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
         </is>
       </c>
     </row>
@@ -12013,12 +15035,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
@@ -12028,7 +15050,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -12040,37 +15062,433 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Optiver Quantitative Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Highest pay in the industry, but a first-year is too early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Optiver regional recruitment events (non-US)</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/recruitment-events/</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>PEAK6 Trading Bootcamp</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>https://peak6.com/campus/</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Palantir Path</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Point72 Academy</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma College Mentor Connect</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Virtu Financial Women's Winternship</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F107"/>
+  <autoFilter ref="A1:F120"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -12162,20 +15580,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11688,7 +11688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11990,108 +11990,108 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by caltech-surf</t>
+          <t>Already watched by builtin-data-analytics</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Caltech SURF</t>
+          <t>Built In data and analytics internships</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
+          <t>https://builtin.com/jobs/data-analytics/internship</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
+          <t>Front page of Built In's data and analytics internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by capitalone-early-career</t>
+          <t>Already watched by builtin-dev-engineering</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Capital One Analyst / Tech / Product Summits</t>
+          <t>Built In software engineering internships</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
+          <t>https://builtin.com/jobs/dev-engineering/internship</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
+          <t>Front page of Built In's software engineering internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by citi-pre-internships</t>
+          <t>Already watched by builtin-finance</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Citi Freshman Discovery</t>
+          <t>Built In finance internships</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
+          <t>https://builtin.com/jobs/finance/internship</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
+          <t>Front page of Built In's finance internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cmu-riss</t>
+          <t>Already watched by caltech-surf</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
+          <t>Caltech SURF</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -12106,29 +12106,29 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://riss.ri.cmu.edu/</t>
+          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
+          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by comap-mcm</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>COMAP MCM/ICM</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -12138,29 +12138,29 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/undergraduate/contests/</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cornell-trading-competition</t>
+          <t>Already watched by citi-pre-internships</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>Citi Freshman Discovery</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -12170,24 +12170,24 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cra-dreu</t>
+          <t>Already watched by cmu-riss</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>CRA DREU</t>
+          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -12202,61 +12202,61 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://cra.org/cra-wp/dreu/</t>
+          <t>https://riss.ri.cmu.edu/</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
+          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cs-social-good-fellowships</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CS+Social Good Summer Fellowships</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by curis</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -12266,189 +12266,189 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by datasurf</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Stanford DataSURF (formerly SURP-Stats)</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by cs-social-good-fellowships</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>CS+Social Good Summer Fellowships</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw campus site</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dimacs-reu</t>
+          <t>Already watched by datasurf</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>DIMACS REU</t>
+          <t>Stanford DataSURF (formerly SURP-Stats)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://dimacs.rutgers.edu/reu-main</t>
+          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
+          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dukequant-competition</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by evercore-campus</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Evercore student events</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -12458,29 +12458,29 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by futureforce-launchpad</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -12490,24 +12490,24 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -12515,31 +12515,31 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://www.duke.edu/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -12554,61 +12554,61 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icerm-summer</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Summer@ICERM</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -12618,61 +12618,61 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://icerm.brown.edu/summerug/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icpc-pnw</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -12682,88 +12682,88 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-prosperity</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ipam-rips</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>IPAM RIPS (UCLA)</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12771,31 +12771,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-preview</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Preview</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12803,63 +12803,63 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
+          <t>https://prosperity.imc.com/</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by ipam-rips</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>IPAM RIPS (UCLA)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -12867,31 +12867,31 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>INVITE</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12899,19 +12899,19 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
+          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12931,17 +12931,21 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>INVITE</t>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -12951,7 +12955,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12961,7 +12965,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -12969,209 +12973,205 @@
           <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jefferies-campus</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Jefferies campus opportunities</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jhuapl-internships</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL internships</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.jhuapl.edu/careers/internships</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-career-edyou</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>JPMorganChase Career.edYOU Academy</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-fellowship</t>
+          <t>Already watched by jefferies-campus</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>JPMC Fellowship Program</t>
+          <t>Jefferies campus opportunities</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
+          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jumptrading-greenhouse</t>
+          <t>Already watched by jhuapl-internships</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading Campus Jump Early Access</t>
+          <t>Johns Hopkins APL internships</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.jumptrading.com/hr/students-new-grads</t>
+          <t>https://www.jhuapl.edu/careers/internships</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
+          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kkr-greenhouse</t>
+          <t>Already watched by jpmc-career-edyou</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>KKR Scholars Program</t>
+          <t>JPMorganChase Career.edYOU Academy</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
+          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kleinerperkins-fellows-ashby</t>
+          <t>Already watched by jpmc-fellowship</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Kleiner Perkins Engineering Fellows</t>
+          <t>JPMC Fellowship Program</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -13179,123 +13179,127 @@
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.kleinerperkins.com/fellows/</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
+          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Already watched by lanl-students</t>
+          <t>Already watched by jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>LANL student internships (Los Alamos National Laboratory)</t>
+          <t>Jump Trading Campus Jump Early Access</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.lanl.gov/engage/collaboration/internships</t>
+          <t>https://www.jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
+          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Already watched by llnl-students</t>
+          <t>Already watched by kkr-greenhouse</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
+          <t>KKR Scholars Program</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
+          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
+          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by kleinerperkins-fellows-ashby</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>Kleiner Perkins Engineering Fellows</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr"/>
+          <t>https://www.kleinerperkins.com/fellows/</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mathprograms-listing</t>
+          <t>Already watched by lanl-students</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MathPrograms.org programme listing</t>
+          <t>LANL student internships (Los Alamos National Laboratory)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -13310,29 +13314,29 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://www.mathprograms.org/db/program</t>
+          <t>https://www.lanl.gov/engage/collaboration/internships</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
+          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Already watched by meta-hacker-cup</t>
+          <t>Already watched by llnl-students</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Meta Hacker Cup</t>
+          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -13342,61 +13346,57 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Already watched by millennium-eightfold</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Meet Millennium</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
-        </is>
-      </c>
+          <t>https://github.com/LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by mathprograms-listing</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>MathPrograms.org programme listing</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -13406,24 +13406,24 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://www.mathprograms.org/db/program</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-trading-competition</t>
+          <t>Already watched by meta-hacker-cup</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Traders@MIT Trading Competition</t>
+          <t>Meta Hacker Cup</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -13431,36 +13431,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>https://traders.mit.edu/competition</t>
+          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
+          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mitll-students</t>
+          <t>Already watched by millennium-eightfold</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>MIT Lincoln Laboratory student opportunities</t>
+          <t>Meet Millennium</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -13470,157 +13470,157 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
+          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
+          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nist-surf</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>NIST SURF</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/surf</t>
+          <t>https://battlecode.org/</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nsa-students</t>
+          <t>Already watched by mit-trading-competition</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>NSA student programs</t>
+          <t>Traders@MIT Trading Competition</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://www.intelligencecareers.gov/nsa/students</t>
+          <t>https://traders.mit.edu/competition</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by mitll-students</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>MIT Lincoln Laboratory student opportunities</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by nist-surf</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>NIST SURF</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.nist.gov/surf</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by nsa-students</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>NSA student programs</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -13630,57 +13630,61 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://www.intelligencecareers.gov/nsa/students</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr"/>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Already watched by purdue-srop</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Purdue Summer Research Opportunities Program (SROP)</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -13690,71 +13694,71 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ramp-ashby</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Ramp Emerging Talent</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://ramp.com/emerging-talent</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Already watched by reufinder-freshmen</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
@@ -13762,12 +13766,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sandia-students</t>
+          <t>Already watched by purdue-srop</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Sandia National Laboratories student internships</t>
+          <t>Purdue Summer Research Opportunities Program (SROP)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -13782,29 +13786,29 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
+          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate and graduate internships across Sandia's sites.</t>
+          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Already watched by scudem</t>
+          <t>Already watched by ramp-ashby</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>SCUDEM XI 2026</t>
+          <t>Ramp Emerging Talent</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -13814,56 +13818,52 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/scudem/index.html</t>
+          <t>https://ramp.com/emerging-talent</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
+          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Already watched by seo-tech</t>
+          <t>Already watched by reufinder-freshmen</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>SEO Tech Developer + First-Year Academy</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>https://tech.seo-usa.org/</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
-        </is>
-      </c>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sfi-ucr</t>
+          <t>Already watched by sandia-students</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>SFI Undergraduate Complexity Research</t>
+          <t>Sandia National Laboratories student internships</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -13878,61 +13878,61 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
+          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
+          <t>Undergraduate and graduate internships across Sandia's sites.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by scudem</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>SCUDEM XI 2026</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
+          <t>https://www.contest.comap.com/scudem/index.html</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
+          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Already watched by smart-scholarship</t>
+          <t>Already watched by seo-tech</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>SMART Scholarship</t>
+          <t>SEO Tech Developer + First-Year Academy</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -13942,29 +13942,29 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>https://www.smartscholarship.org/smart</t>
+          <t>https://tech.seo-usa.org/</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
+          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by sfi-ucr</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>SFI Undergraduate Complexity Research</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -13974,61 +13974,61 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Already watched by surim-apply</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Already watched by treehacks</t>
+          <t>Already watched by smart-scholarship</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>TreeHacks</t>
+          <t>SMART Scholarship</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -14038,61 +14038,61 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>https://treehacks.com/</t>
+          <t>https://www.smartscholarship.org/smart</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
+          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Already watched by twosigma-campus</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma New Seekers Summit</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/new-seekers-summit/</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Already watched by uchicago-trading-competition</t>
+          <t>Already watched by surim-apply</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>UChicago Trading Competition</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -14102,93 +14102,93 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>https://tradingcompetition.uchicago.edu/</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by treehacks</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>TreeHacks</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://treehacks.com/</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Already watched by usc-ict-summer</t>
+          <t>Already watched by twosigma-campus</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>USC ICT Summer Research Program</t>
+          <t>Two Sigma New Seekers Summit</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>https://ict.usc.edu/careers/internships/summer-research-program-application/</t>
+          <t>https://www.twosigma.com/new-seekers-summit/</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>USC Institute for Creative Technologies summer research programme.</t>
+          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Already watched by worldquant-iqc</t>
+          <t>Already watched by uchicago-trading-competition</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>UChicago Trading Competition</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -14198,88 +14198,88 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://tradingcompetition.uchicago.edu/</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Already watched by yutc</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Yale Undergraduate Trading Competition</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>https://www.yale.edu/</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by usc-ict-summer</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>USC ICT Summer Research Program</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://ict.usc.edu/careers/internships/summer-research-program-application/</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>USC Institute for Creative Technologies summer research programme.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by worldquant-iqc</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -14287,51 +14287,51 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yutc</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Yale Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://www.yale.edu/</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
         </is>
       </c>
     </row>
@@ -14343,12 +14343,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -14358,12 +14358,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://www.bofa.com/</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -14375,12 +14375,12 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -14407,12 +14407,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -14471,12 +14471,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -14486,12 +14486,12 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
+          <t>https://www.codingitforward.com/fellowship</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -14567,12 +14567,12 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://campus.deshaw.com/additional-experiences</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -14631,12 +14631,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://databento.com/</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - excludes US-based students.</t>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -14663,12 +14663,12 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -14678,10 +14678,14 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr"/>
+          <t>https://en.tmtpost.com/post/7752441</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -14691,7 +14695,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -14706,12 +14710,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -14723,12 +14727,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -14738,12 +14742,12 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window; a first-year does not qualify.</t>
+          <t>Geographic exclusion - excludes US-based students.</t>
         </is>
       </c>
     </row>
@@ -14755,7 +14759,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -14770,14 +14774,10 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
-        </is>
-      </c>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -14802,10 +14802,14 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr"/>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -14815,12 +14819,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -14830,12 +14834,12 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>That is a junior-year window; a first-year does not qualify.</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14851,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -14862,12 +14866,12 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14883,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -14907,7 +14911,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -14922,12 +14926,12 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>For women, transgender and gender-expansive people.</t>
         </is>
       </c>
     </row>
@@ -14939,12 +14943,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -14954,12 +14958,12 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
         </is>
       </c>
     </row>
@@ -14971,12 +14975,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -14986,14 +14990,10 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -15016,14 +15016,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+          <t>Women / trans / gender-expansive students.</t>
         </is>
       </c>
     </row>
@@ -15035,12 +15035,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://kaxanuk.mx/kn-hack</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+          <t>https://pokerbots.org/</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but a first-year is too early.</t>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
         </is>
       </c>
     </row>
@@ -15099,12 +15099,12 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -15112,14 +15112,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>https://optiver.com/recruitment-events/</t>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
         </is>
       </c>
     </row>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -15146,12 +15146,12 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -15163,12 +15163,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>Optiver Quantitative Intern Summer 2027</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
@@ -15176,12 +15176,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Highest pay in the industry, but a first-year is too early.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -15191,7 +15195,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>Optiver regional recruitment events (non-US)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -15206,12 +15210,12 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
+          <t>https://optiver.com/recruitment-events/</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15227,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>PEAK6 Trading Bootcamp</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -15238,10 +15242,14 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr"/>
+          <t>https://peak6.com/campus/</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -15251,12 +15259,12 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Palantir Path</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -15264,16 +15272,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>6-week remote mentorship on open-source projects.</t>
-        </is>
-      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -15283,7 +15287,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>Point72 Academy</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -15298,10 +15302,14 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr"/>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -15311,7 +15319,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -15326,7 +15334,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
@@ -15339,7 +15347,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Two Sigma College Mentor Connect</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -15354,10 +15362,14 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr"/>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -15367,12 +15379,12 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -15382,14 +15394,10 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -15399,12 +15407,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Two Sigma PhD Fellowship</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -15414,14 +15422,10 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -15431,12 +15435,12 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>Virtu Financial Women's Winternship</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -15446,49 +15450,141 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
-        </is>
-      </c>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F120"/>
+  <autoFilter ref="A1:F123"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -15593,13 +15689,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId113"/>
@@ -15607,6 +15703,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Hull Tactical Market Prediction (Kaggle)</t>
+          <t>Hack for Humanity (Santa Clara University)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Rolling - see Kaggle</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Anyone with an account</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
+          <t>https://hackforhumanity.io/</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
+          <t>Not verified: on 2026-10-08 the site returned HTTP 429 with a Vercel Security Checkpoint page to the tracker's client, so neither eligibility nor travel terms could be read.</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>IICPC Codefest 2026</t>
+          <t>HackMIT</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026 cycle: applications due Jul 4, decisions early Aug; event in the fall</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>College students (check site)</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://codefest.iicpc.com/</t>
+          <t>https://hackmit.org/</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
+          <t>Verified 2026-10-08 (rendered page): 'Everyone who attends HackMIT is eligible for travel reimbursement'; 'travel stipends will be available for accepted hackers'; documentation must follow the travel policy and a project must be submitted to receive reimbursement.</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
+          <t>Hull Tactical Market Prediction (Kaggle)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
+          <t>https://www.kaggle.com/competitions/hull-tactical-market-prediction</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
+          <t>A quant-sponsored Kaggle competition, distinct from the Jane Street one already tracked. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry, no class-year or identity gate.</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Quantiacs Crypto Contest</t>
+          <t>IICPC Codefest 2026</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>2026 contest cycles</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://quantiacs.com/</t>
+          <t>https://codefest.iicpc.com/</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
+          <t>Coding competition listed among quant events. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Almost no detail published and the page is nearly empty; low confidence this is worth time.</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>The Deck Game</t>
+          <t>MITSUI &amp; Co. Commodity Prediction Challenge (Kaggle)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling - see Kaggle</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Anyone with an account</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>https://thedeckgame.com/</t>
+          <t>https://www.kaggle.com/competitions/mitsui-commodity-prediction-challenge</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
+          <t>Commodity price prediction on Kaggle. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry.</t>
         </is>
       </c>
     </row>
@@ -3362,32 +3362,32 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Goldman Sachs Possibilities Summits</t>
+          <t>Quantiacs Crypto Contest</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>2026 contest cycles</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Varies by summit</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://higher.gs.com/campus</t>
+          <t>https://quantiacs.com/</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26. Restricted to specific underrepresented groups - confirm by hand. higher.gs.com/campus is a JavaScript shell (29 chars) and the programme URLs guessed from lists 404.</t>
+          <t>Algorithmic trading contest platform running periodic crypto contests. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Open entry; treat as practice rather than a credential.</t>
         </is>
       </c>
     </row>
@@ -3399,32 +3399,32 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Code for Good</t>
+          <t>The Deck Game</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>VERIFY - historically broader across years</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://thedeckgame.com/</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
+          <t>Landing page renders via JS and exposes ~28 characters of text; its sitemap lists only / and /about, so there is almost nothing to diff even with a browser. Manual check only - see the Manual Watch sheet.</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Quant Invitational</t>
+          <t>Goldman Sachs Possibilities Summits</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate</t>
+          <t>Varies by summit</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
+          <t>https://higher.gs.com/campus</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Listed on their programs page; class-year requirement not published.</t>
+          <t>Found 2026-09-26. Restricted to specific underrepresented groups - confirm by hand. higher.gs.com/campus is a JavaScript shell (29 chars) and the programme URLs guessed from lists 404.</t>
         </is>
       </c>
     </row>
@@ -3473,30 +3473,34 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Cubist Quant Academy</t>
+          <t>JPMorgan Code for Good</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>VERIFY - historically broader across years</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>https://careers.point72.com/</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr"/>
+          <t>https://careers.jpmorgan.com/</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Some Data for Good editions have been HBCU-specific. Check the specific posting.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -3506,7 +3510,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Discover DRW</t>
+          <t>Citadel Securities Quant Invitational</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3521,17 +3525,17 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED for 1st year</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://drw.com/work-at-drw/category/campus</t>
+          <t>https://www.citadelsecurities.com/careers/markets-and-trading/</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2-day quant trading immersion. Verify class year directly.</t>
+          <t>Listed on their programs page; class-year requirement not published.</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3547,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Five Rings Winternship</t>
+          <t>Cubist Quant Academy</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3553,24 +3557,20 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED for 1st year</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://fiverings.com/careers</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
-        </is>
-      </c>
+          <t>https://careers.point72.com/</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>G-Research Spring into Quant Finance 2026</t>
+          <t>Discover DRW</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -3590,22 +3590,22 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Students - verify</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+          <t>https://drw.com/work-at-drw/category/campus</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
+          <t>2-day quant trading immersion. Verify class year directly.</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Campus - Global Programs board</t>
+          <t>Five Rings Winternship</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3627,22 +3627,22 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1st-4th year, varies by programme</t>
+          <t>UNCONFIRMED for 1st year</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+          <t>https://fiverings.com/careers</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+          <t>4 weeks NY: projects, classroom, strategy games, mock trading.</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Optiver Insight Days</t>
+          <t>G-Research Spring into Quant Finance 2026</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3664,20 +3664,24 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>Students - verify</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr"/>
+          <t>https://www.gresearch.com/events/spring-into-quant-finance-2026</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>G-Research student event. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. G-Research is London-based, so confirm whether there is a US or virtual track before counting on it. Not probed.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -3687,7 +3691,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Optiver Market Making Competition</t>
+          <t>Morgan Stanley Campus - Global Programs board</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3697,20 +3701,24 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Rolling by programme; the 2027 summer cycle closes Sep-Oct 2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Not published</t>
+          <t>1st-4th year, varies by programme</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Morgan Stanley's whole campus board, on Talentlink (morganstanley.tal.net) - 125 programmes, 31 in the United States, with business-unit facets including Quantitative Finance (8), Technology (12) and Investment Management (14). Found 2026-09-18 while resolving a pasted posting link. IMPORTANT, the obvious URL is the wrong one: www.morganstanley.com/careers/career-opportunities-search sits behind an Akamai WAF that resets the connection for paths.USER_AGENT and returns HTTP 200 with 134KB to a spoofed Chrome string - same machine, same IP, so the block is User-Agent based and it is the Citadel case, reachable only by misrepresenting the client. Do not re-point a source at it. Morgan Stanley's OTHER board, morganstanley.eightfold.ai, is reachable honestly via /api/pcsx/search but is deliberately NOT watched: it carries 1,327 corporate roles, caps page size at 10 (about 133 requests a day), and a query for 'Sophomore' or 'Freshman' returns zero - the campus programmes are not on it. Probed 2026-09-18: 9,660 chars of visible text, ratio 0.063, allowed by robots.txt (crawl-delay 10; the named-bot block covers ClaudeBot/GPTBot, not this tracker's own UA), no redirect. RETIRED 2026-09-21: this board is no longer watched. It failed on consecutive runs returning only ~350 characters because the Talentlink page renders its listings in JavaScript, and there is no honest route to the same content -- www.morganstanley.com refuses this tracker's User-Agent (the Citadel case) and morganstanley.eightfold.ai does not carry the campus programmes. source_id cleared, so this row is the owner's to check by hand.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3720,7 +3728,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Optiver Trading Day</t>
+          <t>Optiver Insight Days</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3753,7 +3761,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>SIG Insight Week</t>
+          <t>Optiver Market Making Competition</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr"/>
@@ -3786,7 +3794,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Financial Modeling Challenge</t>
+          <t>Optiver Trading Day</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3806,7 +3814,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr"/>
@@ -3819,12 +3827,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>NASA JPL internships</t>
+          <t>SIG Insight Week</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3834,19 +3842,15 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates (see page)</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpl.nasa.gov/edu/internships/</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched; check by hand.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -3856,12 +3860,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>NASA-Caltech JPL SURF</t>
+          <t>Two Sigma Financial Modeling Challenge</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3871,19 +3875,15 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates (see page)</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpl.nasa.gov/edu/intern/apply/caltech-summer-undergraduate-research-fellowship/</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>SURF projects hosted at JPL. jpl.nasa.gov returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
-        </is>
-      </c>
+          <t>https://www.twosigma.com/</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Princeton summer research programs (non-Princeton undergraduates)</t>
+          <t>NASA JPL internships</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>https://undergraduateresearch.princeton.edu/programs/summer-programs</t>
+          <t>https://www.jpl.nasa.gov/edu/internships/</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Princeton's directory of summer research programmes; filterable by eligibility for non-Princeton students and by class year. | 2026-10-01: probed HTTP 200, then HTTP 403 from Cloudflare to the tracker's client minutes later, so it is not watched; check by hand.</t>
+          <t>Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched; check by hand.</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: DIAMONDS: Directed, Intensive and Mentored Opportunities in Data Science (Tufts University)</t>
+          <t>NASA-Caltech JPL SURF</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3940,22 +3940,22 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Most REU sites open Dec-Feb; check the site</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547822</t>
+          <t>https://www.jpl.nasa.gov/edu/intern/apply/caltech-summer-undergraduate-research-fellowship/</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2547822, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>SURF projects hosted at JPL. jpl.nasa.gov returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: Research Experience for Undergraduates in Translational Applications of AI to Engineering (REU-TrACE) (Iowa State University)</t>
+          <t>Princeton summer research programs (non-Princeton undergraduates)</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3977,22 +3977,22 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Most REU sites open Dec-Feb; check the site</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447479</t>
+          <t>https://undergraduateresearch.princeton.edu/programs/summer-programs</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447479, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>Princeton's directory of summer research programmes; filterable by eligibility for non-Princeton students and by class year. | 2026-10-01: probed HTTP 200, then HTTP 403 from Cloudflare to the tracker's client minutes later, so it is not watched; check by hand.</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: Research in Consumer Networking Technologies (University of Missouri-Columbia)</t>
+          <t>REU SITE: DIAMONDS: Directed, Intensive and Mentored Opportunities in Data Science (Tufts University)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548100</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547822</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548100, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547822, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: WAVE SURF: Workforce Advancement in Verification and Emulation of Semiconductor Chips -- Undergraduate Research Fellowships (Texas A&amp;M Engineering Experiment Station)</t>
+          <t>REU SITE: Research Experience for Undergraduates in Translational Applications of AI to Engineering (REU-TrACE) (Iowa State University)</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548388</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447479</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548388, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447479, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>REU Site Renewal: Enhancing AI-Driven Insights Within IoT-Enabled Ecosystems (AIoT-Sys) (University of California-Irvine)</t>
+          <t>REU SITE: Research in Consumer Networking Technologies (University of Missouri-Columbia)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447884</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548100</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447884, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548100, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>REU Site in Software Engineering (REUSE) at Carnegie Mellon University (Carnegie Mellon University)</t>
+          <t>REU SITE: WAVE SURF: Workforce Advancement in Verification and Emulation of Semiconductor Chips -- Undergraduate Research Fellowships (Texas A&amp;M Engineering Experiment Station)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447499</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548388</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447499, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548388, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>REU Site: AI Research for Intelligent Systems and Efficiency (University of Arizona)</t>
+          <t>REU Site Renewal: Enhancing AI-Driven Insights Within IoT-Enabled Ecosystems (AIoT-Sys) (University of California-Irvine)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548190</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447884</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548190, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447884, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>REU Site: AI and Science Summer Lab: advancing AI-enabled scientific discovery across the physical and biological sciences (University of Chicago)</t>
+          <t>REU Site in Software Engineering (REUSE) at Carnegie Mellon University (Carnegie Mellon University)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447314</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447499</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447314, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447499, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Access to Inquiry in Mathematics Undergraduate Program (University of Wisconsin-Milwaukee)</t>
+          <t>REU Site: AI Research for Intelligent Systems and Efficiency (University of Arizona)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447752</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548190</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447752, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548190, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Advancing high-performance computing opportunities in undergraduate research at UW-Eau Claire to meet challenges of multidisciplinary computational science (University of Wisconsin-Eau Claire)</t>
+          <t>REU Site: AI and Science Summer Lab: advancing AI-enabled scientific discovery across the physical and biological sciences (University of Chicago)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447779</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447314</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447779, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447314, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Agile AI Research for Safety Critical Systems (Embry-Riddle Aeronautical University)</t>
+          <t>REU Site: Access to Inquiry in Mathematics Undergraduate Program (University of Wisconsin-Milwaukee)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548167</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447752</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548167, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447752, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Algebra, Combinatorics, and Statistics (Texas State University - San Marcos)</t>
+          <t>REU Site: Advancing high-performance computing opportunities in undergraduate research at UW-Eau Claire to meet challenges of multidisciplinary computational science (University of Wisconsin-Eau Claire)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447229</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447779</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447229, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447779, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Algorithms in Data Science with Applications (Montana State University)</t>
+          <t>REU Site: Agile AI Research for Safety Critical Systems (Embry-Riddle Aeronautical University)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548411</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548167</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548411, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548167, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Artificial Intelligence for Advanced Applications (Worcester Polytechnic Institute)</t>
+          <t>REU Site: Algebra, Combinatorics, and Statistics (Texas State University - San Marcos)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349370</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447229</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2349370, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447229, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Computing Research in Unmanned Aerial Systems (Texas A&amp;M University Corpus Christi)</t>
+          <t>REU Site: Algorithms in Data Science with Applications (Montana State University)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447596</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548411</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447596, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548411, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Mathematics in Real World Problems (Florida State University)</t>
+          <t>REU Site: Applied Artificial Intelligence for Advanced Applications (Worcester Polytechnic Institute)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349382</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349370</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2349382, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349370, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Research in Deep Learning (Missouri State University)</t>
+          <t>REU Site: Applied Computing Research in Unmanned Aerial Systems (Texas A&amp;M University Corpus Christi)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548161</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447596</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548161, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447596, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied and Computational Mathematics (University of California-Los Angeles)</t>
+          <t>REU Site: Applied Mathematics in Real World Problems (Florida State University)</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548181</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349382</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548181, funded through 11/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2349382, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applying Data Science on Energy-efficient Cluster Systems and Applications (The University Corporation, Northridge)</t>
+          <t>REU Site: Applied Research in Deep Learning (Missouri State University)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548509</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548161</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548509, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548161, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Artificial Intelligence for Computational Creativity (Brown University)</t>
+          <t>REU Site: Applied and Computational Mathematics (University of California-Los Angeles)</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447190</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548181</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447190, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548181, funded through 11/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Artificial Intelligence, Security, and Privacy (Northwestern University at Chicago)</t>
+          <t>REU Site: Applying Data Science on Energy-efficient Cluster Systems and Applications (The University Corporation, Northridge)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447155</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548509</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447155, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548509, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>REU Site: CNS: Sensing and Smart Systems (Florida Atlantic University)</t>
+          <t>REU Site: Artificial Intelligence for Computational Creativity (Brown University)</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447437</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447190</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447437, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447190, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Combinatorics, Algorithms, and AI applied to Real Problems (CAAR) (University of Maryland, College Park)</t>
+          <t>REU Site: Artificial Intelligence, Security, and Privacy (Northwestern University at Chicago)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447466</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447155</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447466, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447155, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational Methods for Understanding Music, Media and Minds (University of Rochester)</t>
+          <t>REU Site: CNS: Sensing and Smart Systems (Florida Atlantic University)</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447607</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447437</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447607, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447437, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational Number Theory (Clemson University)</t>
+          <t>REU Site: Combinatorics, Algorithms, and AI applied to Real Problems (CAAR) (University of Maryland, College Park)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349174</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447466</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2349174, funded through 10/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447466, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational Sensing for Human-centered AI (Rochester Institute of Tech)</t>
+          <t>REU Site: Computational Methods for Understanding Music, Media and Minds (University of Rochester)</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445028</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447607</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2445028, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447607, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational and Applied Mathematics Program (Cal Poly Pomona Foundation, Inc.)</t>
+          <t>REU Site: Computational Number Theory (Clemson University)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2348984</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349174</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2348984, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2349174, funded through 10/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computing and Engineering for Safe and Healthy Digital Environment (New York Institute of Technology)</t>
+          <t>REU Site: Computational Sensing for Human-centered AI (Rochester Institute of Tech)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447577</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445028</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447577, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2445028, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cryptography, Coding Theory and Quantum Computing at the USF (University of South Florida)</t>
+          <t>REU Site: Computational and Applied Mathematics Program (Cal Poly Pomona Foundation, Inc.)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548160</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2348984</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548160, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2348984, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cyberinfrastructure (CI) Research for Societal Advancement REU (University of Texas at Austin)</t>
+          <t>REU Site: Computing and Engineering for Safe and Healthy Digital Environment (New York Institute of Technology)</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447887</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447577</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447887, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447577, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cybersecurity Research of Unmanned Aerial Vehicles (Embry-Riddle Aeronautical University)</t>
+          <t>REU Site: Cryptography, Coding Theory and Quantum Computing at the USF (University of South Florida)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548278</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548160</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548278, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548160, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cybersecurity in Emerging Technologies (Mississippi State University)</t>
+          <t>REU Site: Cyberinfrastructure (CI) Research for Societal Advancement REU (University of Texas at Austin)</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447266</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447887</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447266, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447887, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Data Science Across Disciplines (Marquette University)</t>
+          <t>REU Site: Cybersecurity Research of Unmanned Aerial Vehicles (Embry-Riddle Aeronautical University)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548034</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548278</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548034, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548278, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Deep Learning for Dynamical Systems in Biological and Physical Sciences (University of Southern Mississippi)</t>
+          <t>REU Site: Cybersecurity in Emerging Technologies (Mississippi State University)</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447675</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447266</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447675, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447266, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Digital Forensic Research on Emerging Computing Environments (Virginia Commonwealth University)</t>
+          <t>REU Site: Data Science Across Disciplines (Marquette University)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447453</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548034</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447453, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548034, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>REU Site: EXERCISE - Explore Emerging Computing in Science and Engineering (Salisbury University)</t>
+          <t>REU Site: Deep Learning for Dynamical Systems in Biological and Physical Sciences (University of Southern Mississippi)</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447041</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447675</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447041, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447675, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Engineers for Exploration (University of California-San Diego)</t>
+          <t>REU Site: Digital Forensic Research on Emerging Computing Environments (Virginia Commonwealth University)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548467</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447453</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548467, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447453, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Exploring the FABRIC Research Instrument to Catalyze Multi-disciplinary Research in Networks, Distributed Systems, and Emerging CyberInfrastructure (CI) Applications (University of North Carolina at Chapel Hill)</t>
+          <t>REU Site: EXERCISE - Explore Emerging Computing in Science and Engineering (Salisbury University)</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447441</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447041</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447441, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447041, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Extremal Graph Theory and Dynamical Systems at RIT (Rochester Institute of Tech)</t>
+          <t>REU Site: Engineers for Exploration (University of California-San Diego)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2243938</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548467</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, awards 2243938, 2547942, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548467, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Frontier Technologies for Biometrics and Authentication (SUNY at Buffalo)</t>
+          <t>REU Site: Exploring the FABRIC Research Instrument to Catalyze Multi-disciplinary Research in Networks, Distributed Systems, and Emerging CyberInfrastructure (CI) Applications (University of North Carolina at Chapel Hill)</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548357</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447441</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548357, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447441, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Hands-On Research in Federated Learning Security through Red Team vs. Blue Team Exercises (University of Nevada Las Vegas)</t>
+          <t>REU Site: Extremal Graph Theory and Dynamical Systems at RIT (Rochester Institute of Tech)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548041</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2243938</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548041, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, awards 2243938, 2547942, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Hardware Security (University of South Florida)</t>
+          <t>REU Site: Frontier Technologies for Biometrics and Authentication (SUNY at Buffalo)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445849</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548357</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2445849, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548357, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Home Embodied AI and Robot Technology (HEART) Undergraduate Research Experience (Northeastern University)</t>
+          <t>REU Site: Hands-On Research in Federated Learning Security through Red Team vs. Blue Team Exercises (University of Nevada Las Vegas)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548331</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548041</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548331, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548041, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Human-AI Interaction and Evaluation in Web and Information Systems (Old Dominion University Research Foundation)</t>
+          <t>REU Site: Hardware Security (University of South Florida)</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548125</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445849</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548125, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2445849, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Integrative Challenges in Cybersecurity-Deception, Remediation, and Resilient Systems (SUNY at Albany)</t>
+          <t>REU Site: Home Embodied AI and Robot Technology (HEART) Undergraduate Research Experience (Northeastern University)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548335</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548331</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548335, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548331, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Interdisciplinary Research Experience in Computational Sciences (Louisiana State University)</t>
+          <t>REU Site: Human-AI Interaction and Evaluation in Web and Information Systems (Old Dominion University Research Foundation)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447810</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548125</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447810, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548125, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Knowledge Beyond Language with Vector Embeddings (University of North Texas)</t>
+          <t>REU Site: Integrative Challenges in Cybersecurity-Deception, Remediation, and Resilient Systems (SUNY at Albany)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548192</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548335</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548192, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548335, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Making Generative Artificial Intelligence Responsible (University of North Texas)</t>
+          <t>REU Site: Interdisciplinary Research Experience in Computational Sciences (Louisiana State University)</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447834</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447810</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447834, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447810, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Math REU at Kent State (Kent State University)</t>
+          <t>REU Site: Knowledge Beyond Language with Vector Embeddings (University of North Texas)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2439984</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548192</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2439984, funded through 08/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548192, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Mathematical Analysis and Applications (Regents of the University of Michigan - Dearborn)</t>
+          <t>REU Site: Making Generative Artificial Intelligence Responsible (University of North Texas)</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548087</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447834</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548087, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447834, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Quantum Information Science and Engineering (University of Washington)</t>
+          <t>REU Site: Math REU at Kent State (Kent State University)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446908</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2439984</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2446908, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2439984, funded through 08/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Quantum algorithms and optimization (QAO) (University of Tennessee Knoxville)</t>
+          <t>REU Site: Mathematical Analysis and Applications (Regents of the University of Michigan - Dearborn)</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548084</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548087</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548084, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548087, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>REU Site: REU@UNO - An REU Site on Security and Artificial Intelligence/Machine Learning for the Internet of Things (University of Nebraska at Omaha)</t>
+          <t>REU Site: Quantum Information Science and Engineering (University of Washington)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447289</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446908</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447289, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2446908, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research Experience for Undergraduates Intersecting Computing and Evolution (Grand Valley State University)</t>
+          <t>REU Site: Quantum algorithms and optimization (QAO) (University of Tennessee Knoxville)</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547922</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548084</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2547922, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548084, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research Experiences for Undergraduates in Discrete and Applied Mathematics (Michigan State University)</t>
+          <t>REU Site: REU@UNO - An REU Site on Security and Artificial Intelligence/Machine Learning for the Internet of Things (University of Nebraska at Omaha)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2244461</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447289</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2244461, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447289, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research Experiences for Undergraduates in Mathematics at Indiana University (Indiana University)</t>
+          <t>REU Site: Research Experience for Undergraduates Intersecting Computing and Evolution (Grand Valley State University)</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447563</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547922</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447563, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547922, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research on Prescriptive Analytics for AI-enabled Operations Engineering (University of Missouri-Columbia)</t>
+          <t>REU Site: Research Experiences for Undergraduates in Discrete and Applied Mathematics (Michigan State University)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548110</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2244461</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548110, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2244461, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Robotics and Autonomous Systems (University of Southern California)</t>
+          <t>REU Site: Research Experiences for Undergraduates in Mathematics at Indiana University (Indiana University)</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -6059,12 +6059,12 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447397</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447563</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447397, funded through 11/30/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447563, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Robots in the Real World (Oregon State University)</t>
+          <t>REU Site: Research on Prescriptive Analytics for AI-enabled Operations Engineering (University of Missouri-Columbia)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349747</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548110</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2349747, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548110, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>REU Site: SRAII: Safe and Reliable AI and the Internet (University of Southern California)</t>
+          <t>REU Site: Robotics and Autonomous Systems (University of Southern California)</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447729</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447397</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447729, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447397, funded through 11/30/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Statistical Mathematics and Research Training (SMART) (Marist College)</t>
+          <t>REU Site: Robots in the Real World (Oregon State University)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447324</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349747</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447324, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349747, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Summer Program for Interdisciplinary Research and Education-Emerging Interface Technologies (Iowa State University)</t>
+          <t>REU Site: SRAII: Safe and Reliable AI and the Internet (University of Southern California)</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547899</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447729</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2547899, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447729, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Summer Undergraduate Mathematics Research at Kansas State University (SUMaR at K-State) (Kansas State University)</t>
+          <t>REU Site: Statistical Mathematics and Research Training (SMART) (Marist College)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548038</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447324</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548038, funded through 07/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447324, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Summer Undergraduate Research Experience (SURE) at Illinois Tech (Illinois Institute of Technology)</t>
+          <t>REU Site: Summer Program for Interdisciplinary Research and Education-Emerging Interface Technologies (Iowa State University)</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548498</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547899</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548498, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547899, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Technologies for Community-Driven Design (University of California-San Diego)</t>
+          <t>REU Site: Summer Undergraduate Mathematics Research at Kansas State University (SUMaR at K-State) (Kansas State University)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447548</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548038</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447548, funded through 06/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548038, funded through 07/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>REU Site: The Face and Mind of Artificial Intelligence (University of Southern California)</t>
+          <t>REU Site: Summer Undergraduate Research Experience (SURE) at Illinois Tech (Illinois Institute of Technology)</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446866</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548498</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2446866, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548498, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>REU Site: The future of discovery: training students to build and apply open-source machine learning models and tools (University of Illinois at Urbana-Champaign)</t>
+          <t>REU Site: Technologies for Community-Driven Design (University of California-San Diego)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447843</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447548</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447843, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447548, funded through 06/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Trustworthy AI (Rochester Institute of Tech)</t>
+          <t>REU Site: The Face and Mind of Artificial Intelligence (University of Southern California)</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447631</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446866</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447631, funded through 12/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2446866, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Trustworthy AI and Security for Intelligent Vehicles and Transportation Systems (University of Alabama Tuscaloosa)</t>
+          <t>REU Site: The future of discovery: training students to build and apply open-source machine learning models and tools (University of Illinois at Urbana-Champaign)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548476</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447843</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548476, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447843, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>REU Site: UT Rio Grande Valley REU Program on Applied Mathematics and Computational and Data Science (AMCADS) (The University of Texas Rio Grande Valley)</t>
+          <t>REU Site: Trustworthy AI (Rochester Institute of Tech)</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447683</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447631</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447683, funded through 11/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447631, funded through 12/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Computer Research in Cybersecurity and AI (UnCoRe-CyberAI) (Oakland University)</t>
+          <t>REU Site: Trustworthy AI and Security for Intelligent Vehicles and Transportation Systems (University of Alabama Tuscaloosa)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349663</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548476</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2349663, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548476, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research  in Data Analytics (REU:URDA) (Marshall University Research Corporation)</t>
+          <t>REU Site: UT Rio Grande Valley REU Program on Applied Mathematics and Computational and Data Science (AMCADS) (The University of Texas Rio Grande Valley)</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447660</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447683</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447660, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447683, funded through 11/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research Experience in Edge Intelligence (Board of Regents, NSHE, obo University of Nevada, Reno)</t>
+          <t>REU Site: Undergraduate Computer Research in Cybersecurity and AI (UnCoRe-CyberAI) (Oakland University)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548395</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349663</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548395, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349663, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research Experiences in Artificial Intelligence, Data Analytics, and Mixed Reality for Smart and Connected Health (Texas State University - San Marcos)</t>
+          <t>REU Site: Undergraduate Research  in Data Analytics (REU:URDA) (Marshall University Research Corporation)</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447856</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447660</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447856, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447660, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research in the Mathematical Sciences and their Applications (Texas A&amp;M University)</t>
+          <t>REU Site: Undergraduate Research Experience in Edge Intelligence (Board of Regents, NSHE, obo University of Nevada, Reno)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548033</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548395</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548033, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548395, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>UC Davis GREAT program</t>
+          <t>REU Site: Undergraduate Research Experiences in Artificial Intelligence, Data Analytics, and Mixed Reality for Smart and Connected Health (Texas State University - San Marcos)</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -6715,22 +6715,22 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Most REU sites open Dec-Feb; check the site</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates (see page)</t>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>https://great.ucdavis.edu/</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447856</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>Global Research Experience in Advanced Technologies. Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447856, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+          <t>REU Site: Undergraduate Research in the Mathematical Sciences and their Applications (Texas A&amp;M University)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Most REU sites open Dec-Feb; check the site</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>'approximately 30 degree-seeking credits'</t>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>https://spcs.stanford.edu/jobs</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548033</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548033, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg First Year Insights</t>
+          <t>UC Davis GREAT program</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -6794,140 +6794,140 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>First-years (unverified)</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/company/careers/</t>
+          <t>https://great.ucdavis.edu/</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+          <t>Global Research Experience in Advanced Technologies. Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>'approximately 30 degree-seeking credits'</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>https://spcs.stanford.edu/jobs</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg First Year Insights</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>First-years (unverified)</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not by individual application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED - too early</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>NISA Investment Advisors - Intern</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Fall-winter</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.nisa.com/early-careers</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>Edward Jones Internship</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Fall</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>Juniors</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>APPLIED - too early</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Stifel - Institutional Group Internship</t>
+          <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -6937,22 +6937,22 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>~Nov, rolling per office/desk</t>
+          <t>Fall-winter</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>https://www.stifel.com/careers/internships</t>
+          <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
@@ -6964,32 +6964,32 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+          <t>Edward Jones Internship</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Winter-spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Rising sophomore+</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
@@ -7001,32 +7001,32 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>HRT Sophomore Winternship</t>
+          <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.stifel.com/careers/internships</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>January, 2-4 weeks, Python/C++.</t>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -7048,22 +7048,22 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+          <t>Winter-spring</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+          <t>Rising sophomore+</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>HRT Sophomore Winternship</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -7095,10 +7095,14 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G180" s="3" t="inlineStr"/>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>January, 2-4 weeks, Python/C++.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -7108,7 +7112,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -7118,20 +7122,24 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -7141,7 +7149,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -7174,7 +7182,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -7207,7 +7215,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -7230,11 +7238,7 @@
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G184" s="3" t="inlineStr">
-        <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
-        </is>
-      </c>
+      <c r="G184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -7244,7 +7248,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -7259,19 +7263,15 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr">
-        <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
@@ -7281,32 +7281,32 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
@@ -7318,86 +7318,86 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Sophomore Experience</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Sophomores</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>Wells Fargo Sophomore Experience</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -7407,17 +7407,17 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Sophomores</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>CMF Select New York 2026</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>https://fima.partners/</t>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
+          <t>CMF Select New York 2026</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+          <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>https://www.qwafafew.org/</t>
+          <t>https://fima.partners/</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Tapia Conference</t>
+          <t>FutureAlpha / QuantStrats 2026</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -7661,22 +7661,22 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Open, but serves underrepresented groups in computing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Open to attend; low relative value for a first-year.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7688,106 +7688,106 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qwafafew.org/</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Tapia Conference</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Open, but serves underrepresented groups in computing</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>https://tapiaconference.cmd-it.org/</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Open to attend; low relative value for a first-year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C197" s="3" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D197" s="3" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E197" s="3" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G197" s="3" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>Duke Career Hub early-insight table</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>First-year/sophomore</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>https://careerhub.students.duke.edu/</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>Public list of early insight programs by target year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>MLH hackathon season calendar</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>Weekly all year</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>Any undergrad year</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>https://www.mlh.com/seasons/2027/events</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-30: MLH's official season calendar (e.g. Gator Quant Hacks, MHacks, Oct 2026). Too high-churn for page_text; treat as a manual/calendar pointer.</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Yale 'Gorick's List' for quant trading</t>
+          <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -7814,55 +7814,92 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>First-year/sophomore</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr"/>
+          <t>https://careerhub.students.duke.edu/</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Public list of early insight programs by target year.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Yale 'Gorick's List' for quant trading</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F201" s="4" t="inlineStr">
+      <c r="F202" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G201" s="3" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G201"/>
+  <autoFilter ref="A1:G202"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -8061,6 +8098,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8072,7 +8110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9375,8 +9413,82 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Hack for Humanity (Santa Clara University)</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Never - blocked</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-10-08: HTTP 429 Vercel Security Checkpoint ('We're verifying your browser') to the tracker's honest User-Agent.</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Open in your browser.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Winter (check site for the date)</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>https://hackforhumanity.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>HackMIT</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Never - nothing to diff</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-10-08: a JavaScript app (12 chars over plain HTTP, 16,112 rendered), and the rendered page re-orders its organiser list on every load: two renders a minute apart differed on 96 of 163 lines, so a page diff would report a change every morning.</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Open in your browser; the FAQ states travel reimbursement and the application dates.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Spring (2026 applications were due Jul 4)</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>https://hackmit.org/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -9411,6 +9523,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11688,7 +11802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12086,17 +12200,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by caltech-surf</t>
+          <t>Already watched by calhacks</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Caltech SURF</t>
+          <t>Cal Hacks</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -12106,29 +12220,29 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
+          <t>https://www.calhacks.io/</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
+          <t>Verified 2026-10-08: 'Cal Hacks is open to undergraduate and graduate students as well as new grads of under 1 year from all colleges and universities.' Travel: 'This year, we will be offering travel stipends to a limited number of hackers with regional caps based on the region you are coming from'; most attendees get there themselves (Caltrain, BART). Run by Hackers@Berkeley; held in San Francisco.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by capitalone-early-career</t>
+          <t>Already watched by caltech-surf</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Capital One Analyst / Tech / Product Summits</t>
+          <t>Caltech SURF</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -12138,61 +12252,61 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
+          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
+          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by citi-pre-internships</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Citi Freshman Discovery</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cmu-riss</t>
+          <t>Already watched by cerebralvalley-sf-events</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
+          <t>Cerebral Valley SF &amp; Bay Area AI events calendar</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -12202,93 +12316,93 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://riss.ri.cmu.edu/</t>
+          <t>https://cerebralvalley.ai/events/san-francisco</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
+          <t>Verified 2026-10-08: Cerebral Valley's SF and Bay Area AI event feed, mixing hackathons with talks and meetups, e.g. 'The Recursive Agents Hackathon' (Oct 17, Shack15 SF; 'All attendees must apply and be approved') and 'Intelligence at Work Hackathon' (Oct 23, Menlo Park). Not student-specific; check each event's own terms.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by comap-mcm</t>
+          <t>Already watched by citi-pre-internships</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>COMAP MCM/ICM</t>
+          <t>Citi Freshman Discovery</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/undergraduate/contests/</t>
+          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
+          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cornell-trading-competition</t>
+          <t>Already watched by cmu-riss</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://riss.ri.cmu.edu/</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cra-dreu</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CRA DREU</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -12298,29 +12412,29 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://cra.org/cra-wp/dreu/</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cs-social-good-fellowships</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CS+Social Good Summer Fellowships</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -12330,56 +12444,56 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by curis</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by datasurf</t>
+          <t>Already watched by cs-social-good-fellowships</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Stanford DataSURF (formerly SURP-Stats)</t>
+          <t>CS+Social Good Summer Fellowships</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -12394,93 +12508,93 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
+          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
+          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by datasurf</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw campus site</t>
+          <t>Stanford DataSURF (formerly SURP-Stats)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/</t>
+          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
+          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dimacs-reu</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>DIMACS REU</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -12490,125 +12604,125 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://dimacs.rutgers.edu/reu-main</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dukequant-competition</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by evercore-campus</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Evercore student events</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Already watched by futureforce-launchpad</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+          <t>https://www.duke.edu/</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -12618,56 +12732,56 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by hackgt</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>HackGT</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12682,29 +12796,29 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://hack.gt/</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Verified 2026-10-08 (rendered page): 'If you will be traveling from afar, we offer reimbursements to GT'; the page links a travel guide.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icerm-summer</t>
+          <t>Already watched by hackprinceton</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Summer@ICERM</t>
+          <t>HackPrinceton</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -12714,24 +12828,24 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://icerm.brown.edu/summerug/</t>
+          <t>https://www.hackprinceton.com/</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
+          <t>Verified 2026-10-08: 'Applicants must be matriculated in an undergraduate or graduate program at a college or university.' Travel: 'Some admitted hackers may receive a travel stipend that covers part of their travel expenses.' No cost to apply or attend.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icpc-pnw</t>
+          <t>Already watched by hackumass</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>HackUMass</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -12739,36 +12853,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
+          <t>https://www.hackumass.com/</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
+          <t>Verified 2026-10-08: 'HackUMass XIV is open to ALL college students, including graduate students, regardless of major!' Travel: 'If you apply by the early application deadline, you have the opportunity to apply for travel reimbursement.' Early applications for XIV were already closed on 2026-10-08.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -12778,61 +12892,61 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-prosperity</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ipam-rips</t>
+          <t>Already watched by hophacks</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>IPAM RIPS (UCLA)</t>
+          <t>HopHacks</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -12842,61 +12956,61 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
+          <t>https://hophacks.com/</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
+          <t>Verified 2026-10-08: 'We will not be offering individual travel reimbursements. However, please see the busing interest form ... If enough people from your city sign up, we may send a FREE bus.'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-fttp</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FTTP</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-preview</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Preview</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -12906,56 +13020,56 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Jane Street AMP - TA role</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Jane Street ETC</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12965,29 +13079,29 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Jane Street SEE</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -13002,52 +13116,56 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://prosperity.imc.com/</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Experience - OCaml and systems design.</t>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by ipam-rips</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Symposium</t>
+          <t>IPAM RIPS (UCLA)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>INVITE</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Already watched by janestreet-programs</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Unboxed</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -13055,32 +13173,36 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jefferies-campus</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jefferies campus opportunities</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -13090,120 +13212,120 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/preview/</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
+          <t>Verified 2026-09-26 (source research): day-long programme 'for students at any point in their academic career'. One of the 12 programmes on the watched janestreet-programs index; this watches its own page.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jhuapl-internships</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL internships</t>
+          <t>Jane Street AMP - TA role</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.jhuapl.edu/careers/internships</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/amp/</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
+          <t>Paid Jane Street summer on the teaching side. Housing, meals, travel covered. Eligible from spring 2027.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-career-edyou</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>JPMorganChase Career.edYOU Academy</t>
+          <t>Jane Street ETC</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
+          <t>Electronic Trading Challenge. Entry via university, prior JS events, or the puzzle ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jpmc-fellowship</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>JPMC Fellowship Program</t>
+          <t>Jane Street SEE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
+          <t>Software Engineering Experience - OCaml and systems design.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Already watched by jumptrading-greenhouse</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading Campus Jump Early Access</t>
+          <t>Jane Street Symposium</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -13211,31 +13333,27 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>INVITE</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.jumptrading.com/hr/students-new-grads</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kkr-greenhouse</t>
+          <t>Already watched by janestreet-programs</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>KKR Scholars Program</t>
+          <t>Jane Street Unboxed</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -13243,36 +13361,32 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Already watched by kleinerperkins-fellows-ashby</t>
+          <t>Already watched by jefferies-campus</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Kleiner Perkins Engineering Fellows</t>
+          <t>Jefferies campus opportunities</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -13282,24 +13396,24 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>https://www.kleinerperkins.com/fellows/</t>
+          <t>https://jefferies.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 60 entries. Banking is lower priority than quant.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Already watched by lanl-students</t>
+          <t>Already watched by jhuapl-internships</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>LANL student internships (Los Alamos National Laboratory)</t>
+          <t>Johns Hopkins APL internships</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -13314,153 +13428,157 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://www.lanl.gov/engage/collaboration/internships</t>
+          <t>https://www.jhuapl.edu/careers/internships</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
+          <t>Page states a minimum GPA requirement. Simplify already carries some APL postings; this watches the programme page itself.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Already watched by llnl-students</t>
+          <t>Already watched by jpmc-career-edyou</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
+          <t>JPMorganChase Career.edYOU Academy</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/career-edyou</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
+          <t>Verified 2026-09-26: 'designed for college sophomores studying in the United States'.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Already watched by luisae</t>
+          <t>Already watched by jpmc-fellowship</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>LuisaE/opportunities</t>
+          <t>JPMC Fellowship Program</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/LuisaE/opportunities</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr"/>
+          <t>https://www.jpmorganchase.com/careers/explore-opportunities/programs/jpmcfellowship</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: 'sophomore students, including, without limitation, Black, Hispanic and Latino... All sophomore students... regardless of background, are welcome'.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mathprograms-listing</t>
+          <t>Already watched by jumptrading-greenhouse</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MathPrograms.org programme listing</t>
+          <t>Jump Trading Campus Jump Early Access</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://www.mathprograms.org/db/program</t>
+          <t>https://www.jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
+          <t>Verified 2026-09-30 from the 2026 posting: 'First-year undergraduates at US universities' in math/CS/physics/stats/engineering/econ. One-day programme in Chicago, travel/meals/lodging covered. Posts on the Greenhouse board watched by jumptrading-greenhouse; not live today.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Already watched by meta-hacker-cup</t>
+          <t>Already watched by kkr-greenhouse</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Meta Hacker Cup</t>
+          <t>KKR Scholars Program</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
+          <t>https://www.kkr.com/careers/student-careers/student-career-opportunities</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
+          <t>2025 posting: 'rising sophomores graduating with a Bachelor's degree in December 2027 – June 2028'. The 2027 edition should be Dec 2029-Jun 2030, the owner's window. Late-May dates may clash with Stanford spring quarter. Posts on KKR's Greenhouse board, slug 'staged'.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Already watched by millennium-eightfold</t>
+          <t>Already watched by kleinerperkins-fellows-ashby</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Meet Millennium</t>
+          <t>Kleiner Perkins Engineering Fellows</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -13470,24 +13588,24 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
+          <t>https://www.kleinerperkins.com/fellows/</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
+          <t>Verified 2026-09-30 from the Ashby posting: no class-year gate; wants 'Degree in computer science, engineering, math, physics or other fields related to software engineering' and Bay Area availability. Summer placement at a KP portfolio startup plus speaker series. Selective, and cohorts skew upperclass.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-battlecode-2027</t>
+          <t>Already watched by lahacks</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MIT Battlecode 2027</t>
+          <t>LA Hacks</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -13502,56 +13620,56 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://battlecode.org/</t>
+          <t>https://www.lahacks.com/</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
+          <t>Verified 2026-10-08: 'LA Hacks is open to college students of all skill levels'; 'hosted at UCLA's Pauley Pavilion ... in Mid-April 2027'. The FAQ has a 'Travel Reimbursement' tab, but its answer is not in the served HTML, so whether travel is reimbursed for 2027 is unverified.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mit-trading-competition</t>
+          <t>Already watched by lanl-students</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Traders@MIT Trading Competition</t>
+          <t>LANL student internships (Los Alamos National Laboratory)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://traders.mit.edu/competition</t>
+          <t>https://www.lanl.gov/engage/collaboration/internships</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
+          <t>Lab-run undergraduate internship programme. The old /careers/career-options/student-internships URL redirects here.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Already watched by mitll-students</t>
+          <t>Already watched by llnl-students</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MIT Lincoln Laboratory student opportunities</t>
+          <t>LLNL student internships (Lawrence Livermore National Laboratory)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -13566,56 +13684,52 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
+          <t>https://www.llnl.gov/join-our-team/careers/student-internship-veteran-programs</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
+          <t>Undergraduate summer internships plus internally and externally sponsored student programmes. Not part of DOE SULI's lab list in this file.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nist-surf</t>
+          <t>Already watched by luisae</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>NIST SURF</t>
+          <t>LuisaE/opportunities</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/surf</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
-        </is>
-      </c>
+          <t>https://github.com/LuisaE/opportunities</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nsa-students</t>
+          <t>Already watched by mathprograms-listing</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NSA student programs</t>
+          <t>MathPrograms.org programme listing</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -13630,61 +13744,61 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.intelligencecareers.gov/nsa/students</t>
+          <t>https://www.mathprograms.org/db/program</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
+          <t>Verified 2026-09-26: AMS-run application portal most math REUs use (UChicago, PCMI, Polymath Jr); already lists POLYMATHREU2027 and SLMath PROOF 2027. Substitutes for the NSF REU directory (AWS WAF challenge) and the AMS REU list (403), neither readable by this client.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Already watched by nuft-2027</t>
+          <t>Already watched by meta-hacker-cup</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NUFT 2027 Quant Internships</t>
+          <t>Meta Hacker Cup</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
+          <t>https://www.facebook.com/codingcompetitions/hacker-cup</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
+          <t>Verified 2026-09-26: 'Open to participants around the world'. Page still shows the 2025 season. JavaScript page: 15 chars plain, 1,485 rendered.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Already watched by open-source-quantitative-finance</t>
+          <t>Already watched by millennium-eightfold</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Open Source Quantitative Finance Conference</t>
+          <t>Meet Millennium</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -13694,29 +13808,29 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://osqf.org/</t>
+          <t>https://www.mlp.com/life-at-millennium/inside-meet-millennium/</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
+          <t>Verified 2026-09-30: 'high-performing undergraduate and master's students ... Designed as an insight into Millennium's 2027 Summer Intern Program'. Travel to one of five offices; SWE/quant-engineering simulations. www.mlp.com is WP Engine, so not watched directly; the posting should surface via millennium-eightfold.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-futurefocus</t>
+          <t>Already watched by mit-battlecode-2027</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Optiver FutureFocus Chicago 2026</t>
+          <t>MIT Battlecode 2027</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -13726,52 +13840,56 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
+          <t>https://battlecode.org/</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>MIT's real-time strategy AI competition: you write an autonomous player that commands a robot army, then compete in scrimmages and bracketed tournaments over January. Over $20,000 in total prize money. Open beyond MIT - 'Anyone can write a bot, create a team, and participate in scrimmage matches/rankings.' Prize-tournament gates from the Full Eligibility Rules (battlecode.org/about.html): Sprint Tournaments - 'All teams are eligible.' US Qualifier - 'Teams must consist entirely of US college students studying full-time, or in a transition phase.' Final Tournament - 'Teams must have qualified via the US or International Qualifier.' MIT Newbie Tournament is MIT-only and High School Tournament is high-school-only, so neither applies. Unlike MIT Pokerbots, no MIT-affiliated teammate or MIT certificate is needed for the track you would enter. As of Sep 2026 the site still reads 'Battlecode 2026 ended on January 31st, 2026!' - no 2027 registration date posted yet, though the page already references Battlecode 2027 sponsorships. No team size limit, age limit, or citizenship rule beyond 'US college student' was stated on the pages read. Source: battlecode.org home page and about.html.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Already watched by optiver-ready-trader</t>
+          <t>Already watched by mit-trading-competition</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Optiver Ready Trader Go</t>
+          <t>Traders@MIT Trading Competition</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr"/>
+          <t>https://traders.mit.edu/competition</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Largest intercollegiate competition, $20,000+. NOT the same as Pokerbots - this one IS open to first-years.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Already watched by purdue-srop</t>
+          <t>Already watched by mitll-students</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Purdue Summer Research Opportunities Program (SROP)</t>
+          <t>MIT Lincoln Laboratory student opportunities</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -13786,56 +13904,56 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
+          <t>https://www.ll.mit.edu/careers/student-opportunities</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
+          <t>Several tracks. The industry-mentor programme is for students in their junior year; the Summer Research Program takes undergraduate and graduate students.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ramp-ashby</t>
+          <t>Already watched by mlh-season-events</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Ramp Emerging Talent</t>
+          <t>MLH hackathon season calendar</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>https://ramp.com/emerging-talent</t>
+          <t>https://www.mlh.com/seasons/2027/events</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
+          <t>Verified 2026-09-30: MLH's official season calendar (e.g. Gator Quant Hacks, MHacks, Oct 2026). Too high-churn for page_text; treat as a manual/calendar pointer. Correction 2026-10-08: now watched as page_text (source mlh-season-events); one Change per day at most, so the churn is bounded.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Already watched by reufinder-freshmen</t>
+          <t>Already watched by nist-surf</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>REU Finder - freshman-eligible filter</t>
+          <t>NIST SURF</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -13850,20 +13968,24 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>https://reufinder.com/programs-for-freshmen/</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr"/>
+          <t>https://www.nist.gov/surf</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-30: 'only open to U.S. citizens and U.S. permanent residents enrolled as undergraduate students at U.S. colleges or universities'; states no class-year minimum. 11 weeks, $710/week plus lodging/travel allowance. Information Technology Lab has math/CS/ML projects.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sandia-students</t>
+          <t>Already watched by nsa-students</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Sandia National Laboratories student internships</t>
+          <t>NSA student programs</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -13878,61 +14000,61 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
+          <t>https://www.intelligencecareers.gov/nsa/students</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate and graduate internships across Sandia's sites.</t>
+          <t>NSA's student internship and co-op listings on intelligencecareers.gov. Security clearance means US citizens only.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Already watched by scudem</t>
+          <t>Already watched by nuft-2027</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>SCUDEM XI 2026</t>
+          <t>NUFT 2027 Quant Internships</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/scudem/index.html</t>
+          <t>https://github.com/northwesternfintech/2027QuantInternships</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
+          <t>47 firms. No class-year tags - use as a firm checklist and open each careers page yourself.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Already watched by seo-tech</t>
+          <t>Already watched by open-source-quantitative-finance</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>SEO Tech Developer + First-Year Academy</t>
+          <t>Open Source Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -13942,29 +14064,29 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>https://tech.seo-usa.org/</t>
+          <t>https://osqf.org/</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
+          <t>Open-source quant finance conference, free per the article. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify format and whether students may attend.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Already watched by sfi-ucr</t>
+          <t>Already watched by optiver-futurefocus</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>SFI Undergraduate Complexity Research</t>
+          <t>Optiver FutureFocus Chicago 2026</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -13974,61 +14096,57 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
+          <t>https://optiver.com/recruitment-events/futurefocus-chicago</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
+          <t>Optiver's US (Chicago) student recruitment event. The other FutureFocus and Career Kickstarter events are ANZ, China, Singapore, India and Europe - see the consolidated non-US row. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Already watched by simplify-2027</t>
+          <t>Already watched by optiver-ready-trader</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>SimplifyJobs Summer 2027 Internships</t>
+          <t>Optiver Ready Trader Go</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>LOW VALUE</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
-        </is>
-      </c>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Already watched by smart-scholarship</t>
+          <t>Already watched by purdue-srop</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>SMART Scholarship</t>
+          <t>Purdue Summer Research Opportunities Program (SROP)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -14038,61 +14156,61 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>https://www.smartscholarship.org/smart</t>
+          <t>https://www.purdue.edu/academics/ogsps/ogrs/summer-research-opportunity-program/</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
+          <t>Part of the Big Ten Academic Alliance SROP. Page states eligibility includes US citizens, permanent residents, refugees and asylees enrolled at a US institution; read the full criteria on the page.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Already watched by stevens-high-frequency-trading</t>
+          <t>Already watched by ramp-ashby</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Stevens High Frequency Trading Competition 2026</t>
+          <t>Ramp Emerging Talent</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
+          <t>https://ramp.com/emerging-talent</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
+          <t>Verified 2026-09-30: 'For interns: anyone who will be registered in an accredited 4 year university post-internship.' Fintech SWE internships posted on Ashby 'ramp'.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Already watched by surim-apply</t>
+          <t>Already watched by reufinder-freshmen</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Stanford SURIM</t>
+          <t>REU Finder - freshman-eligible filter</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -14102,29 +14220,25 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>https://mathematics.stanford.edu/</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
-        </is>
-      </c>
+          <t>https://reufinder.com/programs-for-freshmen/</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Already watched by treehacks</t>
+          <t>Already watched by sandia-students</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>TreeHacks</t>
+          <t>Sandia National Laboratories student internships</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -14134,29 +14248,29 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>https://treehacks.com/</t>
+          <t>https://www.sandia.gov/careers/careers/students-and-postdocs/</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
+          <t>Undergraduate and graduate internships across Sandia's sites.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Already watched by twosigma-campus</t>
+          <t>Already watched by scudem</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma New Seekers Summit</t>
+          <t>SCUDEM XI 2026</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -14166,88 +14280,88 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/new-seekers-summit/</t>
+          <t>https://www.contest.comap.com/scudem/index.html</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
+          <t>Verified 2026-09-30: COMAP's differential-equations modelling challenge. FAQ: 'open to teams of 3 undergraduate or high school students. Each team must have a coach (typically a faculty member or instructor).' Ends in a 10-minute video judged by at least 3 judges. Needs a faculty coach.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Already watched by uchicago-trading-competition</t>
+          <t>Already watched by seo-tech</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>UChicago Trading Competition</t>
+          <t>SEO Tech Developer + First-Year Academy</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>https://tradingcompetition.uchicago.edu/</t>
+          <t>https://tech.seo-usa.org/</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
+          <t>Verified 2026-09-26: 'Enrolled as a sophomore'; the Academy is for 'first-year college students'. Page says 'All are welcome to apply'; SEO is a diversity organisation, so confirm eligibility by hand.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Already watched by underclassmen-cruz</t>
+          <t>Already watched by sfhacks</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>underclassmen-opportunities (Cruz-Lopez)</t>
+          <t>SF Hacks</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>USE WEEKLY</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
+          <t>https://www.sfhacks.io/</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
+          <t>Verified 2026-10-08: 'All students are welcome, from high school through university.' 'We are not offering travel reimbursements this year.' San Francisco.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Already watched by usc-ict-summer</t>
+          <t>Already watched by sfi-ucr</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>USC ICT Summer Research Program</t>
+          <t>SFI Undergraduate Complexity Research</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -14262,56 +14376,56 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>https://ict.usc.edu/careers/internships/summer-research-program-application/</t>
+          <t>https://www.santafe.edu/engage/learn/programs/undergraduate-complexity-research</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>USC Institute for Creative Technologies summer research programme.</t>
+          <t>Verified 2026-09-26: 'for current undergraduate students. Prior research experience is not required'; 'return to this page in November 2026'.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Already watched by worldquant-iqc</t>
+          <t>Already watched by simplify-2027</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>WorldQuant IQC / BRAIN</t>
+          <t>SimplifyJobs Summer 2027 Internships</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>https://www.worldquant.com/brain/iqc/</t>
+          <t>https://github.com/SimplifyJobs/Summer2027-Internships</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
+          <t>613 roles, 94 quant, but no class-year tagging and almost all target penultimate-year students.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Already watched by yutc</t>
+          <t>Already watched by sjhacks</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Yale Undergraduate Trading Competition</t>
+          <t>SJHacks</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -14319,31 +14433,31 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>https://www.yale.edu/</t>
+          <t>https://www.sjhacks.com/</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
+          <t>Verified 2026-10-08: 'SJHacks is a 24-hour in-person hackathon at San Jose State University'; 2026 edition April 25-26 at Guildhouse, San Jose. The page states no eligibility rule and nothing about travel.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by smart-scholarship</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Bank of America APAC Quant Conference</t>
+          <t>SMART Scholarship</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -14351,255 +14465,255 @@
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>https://www.bofa.com/</t>
+          <t>https://www.smartscholarship.org/smart</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-09-26: scholarship-for-service - requires civilian employment with the Department of War after graduation. 'open annually from August 1 to the first Friday in December'.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by stevens-high-frequency-trading</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Rising Fellows</t>
+          <t>Stevens High Frequency Trading Competition 2026</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/risingfellowsprogram</t>
+          <t>https://www.stevens.edu/page-basic/2026-stevens-high-frequency-trading-competition</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
+          <t>HFT-focused student competition at Stevens Institute (Hoboken NJ). Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Directly relevant to quant dev; verify class-year eligibility.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by surim-apply</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>CQA Young Professionals Event</t>
+          <t>Stanford SURIM</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+          <t>https://mathematics.stanford.edu/</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>8 weeks, $8,500 + up to $1,500 need-based. Needs MATH 56/61CM/61DM/110/113/115 first, and 2 letters (1 from Stanford Math). | Checked 2026-09-26: SURIM has its own page at surim.stanford.edu/apply-surim, which is watched; the listed mathematics.stanford.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by treehacks</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Citadel Securities Ignite</t>
+          <t>TreeHacks</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
+          <t>https://treehacks.com/</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Invite-only weeklong program for sophomore women.</t>
+          <t>Verified 2026-09-26: 'open to any enrolled college student'; Stanford students get priority by the priority deadline.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by twosigma-campus</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Coding it Forward - Civic Digital Fellowship</t>
+          <t>Two Sigma New Seekers Summit</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>https://www.codingitforward.com/fellowship</t>
+          <t>https://www.twosigma.com/new-seekers-summit/</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
+          <t>Verified 2026-09-30: 'gives first-and second-year undergraduates the opportunity to delve into the world of Data Scientists and Quantitative Researchers.' QR seminars, networking, interview prep. www.twosigma.com is WP Engine, which 403s the Actions runner, so it is not watched as page_text; the posting should appear on twosigma-campus (Avature).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by uchicago-trading-competition</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Discovery Fellowship</t>
+          <t>UChicago Trading Competition</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://tradingcompetition.uchicago.edu/</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>PRIORITY TO TEAMS WITHOUT PRIOR TRADING WORK EXPERIENCE - structurally favors freshmen. April event, $15k+ prizes.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by underclassmen-cruz</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Latitude Fellowship</t>
+          <t>underclassmen-opportunities (Cruz-Lopez)</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>USE WEEKLY</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://github.com/Jose-Gael-Cruz-Lopez/underclassmen-opportunities</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Better maintained than zapplyjobs, with open/closing-soon flags. Heavy on ambassador programs - filter hard.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by usc-ict-summer</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw London Insight Programme</t>
+          <t>USC ICT Summer Research Program</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Research / math</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/additional-experiences</t>
+          <t>https://ict.usc.edu/careers/internships/summer-research-program-application/</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
+          <t>USC Institute for Creative Technologies summer research programme.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by worldquant-iqc</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Momentum Fellowship</t>
+          <t>WorldQuant IQC / BRAIN</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -14607,63 +14721,63 @@
           <t>Quant firm program</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://www.worldquant.com/brain/iqc/</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Teams of 1-4 from one university. $100k pool. Solo entry allowed. Huge field (140k+ registrations) so mid-table means little.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yhack</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Databento partner quant events (Shanghai, London)</t>
+          <t>YHack</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>https://databento.com/</t>
+          <t>https://www.yhack.org/</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Verified 2026-10-08: 'Accepted participants will have the opportunity to apply for travel reimbursement. We expect to be able to support many participants traveling from the East Coast, with additional consideration given' beyond it. Yale.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>You cannot apply (NO)</t>
+          <t>Already watched by yutc</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
+          <t>Yale Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -14671,19 +14785,19 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>https://en.tmtpost.com/post/7752441</t>
+          <t>https://www.yale.edu/</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$10,000+ in prizes, nationwide. | Checked 2026-09-26: the competition's own site is yutc.org (a JavaScript page, watched with render_js); the listed yale.edu is kept.</t>
         </is>
       </c>
     </row>
@@ -14695,12 +14809,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>IMC EU Business Course</t>
+          <t>Bank of America APAC Quant Conference</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -14710,12 +14824,12 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
+          <t>https://www.bofa.com/</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - APAC, May 20 2026. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14841,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>IMC UK Masterclass</t>
+          <t>Bridgewater Rising Fellows</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -14742,12 +14856,12 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/</t>
+          <t>https://www.bridgewater.com/risingfellowsprogram</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Geographic exclusion - excludes US-based students.</t>
+          <t>CORRECTED: first-year eligible BUT targets backgrounds underrepresented in the industry, recruiting via HBCUs, O4U, BLK Capital, Prep for Prep. | Checked 2026-09-26: now redirects to the generic /working-at-bridgewater page. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -14759,12 +14873,12 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>IMC WiT (Women in Technology)</t>
+          <t>CQA Young Professionals Event</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -14774,10 +14888,14 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>https://careers.imc.com/us/en/student-opportunities</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr"/>
+          <t>https://cqa.org/upcoming-events-cqa-young-professional</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - for working professionals, not undergraduates. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -14787,7 +14905,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>IMC Women in Trading and Engineering</t>
+          <t>Citadel Securities Ignite</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -14802,12 +14920,12 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
+          <t>https://www.citadelsecurities.com/careers/programs-and-events/</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Invite-only weeklong program for sophomore women.</t>
         </is>
       </c>
     </row>
@@ -14819,12 +14937,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Data for Good Hackathon</t>
+          <t>Coding it Forward - Civic Digital Fellowship</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -14834,12 +14952,12 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://www.codingitforward.com/fellowship</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>That is a junior-year window; a first-year does not qualify.</t>
+          <t>TRAP - appears on most underclassmen lists but 2026 required graduating May 2025-Dec 2027. Diary for junior year.</t>
         </is>
       </c>
     </row>
@@ -14851,7 +14969,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Jane Street FOCUS and IN FOCUS</t>
+          <t>D. E. Shaw Discovery Fellowship</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -14866,12 +14984,12 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -14883,7 +15001,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Graduate Research Fellowship</t>
+          <t>D. E. Shaw Latitude Fellowship</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -14898,10 +15016,14 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr"/>
+          <t>https://campus.deshaw.com/fellowships</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -14911,7 +15033,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Jane Street INSIGHT</t>
+          <t>D. E. Shaw London Insight Programme</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -14926,12 +15048,12 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+          <t>https://campus.deshaw.com/additional-experiences</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>For women, transgender and gender-expansive people.</t>
+          <t>Ruled out on geography - London. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. | Checked 2026-09-26: campus.deshaw.com/additional-experiences now redirects to the campus root (which lists London Insight as closed). Kept.</t>
         </is>
       </c>
     </row>
@@ -14943,7 +15065,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Jane Street JSIP</t>
+          <t>D. E. Shaw Momentum Fellowship</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -14958,12 +15080,12 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
+          <t>Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
@@ -14975,12 +15097,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Jane Street Visiting Researcher / Prefaculty</t>
+          <t>Databento partner quant events (Shanghai, London)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -14990,10 +15112,14 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr"/>
+          <t>https://databento.com/</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Consolidated row for the Databento events with Nasdaq/Bank of America (Shanghai, May 21 2026), Google (London, June 2026) and Man Group (London, June 2026). Ruled out on geography. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -15003,12 +15129,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Jane Street WiSE</t>
+          <t>Global Crypto Quant Competition and Digital Asset Forum Hong Kong 2026</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -15018,12 +15144,12 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+          <t>https://en.tmtpost.com/post/7752441</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Women / trans / gender-expansive students.</t>
+          <t>Ruled out on geography - Hong Kong. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -15035,12 +15161,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>KNHack 2026 Research Challenge (Mexico)</t>
+          <t>IMC EU Business Course</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
@@ -15050,12 +15176,12 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>https://kaxanuk.mx/kn-hack</t>
+          <t>https://www.imc.com/eu/careers/students-graduates/programs/business-course</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out on geography - EU. The US Launchpad program is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15193,12 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MIT Pokerbots</t>
+          <t>IMC UK Masterclass</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -15082,12 +15208,12 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>https://pokerbots.org/</t>
+          <t>https://careers.imc.com/</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+          <t>Geographic exclusion - excludes US-based students.</t>
         </is>
       </c>
     </row>
@@ -15099,12 +15225,12 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Meta University</t>
+          <t>IMC WiT (Women in Technology)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -15112,16 +15238,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
-        </is>
-      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.imc.com/us/en/student-opportunities</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -15131,7 +15253,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Optiver Career Kickstarter: Women in Tech</t>
+          <t>IMC Women in Trading and Engineering</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -15146,7 +15268,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
+          <t>https://www.imc.com/ap/careers/students-graduates/programs/womens-talent</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -15163,12 +15285,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Optiver Quantitative Intern Summer 2027</t>
+          <t>JPMorgan Data for Good Hackathon</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
@@ -15178,12 +15300,12 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Highest pay in the industry, but a first-year is too early.</t>
+          <t>That is a junior-year window; a first-year does not qualify.</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15317,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Optiver regional recruitment events (non-US)</t>
+          <t>Jane Street FOCUS and IN FOCUS</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -15210,12 +15332,12 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>https://optiver.com/recruitment-events/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Barriers-to-access criteria (first-gen, Pell-eligible, under-resourced school). Read criteria yourself.</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15349,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>PEAK6 Trading Bootcamp</t>
+          <t>Jane Street Graduate Research Fellowship</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -15242,14 +15364,10 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>https://peak6.com/campus/</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
-        </is>
-      </c>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -15259,12 +15377,12 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Palantir Path</t>
+          <t>Jane Street INSIGHT</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -15272,12 +15390,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/insight/</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>For women, transgender and gender-expansive people.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -15287,7 +15409,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Point72 Academy</t>
+          <t>Jane Street JSIP</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -15302,12 +15424,12 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>https://point72.com/point72-academy/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/jsip/</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+          <t>Multi-week paid NYC program, $12,500 scholarship - but requires having experienced barriers to access in CS. | Checked 2026-09-26: now redirects to the programs-and-events index, which does not list JSIP. Kept: it may reopen for the next cycle.</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15441,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+          <t>Jane Street Visiting Researcher / Prefaculty</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -15334,7 +15456,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
@@ -15347,7 +15469,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma College Mentor Connect</t>
+          <t>Jane Street WiSE</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -15362,12 +15484,12 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>6-week remote mentorship on open-source projects.</t>
+          <t>Women / trans / gender-expansive students.</t>
         </is>
       </c>
     </row>
@@ -15379,12 +15501,12 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+          <t>KNHack 2026 Research Challenge (Mexico)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -15394,10 +15516,14 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr"/>
+          <t>https://kaxanuk.mx/kn-hack</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on geography - Mexico. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -15407,12 +15533,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma PhD Fellowship</t>
+          <t>MIT Pokerbots</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -15422,10 +15548,14 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr"/>
+          <t>https://pokerbots.org/</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Must be able to register for MIT IAP classes; a team member needs MIT certificates for the competition server.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -15435,12 +15565,12 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Virtu Financial Women's Winternship</t>
+          <t>Meta University</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -15448,12 +15578,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>https://www.virtu.com/careers/</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr"/>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Discontinued with no replacement. Ignore any list that still includes it.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -15463,12 +15597,12 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Wharton Global High School Investment Competition</t>
+          <t>Optiver Career Kickstarter: Women in Tech</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -15478,12 +15612,12 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/8177160002</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
         </is>
       </c>
     </row>
@@ -15495,12 +15629,12 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance Americas Conference</t>
+          <t>Optiver Quantitative Intern Summer 2027</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -15510,12 +15644,12 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/wqfa</t>
+          <t>https://optiver.com/working-at-optiver/career-opportunities/</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Highest pay in the industry, but a first-year is too early.</t>
         </is>
       </c>
     </row>
@@ -15527,12 +15661,12 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Women in Quantitative Finance London Conference</t>
+          <t>Optiver regional recruitment events (non-US)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
@@ -15542,49 +15676,381 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+          <t>https://optiver.com/recruitment-events/</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+          <t>Consolidated row for the ANZ, China, Singapore, India, Amsterdam and Catalunya FutureFocus / Career Kickstarter / masterclass events. Ruled out on geography; the Chicago event is tracked separately. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>PEAK6 Trading Bootcamp</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>https://peak6.com/campus/</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>One week, $25-31.25/hr, two sessions (May and Aug).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Palantir Path</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Point72 Academy</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>https://point72.com/point72-academy/</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>NOT an underclassman program. 10-month paid post-grad program, $125k base. 2027 class wants Dec 2026-Jul 2027 grads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>SIG Sophomore Discovery Days for Women (all tracks)</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma College Mentor Connect</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>6-week remote mentorship on open-source projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma Diversity Undergraduate Scholarship</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Two Sigma PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twosigma.com/graduate-students/phd-fellowships/</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Virtu Financial Women's Winternship</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.virtu.com/careers/</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Wharton Global High School Investment Competition</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>https://globalyouth.wharton.upenn.edu/competitions/investment-competition</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out on stage - high school students only. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance Americas Conference</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/wqfa</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>You cannot apply (NO)</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Women in Quantitative Finance London Conference</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wbstraining.com/events/london-wqf-conference</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Ruled out by an identity gate: this program is for women. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Listed here so it is not re-researched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
           <t>You cannot apply (STALE)</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>zapplyjobs underclassmen-internships</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="D134" s="8" t="inlineStr">
         <is>
           <t>STALE</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>https://github.com/zapplyjobs/underclassmen-internships</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>Right shape, but entries and links are out of date.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F123"/>
+  <autoFilter ref="A1:F134"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -15692,20 +16158,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/programs.xlsx
+++ b/out/programs.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Left Out" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Check By Hand'!$A$1:$G$205</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual Watch'!$A$1:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Priority'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Left Out'!$A$1:$F$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>NASA JPL internships</t>
+          <t>Caltech SURF</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpl.nasa.gov/edu/internships/</t>
+          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched; check by hand.</t>
+          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>NASA-Caltech JPL SURF</t>
+          <t>NASA JPL internships</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://www.jpl.nasa.gov/edu/intern/apply/caltech-summer-undergraduate-research-fellowship/</t>
+          <t>https://www.jpl.nasa.gov/edu/internships/</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>SURF projects hosted at JPL. jpl.nasa.gov returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
+          <t>Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched; check by hand.</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Princeton summer research programs (non-Princeton undergraduates)</t>
+          <t>NASA-Caltech JPL SURF</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>https://undergraduateresearch.princeton.edu/programs/summer-programs</t>
+          <t>https://www.jpl.nasa.gov/edu/intern/apply/caltech-summer-undergraduate-research-fellowship/</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Princeton's directory of summer research programmes; filterable by eligibility for non-Princeton students and by class year. | 2026-10-01: probed HTTP 200, then HTTP 403 from Cloudflare to the tracker's client minutes later, so it is not watched; check by hand.</t>
+          <t>SURF projects hosted at JPL. jpl.nasa.gov returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: DIAMONDS: Directed, Intensive and Mentored Opportunities in Data Science (Tufts University)</t>
+          <t>Princeton summer research programs (non-Princeton undergraduates)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -4014,22 +4014,22 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Most REU sites open Dec-Feb; check the site</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547822</t>
+          <t>https://undergraduateresearch.princeton.edu/programs/summer-programs</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2547822, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>Princeton's directory of summer research programmes; filterable by eligibility for non-Princeton students and by class year. | 2026-10-01: probed HTTP 200, then HTTP 403 from Cloudflare to the tracker's client minutes later, so it is not watched; check by hand.</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: Research Experience for Undergraduates in Translational Applications of AI to Engineering (REU-TrACE) (Iowa State University)</t>
+          <t>REU SITE: DIAMONDS: Directed, Intensive and Mentored Opportunities in Data Science (Tufts University)</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447479</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547822</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447479, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547822, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: Research in Consumer Networking Technologies (University of Missouri-Columbia)</t>
+          <t>REU SITE: Research Experience for Undergraduates in Translational Applications of AI to Engineering (REU-TrACE) (Iowa State University)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548100</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447479</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548100, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447479, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>REU SITE: WAVE SURF: Workforce Advancement in Verification and Emulation of Semiconductor Chips -- Undergraduate Research Fellowships (Texas A&amp;M Engineering Experiment Station)</t>
+          <t>REU SITE: Research in Consumer Networking Technologies (University of Missouri-Columbia)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548388</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548100</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548388, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548100, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>REU Site Renewal: Enhancing AI-Driven Insights Within IoT-Enabled Ecosystems (AIoT-Sys) (University of California-Irvine)</t>
+          <t>REU SITE: WAVE SURF: Workforce Advancement in Verification and Emulation of Semiconductor Chips -- Undergraduate Research Fellowships (Texas A&amp;M Engineering Experiment Station)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447884</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548388</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447884, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548388, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>REU Site in Software Engineering (REUSE) at Carnegie Mellon University (Carnegie Mellon University)</t>
+          <t>REU Site Renewal: Enhancing AI-Driven Insights Within IoT-Enabled Ecosystems (AIoT-Sys) (University of California-Irvine)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447499</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447884</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447499, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447884, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>REU Site: AI Research for Intelligent Systems and Efficiency (University of Arizona)</t>
+          <t>REU Site in Software Engineering (REUSE) at Carnegie Mellon University (Carnegie Mellon University)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548190</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447499</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548190, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447499, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>REU Site: AI and Science Summer Lab: advancing AI-enabled scientific discovery across the physical and biological sciences (University of Chicago)</t>
+          <t>REU Site: AI Research for Intelligent Systems and Efficiency (University of Arizona)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447314</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548190</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447314, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548190, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Access to Inquiry in Mathematics Undergraduate Program (University of Wisconsin-Milwaukee)</t>
+          <t>REU Site: AI and Science Summer Lab: advancing AI-enabled scientific discovery across the physical and biological sciences (University of Chicago)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447752</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447314</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447752, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447314, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Advancing high-performance computing opportunities in undergraduate research at UW-Eau Claire to meet challenges of multidisciplinary computational science (University of Wisconsin-Eau Claire)</t>
+          <t>REU Site: Access to Inquiry in Mathematics Undergraduate Program (University of Wisconsin-Milwaukee)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447779</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447752</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447779, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447752, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Agile AI Research for Safety Critical Systems (Embry-Riddle Aeronautical University)</t>
+          <t>REU Site: Advancing high-performance computing opportunities in undergraduate research at UW-Eau Claire to meet challenges of multidisciplinary computational science (University of Wisconsin-Eau Claire)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548167</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447779</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548167, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447779, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Algebra, Combinatorics, and Statistics (Texas State University - San Marcos)</t>
+          <t>REU Site: Agile AI Research for Safety Critical Systems (Embry-Riddle Aeronautical University)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447229</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548167</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447229, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548167, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Algorithms in Data Science with Applications (Montana State University)</t>
+          <t>REU Site: Algebra, Combinatorics, and Statistics (Texas State University - San Marcos)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548411</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447229</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548411, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447229, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Artificial Intelligence for Advanced Applications (Worcester Polytechnic Institute)</t>
+          <t>REU Site: Algorithms in Data Science with Applications (Montana State University)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349370</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548411</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2349370, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548411, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Computing Research in Unmanned Aerial Systems (Texas A&amp;M University Corpus Christi)</t>
+          <t>REU Site: Applied Artificial Intelligence for Advanced Applications (Worcester Polytechnic Institute)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447596</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349370</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447596, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349370, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Mathematics in Real World Problems (Florida State University)</t>
+          <t>REU Site: Applied Computing Research in Unmanned Aerial Systems (Texas A&amp;M University Corpus Christi)</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349382</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447596</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2349382, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447596, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied Research in Deep Learning (Missouri State University)</t>
+          <t>REU Site: Applied Mathematics in Real World Problems (Florida State University)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548161</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349382</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548161, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2349382, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applied and Computational Mathematics (University of California-Los Angeles)</t>
+          <t>REU Site: Applied Research in Deep Learning (Missouri State University)</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548181</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548161</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548181, funded through 11/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548161, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Applying Data Science on Energy-efficient Cluster Systems and Applications (The University Corporation, Northridge)</t>
+          <t>REU Site: Applied and Computational Mathematics (University of California-Los Angeles)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548509</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548181</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548509, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548181, funded through 11/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Artificial Intelligence for Computational Creativity (Brown University)</t>
+          <t>REU Site: Applying Data Science on Energy-efficient Cluster Systems and Applications (The University Corporation, Northridge)</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447190</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548509</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447190, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548509, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Artificial Intelligence, Security, and Privacy (Northwestern University at Chicago)</t>
+          <t>REU Site: Artificial Intelligence for Computational Creativity (Brown University)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447155</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447190</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447155, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447190, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>REU Site: CNS: Sensing and Smart Systems (Florida Atlantic University)</t>
+          <t>REU Site: Artificial Intelligence, Security, and Privacy (Northwestern University at Chicago)</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447437</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447155</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447437, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447155, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Combinatorics, Algorithms, and AI applied to Real Problems (CAAR) (University of Maryland, College Park)</t>
+          <t>REU Site: CNS: Sensing and Smart Systems (Florida Atlantic University)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447466</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447437</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447466, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447437, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational Methods for Understanding Music, Media and Minds (University of Rochester)</t>
+          <t>REU Site: Combinatorics, Algorithms, and AI applied to Real Problems (CAAR) (University of Maryland, College Park)</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447607</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447466</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447607, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447466, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational Number Theory (Clemson University)</t>
+          <t>REU Site: Computational Methods for Understanding Music, Media and Minds (University of Rochester)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349174</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447607</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2349174, funded through 10/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447607, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational Sensing for Human-centered AI (Rochester Institute of Tech)</t>
+          <t>REU Site: Computational Number Theory (Clemson University)</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445028</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349174</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2445028, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2349174, funded through 10/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computational and Applied Mathematics Program (Cal Poly Pomona Foundation, Inc.)</t>
+          <t>REU Site: Computational Sensing for Human-centered AI (Rochester Institute of Tech)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2348984</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445028</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2348984, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2445028, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Computing and Engineering for Safe and Healthy Digital Environment (New York Institute of Technology)</t>
+          <t>REU Site: Computational and Applied Mathematics Program (Cal Poly Pomona Foundation, Inc.)</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447577</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2348984</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447577, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2348984, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cryptography, Coding Theory and Quantum Computing at the USF (University of South Florida)</t>
+          <t>REU Site: Computing and Engineering for Safe and Healthy Digital Environment (New York Institute of Technology)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548160</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447577</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548160, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447577, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cyberinfrastructure (CI) Research for Societal Advancement REU (University of Texas at Austin)</t>
+          <t>REU Site: Cryptography, Coding Theory and Quantum Computing at the USF (University of South Florida)</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447887</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548160</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447887, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548160, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cybersecurity Research of Unmanned Aerial Vehicles (Embry-Riddle Aeronautical University)</t>
+          <t>REU Site: Cyberinfrastructure (CI) Research for Societal Advancement REU (University of Texas at Austin)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548278</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447887</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548278, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447887, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Cybersecurity in Emerging Technologies (Mississippi State University)</t>
+          <t>REU Site: Cybersecurity Research of Unmanned Aerial Vehicles (Embry-Riddle Aeronautical University)</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447266</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548278</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447266, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548278, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Data Science Across Disciplines (Marquette University)</t>
+          <t>REU Site: Cybersecurity in Emerging Technologies (Mississippi State University)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548034</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447266</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548034, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447266, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Deep Learning for Dynamical Systems in Biological and Physical Sciences (University of Southern Mississippi)</t>
+          <t>REU Site: Data Science Across Disciplines (Marquette University)</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447675</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548034</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447675, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548034, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Digital Forensic Research on Emerging Computing Environments (Virginia Commonwealth University)</t>
+          <t>REU Site: Deep Learning for Dynamical Systems in Biological and Physical Sciences (University of Southern Mississippi)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447453</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447675</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447453, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447675, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>REU Site: EXERCISE - Explore Emerging Computing in Science and Engineering (Salisbury University)</t>
+          <t>REU Site: Digital Forensic Research on Emerging Computing Environments (Virginia Commonwealth University)</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447041</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447453</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447041, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447453, funded through 09/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Engineers for Exploration (University of California-San Diego)</t>
+          <t>REU Site: EXERCISE - Explore Emerging Computing in Science and Engineering (Salisbury University)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548467</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447041</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548467, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447041, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Exploring the FABRIC Research Instrument to Catalyze Multi-disciplinary Research in Networks, Distributed Systems, and Emerging CyberInfrastructure (CI) Applications (University of North Carolina at Chapel Hill)</t>
+          <t>REU Site: Engineers for Exploration (University of California-San Diego)</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447441</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548467</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447441, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548467, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Extremal Graph Theory and Dynamical Systems at RIT (Rochester Institute of Tech)</t>
+          <t>REU Site: Exploring the FABRIC Research Instrument to Catalyze Multi-disciplinary Research in Networks, Distributed Systems, and Emerging CyberInfrastructure (CI) Applications (University of North Carolina at Chapel Hill)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2243938</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447441</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, awards 2243938, 2547942, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447441, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Frontier Technologies for Biometrics and Authentication (SUNY at Buffalo)</t>
+          <t>REU Site: Extremal Graph Theory and Dynamical Systems at RIT (Rochester Institute of Tech)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548357</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2243938</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548357, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, awards 2243938, 2547942, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Hands-On Research in Federated Learning Security through Red Team vs. Blue Team Exercises (University of Nevada Las Vegas)</t>
+          <t>REU Site: Frontier Technologies for Biometrics and Authentication (SUNY at Buffalo)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548041</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548357</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548041, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548357, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Hardware Security (University of South Florida)</t>
+          <t>REU Site: Hands-On Research in Federated Learning Security through Red Team vs. Blue Team Exercises (University of Nevada Las Vegas)</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445849</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548041</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2445849, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548041, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Home Embodied AI and Robot Technology (HEART) Undergraduate Research Experience (Northeastern University)</t>
+          <t>REU Site: Hardware Security (University of South Florida)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548331</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2445849</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548331, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2445849, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Human-AI Interaction and Evaluation in Web and Information Systems (Old Dominion University Research Foundation)</t>
+          <t>REU Site: Home Embodied AI and Robot Technology (HEART) Undergraduate Research Experience (Northeastern University)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548125</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548331</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548125, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548331, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Integrative Challenges in Cybersecurity-Deception, Remediation, and Resilient Systems (SUNY at Albany)</t>
+          <t>REU Site: Human-AI Interaction and Evaluation in Web and Information Systems (Old Dominion University Research Foundation)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548335</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548125</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548335, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548125, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Interdisciplinary Research Experience in Computational Sciences (Louisiana State University)</t>
+          <t>REU Site: Integrative Challenges in Cybersecurity-Deception, Remediation, and Resilient Systems (SUNY at Albany)</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447810</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548335</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447810, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548335, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Knowledge Beyond Language with Vector Embeddings (University of North Texas)</t>
+          <t>REU Site: Interdisciplinary Research Experience in Computational Sciences (Louisiana State University)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548192</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447810</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548192, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447810, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Making Generative Artificial Intelligence Responsible (University of North Texas)</t>
+          <t>REU Site: Knowledge Beyond Language with Vector Embeddings (University of North Texas)</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447834</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548192</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447834, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548192, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Math REU at Kent State (Kent State University)</t>
+          <t>REU Site: Making Generative Artificial Intelligence Responsible (University of North Texas)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2439984</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447834</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2439984, funded through 08/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447834, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Mathematical Analysis and Applications (Regents of the University of Michigan - Dearborn)</t>
+          <t>REU Site: Math REU at Kent State (Kent State University)</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548087</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2439984</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548087, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2439984, funded through 08/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Quantum Information Science and Engineering (University of Washington)</t>
+          <t>REU Site: Mathematical Analysis and Applications (Regents of the University of Michigan - Dearborn)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446908</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548087</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2446908, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548087, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Quantum algorithms and optimization (QAO) (University of Tennessee Knoxville)</t>
+          <t>REU Site: Quantum Information Science and Engineering (University of Washington)</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548084</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446908</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548084, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2446908, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>REU Site: REU@UNO - An REU Site on Security and Artificial Intelligence/Machine Learning for the Internet of Things (University of Nebraska at Omaha)</t>
+          <t>REU Site: Quantum algorithms and optimization (QAO) (University of Tennessee Knoxville)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447289</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548084</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447289, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548084, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research Experience for Undergraduates Intersecting Computing and Evolution (Grand Valley State University)</t>
+          <t>REU Site: REU@UNO - An REU Site on Security and Artificial Intelligence/Machine Learning for the Internet of Things (University of Nebraska at Omaha)</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547922</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447289</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2547922, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447289, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research Experiences for Undergraduates in Discrete and Applied Mathematics (Michigan State University)</t>
+          <t>REU Site: Research Experience for Undergraduates Intersecting Computing and Evolution (Grand Valley State University)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2244461</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547922</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2244461, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547922, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research Experiences for Undergraduates in Mathematics at Indiana University (Indiana University)</t>
+          <t>REU Site: Research Experiences for Undergraduates in Discrete and Applied Mathematics (Michigan State University)</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -6059,12 +6059,12 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447563</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2244461</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447563, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2244461, funded through 08/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Research on Prescriptive Analytics for AI-enabled Operations Engineering (University of Missouri-Columbia)</t>
+          <t>REU Site: Research Experiences for Undergraduates in Mathematics at Indiana University (Indiana University)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548110</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447563</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548110, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447563, funded through 06/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Robotics and Autonomous Systems (University of Southern California)</t>
+          <t>REU Site: Research on Prescriptive Analytics for AI-enabled Operations Engineering (University of Missouri-Columbia)</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447397</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548110</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447397, funded through 11/30/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548110, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Robots in the Real World (Oregon State University)</t>
+          <t>REU Site: Robotics and Autonomous Systems (University of Southern California)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349747</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447397</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2349747, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447397, funded through 11/30/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>REU Site: SRAII: Safe and Reliable AI and the Internet (University of Southern California)</t>
+          <t>REU Site: Robots in the Real World (Oregon State University)</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447729</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349747</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447729, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349747, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Statistical Mathematics and Research Training (SMART) (Marist College)</t>
+          <t>REU Site: SRAII: Safe and Reliable AI and the Internet (University of Southern California)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447324</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447729</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447324, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447729, funded through 07/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Summer Program for Interdisciplinary Research and Education-Emerging Interface Technologies (Iowa State University)</t>
+          <t>REU Site: Statistical Mathematics and Research Training (SMART) (Marist College)</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547899</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447324</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2547899, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447324, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Summer Undergraduate Mathematics Research at Kansas State University (SUMaR at K-State) (Kansas State University)</t>
+          <t>REU Site: Summer Program for Interdisciplinary Research and Education-Emerging Interface Technologies (Iowa State University)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548038</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2547899</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548038, funded through 07/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2547899, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Summer Undergraduate Research Experience (SURE) at Illinois Tech (Illinois Institute of Technology)</t>
+          <t>REU Site: Summer Undergraduate Mathematics Research at Kansas State University (SUMaR at K-State) (Kansas State University)</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548498</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548038</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548498, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548038, funded through 07/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Technologies for Community-Driven Design (University of California-San Diego)</t>
+          <t>REU Site: Summer Undergraduate Research Experience (SURE) at Illinois Tech (Illinois Institute of Technology)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447548</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548498</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447548, funded through 06/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548498, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>REU Site: The Face and Mind of Artificial Intelligence (University of Southern California)</t>
+          <t>REU Site: Technologies for Community-Driven Design (University of California-San Diego)</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446866</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447548</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2446866, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447548, funded through 06/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>REU Site: The future of discovery: training students to build and apply open-source machine learning models and tools (University of Illinois at Urbana-Champaign)</t>
+          <t>REU Site: The Face and Mind of Artificial Intelligence (University of Southern California)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447843</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2446866</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447843, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2446866, funded through 05/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Trustworthy AI (Rochester Institute of Tech)</t>
+          <t>REU Site: The future of discovery: training students to build and apply open-source machine learning models and tools (University of Illinois at Urbana-Champaign)</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447631</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447843</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447631, funded through 12/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447843, funded through 01/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Trustworthy AI and Security for Intelligent Vehicles and Transportation Systems (University of Alabama Tuscaloosa)</t>
+          <t>REU Site: Trustworthy AI (Rochester Institute of Tech)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548476</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447631</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548476, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447631, funded through 12/31/2027. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>REU Site: UT Rio Grande Valley REU Program on Applied Mathematics and Computational and Data Science (AMCADS) (The University of Texas Rio Grande Valley)</t>
+          <t>REU Site: Trustworthy AI and Security for Intelligent Vehicles and Transportation Systems (University of Alabama Tuscaloosa)</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447683</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548476</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2447683, funded through 11/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548476, funded through 04/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Computer Research in Cybersecurity and AI (UnCoRe-CyberAI) (Oakland University)</t>
+          <t>REU Site: UT Rio Grande Valley REU Program on Applied Mathematics and Computational and Data Science (AMCADS) (The University of Texas Rio Grande Valley)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349663</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447683</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2349663, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2447683, funded through 11/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research  in Data Analytics (REU:URDA) (Marshall University Research Corporation)</t>
+          <t>REU Site: Undergraduate Computer Research in Cybersecurity and AI (UnCoRe-CyberAI) (Oakland University)</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447660</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2349663</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447660, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2349663, funded through 02/29/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research Experience in Edge Intelligence (Board of Regents, NSHE, obo University of Nevada, Reno)</t>
+          <t>REU Site: Undergraduate Research  in Data Analytics (REU:URDA) (Marshall University Research Corporation)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548395</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447660</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2548395, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447660, funded through 04/30/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research Experiences in Artificial Intelligence, Data Analytics, and Mixed Reality for Smart and Connected Health (Texas State University - San Marcos)</t>
+          <t>REU Site: Undergraduate Research Experience in Edge Intelligence (Board of Regents, NSHE, obo University of Nevada, Reno)</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447856</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548395</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Computer and Information Science (CISE), award 2447856, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2548395, funded through 09/30/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>REU Site: Undergraduate Research in the Mathematical Sciences and their Applications (Texas A&amp;M University)</t>
+          <t>REU Site: Undergraduate Research Experiences in Artificial Intelligence, Data Analytics, and Mixed Reality for Smart and Connected Health (Texas State University - San Marcos)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548033</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2447856</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>NSF REU Site, Mathematical Sciences, award 2548033, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
+          <t>NSF REU Site, Computer and Information Science (CISE), award 2447856, funded through 03/31/2028. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>UC Davis GREAT program</t>
+          <t>REU Site: Undergraduate Research in the Mathematical Sciences and their Applications (Texas A&amp;M University)</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -6789,22 +6789,22 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Most REU sites open Dec-Feb; check the site</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Undergraduates (see page)</t>
+          <t>Undergraduates; NSF-funded places require US citizenship or permanent residency</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>https://great.ucdavis.edu/</t>
+          <t>https://www.nsf.gov/awardsearch/showAward?AWD_ID=2548033</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>Global Research Experience in Advanced Technologies. Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
+          <t>NSF REU Site, Mathematical Sciences, award 2548033, funded through 08/31/2029. Added 2026-10-01 from NSF's Award Search API (the nsf-reu-sites watcher reports new sites from here on). The award page names the PI and usually links the site's own page, which states the class-year rule and deadline.</t>
         </is>
       </c>
     </row>
@@ -6816,32 +6816,32 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+          <t>UC Davis GREAT program</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>'approximately 30 degree-seeking credits'</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>https://spcs.stanford.edu/jobs</t>
+          <t>https://great.ucdavis.edu/</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+          <t>Global Research Experience in Advanced Technologies. Returned HTTP 403 to the tracker's client on 2026-10-01, so it is not watched.</t>
         </is>
       </c>
     </row>
@@ -6853,12 +6853,12 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg First Year Insights</t>
+          <t>USC ICT Summer Research Program</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -6868,140 +6868,140 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>First-years (unverified)</t>
+          <t>Undergraduates (see page)</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/company/careers/</t>
+          <t>https://ict.usc.edu/careers/internships/summer-research-program-application/</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+          <t>USC Institute for Creative Technologies summer research programme.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Stanford Pre-Collegiate Studies jobs (SUMaC RC / TA)</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>'approximately 30 degree-seeking credits'</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>https://spcs.stanford.edu/jobs</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Verified 2026-09-26: RC posting needs 'completion of approximately 30 degree-seeking credits ... majoring in mathematics or ... advanced coursework' - probably met by spring of first year, confirm by hand. The Instructional Assistant posting returned 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg First Year Insights</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>First-years (unverified)</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>Found 2026-09-26 on university early-insight lists. Every bloomberg.com/company path returns 403 to this client; bloomberg.avature.net is the experienced-hire board with no student postings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
           <t>VIA CLUB</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
         <is>
           <t>Rotman International Trading Competition</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Fall, via your university</t>
         </is>
       </c>
-      <c r="E175" s="3" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>University-sponsored team</t>
         </is>
       </c>
-      <c r="F175" s="4" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>https://www.rotman.utoronto.ca/</t>
         </is>
       </c>
-      <c r="G175" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>40+ universities, RIT Market Simulator. Entry runs through Traders @ Stanford, not by individual application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED - too early</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>NISA Investment Advisors - Intern</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Fall-winter</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>Prefers Winter 2026 / Spring 2027 grads</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.nisa.com/early-careers</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>Edward Jones Internship</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>Local (St. Louis)</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Fall</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>Juniors</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>LATER</t>
+          <t>APPLIED - too early</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Stifel - Institutional Group Internship</t>
+          <t>NISA Investment Advisors - Intern</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>~Nov, rolling per office/desk</t>
+          <t>Fall-winter</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Juniors</t>
+          <t>Prefers Winter 2026 / Spring 2027 grads</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>https://www.stifel.com/careers/internships</t>
+          <t>https://careers.nisa.com/early-careers</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
+          <t>Clayton MO, 10 min from home. Real quant work: Monte Carlo, regression, proprietary modelling. Reapply each cycle.</t>
         </is>
       </c>
     </row>
@@ -7038,32 +7038,32 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
+          <t>Edward Jones Internship</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Winter-spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Rising sophomore+</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>https://www.deshawresearch.com/stemfellowship/</t>
+          <t>https://careers.edwardjones.com/career-areas/students-and-recent-grads/</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
+          <t>10-week program, St. Louis or Tempe.</t>
         </is>
       </c>
     </row>
@@ -7075,32 +7075,32 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>HRT Sophomore Winternship</t>
+          <t>Stifel - Institutional Group Internship</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Local (St. Louis)</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>~Nov, rolling per office/desk</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Juniors</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+          <t>https://www.stifel.com/careers/internships</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>January, 2-4 weeks, Python/C++.</t>
+          <t>9-10 weeks, St. Louis HQ. Prior cycle opened Nov 16.</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
+          <t>D. E. Shaw Research (DESRES) STEM Fellowship</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -7122,22 +7122,22 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
+          <t>Winter-spring</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
+          <t>Rising sophomore+</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+          <t>https://www.deshawresearch.com/stemfellowship/</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+          <t>Open to RISING sophomores - a first-year qualifies in spring 2027. Computational biochemistry entity, not the fund. | Checked 2026-09-26: now redirects to deshawresearch.com/joining.html, which mentions only summer internships. Kept: it may reopen.</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Capital Markets</t>
+          <t>HRT Sophomore Winternship</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -7169,10 +7169,14 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr"/>
+          <t>https://www.hudsonrivertrading.com/student-opportunities/</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>January, 2-4 weeks, Python/C++.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -7182,7 +7186,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Growth Equity</t>
+          <t>Morgan Stanley Investment Management Sophomore Summer Analyst Program - Private Credit &amp; Equity (New York)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -7192,20 +7196,24 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>2027 cycle closed Sep 25 2026; expect the 2028 cycle to open around Aug-Sep 2027</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>2nd year</t>
+          <t>Sophomore - 2027 cycle wanted graduation Dec 2028-Jun 2029</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>https://careers.sig.com/discovery-programs/jobs</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr"/>
+          <t>https://morganstanley.tal.net/vx/candidate/jobboard/vacancy/1/adv/?ftq=Sophomore</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>Right programme, wrong year. The 2027 edition states applicants must 'graduate between December 2028 and June 2029', which is the class of 2029 - a class of 2030 student is a year early. The 2028 edition should target Dec 2029-Jun 2030 and is the one to apply to. Ten weeks from June 2027, New York, on the MSIM Tactical Value team; $36.06/hr. The 2027 deadline was Sep 25 2026 11:55pm ET with a HireVue due Sep 27. Added 2026-09-18 from a pasted link. The website column points at the campus board's keyword search rather than the requisition URL, which dies when the req closes; ?ftq=Sophomore returned exactly this one posting on 2026-09-18. Eligibility read from the reposted job description, not from morganstanley.com, which refuses this tracker's User-Agent - worth re-reading by hand before the 2028 cycle.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
@@ -7215,7 +7223,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology</t>
+          <t>SIG Sophomore Discovery Day - Capital Markets</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -7248,7 +7256,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
+          <t>SIG Sophomore Discovery Day - Growth Equity</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -7281,7 +7289,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>SIG Sophomore Discovery Day - Trading</t>
+          <t>SIG Sophomore Discovery Day - Technology</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -7304,11 +7312,7 @@
           <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>Reports say includes an interview, unlike the freshman event.</t>
-        </is>
-      </c>
+      <c r="G186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -7318,7 +7322,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Two Sigma Undergraduate Scholarship</t>
+          <t>SIG Sophomore Discovery Day - Technology Infrastructure</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -7333,19 +7337,15 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>3rd year of 4-year degree</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>https://www.twosigma.com/undergraduate-students/</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
-        </is>
-      </c>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -7355,32 +7355,32 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Stanford VPUE Major Grant</t>
+          <t>SIG Sophomore Discovery Day - Trading</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Faculty mentor letter due Mar 8, 2027</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Priority to juniors</t>
+          <t>2nd year</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>https://undergradresearch.stanford.edu/</t>
+          <t>https://careers.sig.com/discovery-programs/jobs</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>$8,500 full-time summer. No GPA requirement.</t>
+          <t>Reports say includes an interview, unlike the freshman event.</t>
         </is>
       </c>
     </row>
@@ -7392,49 +7392,49 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Sophomore Experience</t>
+          <t>Two Sigma Undergraduate Scholarship</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Sophomores</t>
+          <t>3rd year of 4-year degree</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
+          <t>https://www.twosigma.com/undergraduate-students/</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
+          <t>Merit-based (resume, transcript, letters). Guarantees a first-round internship interview.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Limex Challenge</t>
+          <t>Berkeley SUPERB-AI4E REU</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -7444,71 +7444,71 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Rising juniors and seniors; US citizens or permanent residents</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>https://challenges.limex.com/</t>
+          <t>https://eecs.berkeley.edu/resources/undergrads/undergraduate-research/superb/</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>NSF REU site in EECS at UC Berkeley. Page states: US citizens or permanent residents who are rising juniors or seniors with some upper-division EECS coursework, so a first-year is not yet eligible.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Quant Tekel QT Funded Elite Trader Competition</t>
+          <t>Stanford VPUE Major Grant</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Faculty mentor letter due Mar 8, 2027</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Priority to juniors</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
+          <t>https://undergradresearch.stanford.edu/</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>$8,500 full-time summer. No GPA requirement.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>LOW VALUE</t>
+          <t>LATER</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Quantegies Global Quant Competition</t>
+          <t>Wells Fargo Sophomore Experience</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Sophomores</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>https://quantegies.com/</t>
+          <t>https://talent.wellsfargojobs.com/flows/sdfp2026</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Found 2026-09-26; formerly the Sophomore Discovery Fellowship. The flow URL returns 403 to this client and the undergraduate programmes page carries no programme text.</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
+          <t>Limex Challenge</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>https://battleofthequants.com/new-york-city-2026</t>
+          <t>https://challenges.limex.com/</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Retail-facing algorithmic trading challenge platform. Not probed; low expected signal. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>CMF Select New York 2026</t>
+          <t>Quant Tekel QT Funded Elite Trader Competition</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>https://global-cmf.com/cmfselectnewyork2026</t>
+          <t>https://qtfunded.quanttekel.com/online-trading-championship</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>A funded-trader / prop-firm style online championship. These are generally marketing funnels for paid evaluations rather than recruiting credentials - weak signal relative to the time. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Future Investment Manager Academy (FIMA)</t>
+          <t>Quantegies Global Quant Competition</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>https://fima.partners/</t>
+          <t>https://quantegies.com/</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Little published detail and not probed during ingest; unclear whether it is a recruiting-relevant competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>FutureAlpha / QuantStrats 2026</t>
+          <t>Battle of the Quants (NYC spring / London fall 2026)</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+          <t>https://battleofthequants.com/new-york-city-2026</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference for allocators and fund managers rather than a student event; typically paid admission. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+          <t>CMF Select New York 2026</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>https://www.qwafafew.org/</t>
+          <t>https://global-cmf.com/cmfselectnewyork2026</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Tapia Conference</t>
+          <t>Future Investment Manager Academy (FIMA)</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -7735,22 +7735,22 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Open, but serves underrepresented groups in computing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>https://tapiaconference.cmd-it.org/</t>
+          <t>https://fima.partners/</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>Open to attend; low relative value for a first-year.</t>
+          <t>Not probed during ingest; unclear format and eligibility. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
         </is>
       </c>
     </row>
@@ -7762,144 +7762,255 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
+          <t>FutureAlpha / QuantStrats 2026</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.alphaevents.com/events-futurealphaglobal</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Industry conference, not a student program. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>QWAFAFEW / QWAFAxNEW chapters</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qwafafew.org/</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Professional quant networking chapters. Open but aimed at practitioners; low signal for a first-year, though a local chapter could be worth one visit. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Tapia Conference</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Open, but serves underrepresented groups in computing</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>https://tapiaconference.cmd-it.org/</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Open to attend; low relative value for a first-year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>LOW VALUE</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
           <t>PwC AI Externship (via Extern)</t>
         </is>
       </c>
-      <c r="C199" s="3" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>Tech internship</t>
         </is>
       </c>
-      <c r="D199" s="3" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="E199" s="3" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="F199" s="4" t="inlineStr">
+      <c r="F202" s="4" t="inlineStr">
         <is>
           <t>https://www.extern.com/pwc-ai-externships</t>
         </is>
       </c>
-      <c r="G199" s="3" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>4 weeks, ~5 hrs/wk, $100 stipend. Aimed at career changers with empty resumes. The in-person PwC AI Workshop ($50) is a cheaper afternoon.</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>Duke Career Hub early-insight table</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E200" s="3" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>First-year/sophomore</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr">
+      <c r="F203" s="4" t="inlineStr">
         <is>
           <t>https://careerhub.students.duke.edu/</t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
         <is>
           <t>Public list of early insight programs by target year.</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>USE</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>Yale 'Gorick's List' for quant trading</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F201" s="4" t="inlineStr">
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>https://ocs.yale.edu/resources/goricks-list-4/</t>
         </is>
       </c>
-      <c r="G201" s="3" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>USE WEEKLY</t>
         </is>
       </c>
-      <c r="B202" s="3" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>OpenQuant job board + newsletter</t>
         </is>
       </c>
-      <c r="C202" s="3" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>Tracker / resource</t>
         </is>
       </c>
-      <c r="D202" s="3" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E202" s="3" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F202" s="4" t="inlineStr">
+      <c r="F205" s="4" t="inlineStr">
         <is>
           <t>https://openquant.co/</t>
         </is>
       </c>
-      <c r="G202" s="3" t="inlineStr">
+      <c r="G205" s="3" t="inlineStr">
         <is>
           <t>Best-maintained source found. See openquant.co/blog/quantitative-finance-events-2026 for the events roundup.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G202"/>
+  <autoFilter ref="A1:G205"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -8099,6 +8210,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId201"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11802,7 +11916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11944,49 +12058,49 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Already watched by berkeley-superb</t>
+          <t>Already watched by berkeley-trading-competition</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Berkeley SUPERB-AI4E REU</t>
+          <t>Berkeley Trading Competition</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://eecs.berkeley.edu/resources/undergrads/undergraduate-research/superb/</t>
+          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>NSF REU site in EECS at UC Berkeley. Page states: US citizens or permanent residents who are rising juniors or seniors with some upper-division EECS coursework, so a first-year is not yet eligible.</t>
+          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Already watched by berkeley-trading-competition</t>
+          <t>Already watched by bny-pre-internship</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Berkeley Trading Competition</t>
+          <t>BNY Freshman Jumpstart</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -11996,24 +12110,24 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://traders.studentorg.berkeley.edu/competition.html</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>West Coast's premier event, $20,000 pool, 45 min from campus. Best convenience-to-value ratio on this list. | Checked 2026-09-26: the listed competition.html URL returns 404; the live page is traders.studentorg.berkeley.edu/competition/, which is what is watched. The listed URL is kept.</t>
+          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bny-pre-internship</t>
+          <t>Already watched by bofa-campus-events</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BNY Freshman Jumpstart</t>
+          <t>Bank of America campus events (Early Insights)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -12021,95 +12135,95 @@
           <t>Conference / other</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/about-us/careers/students/pre-internship.html</t>
+          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Undergraduate first-year students ... with an expected graduation date of December 2029 or May 2030.' Two virtual half-days, business &amp; corporate functions track. Low effort, low depth.</t>
+          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bofa-campus-events</t>
+          <t>Already watched by bridgewater-students</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Bank of America campus events (Early Insights)</t>
+          <t>Bridgewater Investment Immersion Program</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://bankcampuscareers.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo (tal.net) Atom feed of campus events, 18 entries, answers the honest User-Agent. Also available: vacancy/1/feed (152 entries) and a JSON API at careers.bankofamerica.com/services/campusjobssearchservlet.</t>
+          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Already watched by bridgewater-students</t>
+          <t>Already watched by builtin-data-analytics</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater Investment Immersion Program</t>
+          <t>Built In data and analytics internships</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Tracker / resource</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>USE</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://www.bridgewater.com/working-at-bridgewater/students</t>
+          <t>https://builtin.com/jobs/data-analytics/internship</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3 days onsite in Westport. Explicitly 'second year of a 4-year degree'.</t>
+          <t>Front page of Built In's data and analytics internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Already watched by builtin-data-analytics</t>
+          <t>Already watched by builtin-dev-engineering</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Built In data and analytics internships</t>
+          <t>Built In software engineering internships</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -12124,24 +12238,24 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://builtin.com/jobs/data-analytics/internship</t>
+          <t>https://builtin.com/jobs/dev-engineering/internship</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Front page of Built In's data and analytics internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+          <t>Front page of Built In's software engineering internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Already watched by builtin-dev-engineering</t>
+          <t>Already watched by builtin-finance</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Built In software engineering internships</t>
+          <t>Built In finance internships</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -12156,61 +12270,61 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://builtin.com/jobs/dev-engineering/internship</t>
+          <t>https://builtin.com/jobs/finance/internship</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Front page of Built In's software engineering internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+          <t>Front page of Built In's finance internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Already watched by builtin-finance</t>
+          <t>Already watched by calhacks</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Built In finance internships</t>
+          <t>Cal Hacks</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>USE</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://builtin.com/jobs/finance/internship</t>
+          <t>https://www.calhacks.io/</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Front page of Built In's finance internship listings, newest first (about 14-25 cards), watched as a what's-new feed rather than a full list: the site returns HTTP 429 after roughly 70 requests at one a second, so a full crawl is not polite. Measured 2026-10-01 across a deeper crawl: most of its in-field internships were not on Simplify, but many are generic internships at large non-technology employers.</t>
+          <t>Verified 2026-10-08: 'Cal Hacks is open to undergraduate and graduate students as well as new grads of under 1 year from all colleges and universities.' Travel: 'This year, we will be offering travel stipends to a limited number of hackers with regional caps based on the region you are coming from'; most attendees get there themselves (Caltrain, BART). Run by Hackers@Berkeley; held in San Francisco.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Already watched by calhacks</t>
+          <t>Already watched by capitalone-early-career</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Cal Hacks</t>
+          <t>Capital One Analyst / Tech / Product Summits</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Tech internship</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -12220,29 +12334,29 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://www.calhacks.io/</t>
+          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'Cal Hacks is open to undergraduate and graduate students as well as new grads of under 1 year from all colleges and universities.' Travel: 'This year, we will be offering travel stipends to a limited number of hackers with regional caps based on the region you are coming from'; most attendees get there themselves (Caltrain, BART). Run by Hackers@Berkeley; held in San Francisco.</t>
+          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Already watched by caltech-surf</t>
+          <t>Already watched by cerebralvalley-sf-events</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Caltech SURF</t>
+          <t>Cerebral Valley SF &amp; Bay Area AI events calendar</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Tracker / resource</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -12252,61 +12366,61 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://sfp.caltech.edu/undergraduate-research/programs/surf/application_information</t>
+          <t>https://cerebralvalley.ai/events/san-francisco</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Summer Undergraduate Research Fellowship. Open to non-Caltech students, though the page notes they may find it harder to secure a mentor.</t>
+          <t>Verified 2026-10-08: Cerebral Valley's SF and Bay Area AI event feed, mixing hackathons with talks and meetups, e.g. 'The Recursive Agents Hackathon' (Oct 17, Shack15 SF; 'All attendees must apply and be approved') and 'Intelligence at Work Hackathon' (Oct 23, Menlo Park). Not student-specific; check each event's own terms.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Already watched by capitalone-early-career</t>
+          <t>Already watched by citi-pre-internships</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Capital One Analyst / Tech / Product Summits</t>
+          <t>Citi Freshman Discovery</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://www.capitalonecareers.com/get-ahead-with-early-career-programs-for-students</t>
+          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Analyst Summit 'First-year students or sophomores pursuing a quantitative/STEM major'; Tech Summit 'Sophomores with beginner coding experience'. Separate from the Capital One TEIP row.</t>
+          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cerebralvalley-sf-events</t>
+          <t>Already watched by cmu-riss</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Cerebral Valley SF &amp; Bay Area AI events calendar</t>
+          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Tracker / resource</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -12316,93 +12430,93 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://cerebralvalley.ai/events/san-francisco</t>
+          <t>https://riss.ri.cmu.edu/</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: Cerebral Valley's SF and Bay Area AI event feed, mixing hackathons with talks and meetups, e.g. 'The Recursive Agents Hackathon' (Oct 17, Shack15 SF; 'All attendees must apply and be approved') and 'Intelligence at Work Hackathon' (Oct 23, Menlo Park). Not student-specific; check each event's own terms.</t>
+          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Already watched by citi-pre-internships</t>
+          <t>Already watched by comap-mcm</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Citi Freshman Discovery</t>
+          <t>COMAP MCM/ICM</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.citi.com/early-career-programs-pre-internships</t>
+          <t>https://www.contest.comap.com/undergraduate/contests/</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'All first-year students in a four-year bachelor's degree program from a US accredited institution, regardless of major.' 3-day virtual introduction to financial services.</t>
+          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cmu-riss</t>
+          <t>Already watched by cornell-trading-competition</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CMU Robotics Institute Summer Scholars (RISS)</t>
+          <t>Cornell Trading Competition</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://riss.ri.cmu.edu/</t>
+          <t>https://cornellquantfund.org/competition</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>11-week summer research immersion for undergraduates at CMU's Robotics Institute.</t>
+          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Already watched by comap-mcm</t>
+          <t>Already watched by cra-dreu</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>COMAP MCM/ICM</t>
+          <t>CRA DREU</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -12412,29 +12526,29 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://www.contest.comap.com/undergraduate/contests/</t>
+          <t>https://cra.org/cra-wp/dreu/</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'high school students and college undergraduates'; 2027 contest 28 Jan - 1 Feb.</t>
+          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cornell-trading-competition</t>
+          <t>Already watched by cs-social-good-fellowships</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Cornell Trading Competition</t>
+          <t>CS+Social Good Summer Fellowships</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Stanford-only</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -12444,56 +12558,56 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://cornellquantfund.org/competition</t>
+          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Teams of 4, NO EXPERIENCE NECESSARY, $10k+ prizes, Cornell Tech NYC. Case packets released 2 weeks early.</t>
+          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cra-dreu</t>
+          <t>Already watched by curis</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CRA DREU</t>
+          <t>Stanford CURIS</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Stanford-only</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://cra.org/cra-wp/dreu/</t>
+          <t>https://curis.stanford.edu/</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'High school graduates who have been accepted ... are also eligible'; priority to CS majors. Large page (94K chars).</t>
+          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Already watched by cs-social-good-fellowships</t>
+          <t>Already watched by datasurf</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>CS+Social Good Summer Fellowships</t>
+          <t>Stanford DataSURF (formerly SURP-Stats)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -12508,93 +12622,93 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://cardinalservice.stanford.edu/opportunities/cssocial-good-summer-fellowships</t>
+          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30 from the 2026 SOLO listing: 'enrolled as a first-year, sophomore, or junior ... must have completed CS 106B by the end of Spring Quarter.' $7,000 base stipend, full-time summer with a tech-for-good partner. Cardinal Quarter.</t>
+          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Already watched by curis</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Stanford CURIS</t>
+          <t>D. E. Shaw Nexus Fellowship</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://curis.stanford.edu/</t>
+          <t>https://campus.deshaw.com/fellowships</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>CS dept paid summer research. Project list posted late Jan. Also lists year-round projects for units or hourly pay. | Checked 2026-09-26: now watched with render_js - the page is client-rendered and yields 1,264 chars in the browser.</t>
+          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Already watched by datasurf</t>
+          <t>Already watched by deshaw-campus</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Stanford DataSURF (formerly SURP-Stats)</t>
+          <t>D. E. Shaw campus site</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Stanford-only</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Quant firm program</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://datasciencemajor.stanford.edu/research-impact/data-science-undergraduate-research-focus</t>
+          <t>https://campus.deshaw.com/</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-30: 'Stanford undergraduate students from any department who meet the prerequisites are encouraged to apply' (examples: STATS 60, MATH 51-53, CS 106A/B). 10 weeks, $8,500 stipend plus need-based supplement.</t>
+          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by dimacs-reu</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw Nexus Fellowship</t>
+          <t>DIMACS REU</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -12604,125 +12718,125 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/fellowships</t>
+          <t>https://dimacs.rutgers.edu/reu-main</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>THE one for a first-year to target the following year - Nexus is the all-students track. 3 days NYC, $1,500 stipend, travel + lodging. | Checked 2026-09-26: campus.deshaw.com/fellowships now redirects to the campus root, which mentions no fellowships. Kept; the root is watched as deshaw-campus.</t>
+          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Already watched by deshaw-campus</t>
+          <t>Already watched by dukequant-competition</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>D. E. Shaw campus site</t>
+          <t>Duke FinTech Trading Competition</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://campus.deshaw.com/</t>
+          <t>https://www.duke.edu/</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: internships for 'undergraduate and graduate students'. The fellowship rows' campus.deshaw.com/fellowships URL now redirects here; this page is watched so a returning fellowship shows up.</t>
+          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dimacs-reu</t>
+          <t>Already watched by evercore-campus</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>DIMACS REU</t>
+          <t>Evercore student events</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Conference / other</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://dimacs.rutgers.edu/reu-main</t>
+          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'We do not usually admit freshmen' - watch for sophomore year.</t>
+          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Already watched by dukequant-competition</t>
+          <t>Already watched by futureforce-launchpad</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Duke FinTech Trading Competition</t>
+          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>Tech internship</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>LATER</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.duke.edu/</t>
+          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>3 months, paper trading, bracket format. Sponsors include Schonfeld. Lowest time commitment. | Checked 2026-09-26: Duke Quantitative Finance's competition page is dukequant.com/general-7 (watched with render_js); not yet confirmed to be the same event this row names. The listed duke.edu is kept.</t>
+          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Already watched by evercore-campus</t>
+          <t>Already watched by hackgt</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Evercore student events</t>
+          <t>HackGT</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -12732,56 +12846,56 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://evercore.tal.net/vx/mobile-0/candidate/jobboard/vacancy/2/feed</t>
+          <t>https://hack.gt/</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: Oleeo Atom feed, 39 entries; vacancy/1/feed has 29 more. Some events are restricted-audience per the Simplify blog.</t>
+          <t>Verified 2026-10-08 (rendered page): 'If you will be traveling from afar, we offer reimbursements to GT'; the page links a travel guide.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Already watched by futureforce-launchpad</t>
+          <t>Already watched by hackprinceton</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Futureforce Tech Launchpad (CodePath)</t>
+          <t>HackPrinceton</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Tech internship</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>LATER</t>
+          <t>Competition</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://info.codepath.org/futureforce-tech-launchpad</t>
+          <t>https://www.hackprinceton.com/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Students who will complete their sophomore year in Spring 2026' - so summer 2028 for a class of 2030.</t>
+          <t>Verified 2026-10-08: 'Applicants must be matriculated in an undergraduate or graduate program at a college or university.' Travel: 'Some admitted hackers may receive a travel stipend that covers part of their travel expenses.' No cost to apply or attend.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hackgt</t>
+          <t>Already watched by hackumass</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>HackGT</t>
+          <t>HackUMass</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12796,24 +12910,24 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://hack.gt/</t>
+          <t>https://www.hackumass.com/</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08 (rendered page): 'If you will be traveling from afar, we offer reimbursements to GT'; the page links a travel guide.</t>
+          <t>Verified 2026-10-08: 'HackUMass XIV is open to ALL college students, including graduate students, regardless of major!' Travel: 'If you apply by the early application deadline, you have the opportunity to apply for travel reimbursement.' Early applications for XIV were already closed on 2026-10-08.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hackprinceton</t>
+          <t>Already watched by harvard-undergraduate-trading</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>HackPrinceton</t>
+          <t>Harvard Undergraduate Trading Competition</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12828,29 +12942,29 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://www.hackprinceton.com/</t>
+          <t>https://www.huqt.com/</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'Applicants must be matriculated in an undergraduate or graduate program at a college or university.' Travel: 'Some admitted hackers may receive a travel stipend that covers part of their travel expenses.' No cost to apply or attend.</t>
+          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hackumass</t>
+          <t>Already watched by hedgewest-sf-meetup-series</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>HackUMass</t>
+          <t>HedgeWest SF Meetup Series</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Conference / other</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -12860,24 +12974,24 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://www.hackumass.com/</t>
+          <t>https://hedgewestsf.org/</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'HackUMass XIV is open to ALL college students, including graduate students, regardless of major!' Travel: 'If you apply by the early application deadline, you have the opportunity to apply for travel reimbursement.' Early applications for XIV were already closed on 2026-10-08.</t>
+          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Already watched by harvard-undergraduate-trading</t>
+          <t>Already watched by hophacks</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Harvard Undergraduate Trading Competition</t>
+          <t>HopHacks</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12892,29 +13006,29 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.huqt.com/</t>
+          <t>https://hophacks.com/</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Undergraduate intercollegiate trading competition run by Harvard Undergraduate Quantitative Traders. The organisation rebranded: the article's link harvarduqt.com/competition 301-redirects to www.huqt.com/competition, which 404s. The live site is huqt.com and it has an Apply link. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year and team format not published - verify before planning.</t>
+          <t>Verified 2026-10-08: 'We will not be offering individual travel reimbursements. However, please see the busing interest form ... If enough people from your city sign up, we may send a FREE bus.'</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hedgewest-sf-meetup-series</t>
+          <t>Already watched by iaqf-academic-paper-competition</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>HedgeWest SF Meetup Series</t>
+          <t>IAQF Academic Paper Competition</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Conference / other</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -12924,29 +13038,29 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://hedgewestsf.org/</t>
+          <t>https://www.iaqf.org/upcoming-events</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Quant/hedge-fund meetup series in San Francisco - one of the very few items in this article that is geographically local to Stanford. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Verify whether undergraduates may attend.</t>
+          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Already watched by hophacks</t>
+          <t>Already watched by icerm-summer</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>HopHacks</t>
+          <t>Summer@ICERM</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -12956,24 +13070,24 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://hophacks.com/</t>
+          <t>https://icerm.brown.edu/summerug/</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-10-08: 'We will not be offering individual travel reimbursements. However, please see the busing interest form ... If enough people from your city sign up, we may send a FREE bus.'</t>
+          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Already watched by iaqf-academic-paper-competition</t>
+          <t>Already watched by icpc-pnw</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>IAQF Academic Paper Competition</t>
+          <t>ICPC</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -12981,36 +13095,36 @@
           <t>Competition</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>CHECK</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.iaqf.org/upcoming-events</t>
+          <t>https://icpc.global/</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>International Association for Quantitative Finance paper competition. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. A paper is a slower but more durable credential than a trading competition; verify undergraduate eligibility.</t>
+          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icerm-summer</t>
+          <t>Already watched by imc-launchpad-us</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Summer@ICERM</t>
+          <t>IMC Launchpad (US)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -13020,29 +13134,29 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://icerm.brown.edu/summerug/</t>
+          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Verified 2026-09-26: 'Applicants must be matriculating undergraduate students'.</t>
+          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Already watched by icpc-pnw</t>
+          <t>Already watched by imc-prosperity</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>ICPC</t>
+          <t>IMC Prosperity Trading Competition</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -13052,29 +13166,29 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://icpc.global/</t>
+          <t>https://prosperity.imc.com/</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Checked 2026-09-26: icpc.global is a JavaScript shell (53 chars); Stanford's regional, pnw.na.icpc.global, is what is watched.</t>
+          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-launchpad-us</t>
+          <t>Already watched by ipam-rips</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IMC Launchpad (US)</t>
+          <t>IPAM RIPS (UCLA)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Quant firm program</t>
+          <t>Research / math</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -13084,24 +13198,24 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://www.imc.com/us/careers/students-graduates/programs/launchpad</t>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>IMC's US student program - distinct from the EU Business Course and UK Masterclass, which are geography-excluded. Christina Qi's 2026 quant competitions &amp; events list (LinkedIn Pulse), read 2026-09-06. Class year not published; verify.</t>
+          <t>Research in Industrial Projects for Students: teams of undergraduates on sponsored industry problems in applied mathematics.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Already watched by imc-prosperity</t>
+          <t>Already watched by janestreet-fttp</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>IMC Prosperity Trading Competition</t>
+          <t>Jane Street FTTP</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -13116,29 +13230,29 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://prosperity.imc.com/</t>
+          <t>https://www.janestreet.com/join-jane-street/programs-and-events/fttp/</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Teams up to 5, $50,000 pool, fully online. Most accessible serious quant competition. Stanford won top-US in year one.</t>
+          <t>Classes + team-based mock trading. STEM majors, no finance background needed. Rolling - apply week one.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Already watched by ipam-rips</t>
+          <t>Already watched by janestreet-preview</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>IPAM RIPS (UCLA)</t>
+          <t>Jane Street Preview</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Research / math</t>
+          <t>Quant firm program</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -13148,24 +13262,24 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.ipam.ucla.edu/programs/student-research-programs/</t>
+          <t>https